--- a/SmartLicense.xlsx
+++ b/SmartLicense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D755773-3885-4BB1-B372-8EBC8B4153BC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A972B4-E6D1-4B68-8ECA-B08DB140C9AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2379,7 +2379,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-101041E]d\ mmm\ yy;@"/>
-    <numFmt numFmtId="168" formatCode="dd/ดดด/yy"/>
+    <numFmt numFmtId="166" formatCode="dd/ดดด/yy"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -2622,7 +2622,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2648,10 +2648,10 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2663,7 +2663,7 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2679,7 +2679,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -2725,7 +2725,7 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2752,7 +2752,42 @@
     <cellStyle name="Percent 2" xfId="19" xr:uid="{52C74F60-A476-4152-873D-B4183CDD4F15}"/>
     <cellStyle name="Style 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="34">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -13057,7 +13092,7 @@
         <v>775</v>
       </c>
       <c r="F117" s="32">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G117" s="33" t="s">
         <v>3</v>
@@ -14755,7 +14790,7 @@
         <v>775</v>
       </c>
       <c r="F197" s="22">
-        <v>244592</v>
+        <v>244565</v>
       </c>
       <c r="G197" s="13" t="s">
         <v>779</v>
@@ -14952,7 +14987,7 @@
         <v>775</v>
       </c>
       <c r="F206" s="32">
-        <v>244592</v>
+        <v>244565</v>
       </c>
       <c r="G206" s="33" t="s">
         <v>744</v>
@@ -15745,7 +15780,7 @@
         <v>775</v>
       </c>
       <c r="F243" s="32">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G243" s="33" t="s">
         <v>3</v>
@@ -15768,7 +15803,7 @@
         <v>775</v>
       </c>
       <c r="F244" s="32">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G244" s="33" t="s">
         <v>3</v>
@@ -15854,7 +15889,7 @@
         <v>775</v>
       </c>
       <c r="F248" s="32">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G248" s="33" t="s">
         <v>3</v>
@@ -16882,147 +16917,147 @@
     <sortCondition ref="A2:A295"/>
   </sortState>
   <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G295 F261:G275 F277:F295 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204:F205 F4:F5 F51 F27:F28 F56 F65:G100 A3:D295 G203:G211 E3:E296 F102:G202">
-    <cfRule type="expression" dxfId="28" priority="341">
+    <cfRule type="expression" dxfId="33" priority="345">
       <formula>$F2="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G101">
-    <cfRule type="expression" dxfId="27" priority="252">
+    <cfRule type="expression" dxfId="32" priority="256">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="expression" dxfId="26" priority="227">
+    <cfRule type="expression" dxfId="31" priority="231">
       <formula>$F4="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="25" priority="226">
+    <cfRule type="expression" dxfId="30" priority="230">
       <formula>$F5="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="expression" dxfId="24" priority="225">
+    <cfRule type="expression" dxfId="29" priority="229">
       <formula>$F27="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41">
-    <cfRule type="expression" dxfId="23" priority="222">
+    <cfRule type="expression" dxfId="28" priority="226">
       <formula>$F41="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51">
-    <cfRule type="expression" dxfId="22" priority="220">
+    <cfRule type="expression" dxfId="27" priority="224">
       <formula>$F51="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64">
-    <cfRule type="expression" dxfId="21" priority="219">
+    <cfRule type="expression" dxfId="26" priority="223">
       <formula>$F64="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="20" priority="218">
+    <cfRule type="expression" dxfId="25" priority="222">
       <formula>$F56="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="expression" dxfId="19" priority="204">
+    <cfRule type="expression" dxfId="24" priority="208">
       <formula>$F28="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59">
-    <cfRule type="expression" dxfId="18" priority="198">
+    <cfRule type="expression" dxfId="23" priority="202">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="expression" dxfId="17" priority="180">
+    <cfRule type="expression" dxfId="22" priority="184">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A296">
-    <cfRule type="expression" dxfId="16" priority="178">
+    <cfRule type="expression" dxfId="21" priority="182">
       <formula>$F296="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F206">
-    <cfRule type="expression" dxfId="15" priority="173">
+    <cfRule type="expression" dxfId="20" priority="177">
       <formula>$F206="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F203">
-    <cfRule type="expression" dxfId="14" priority="168">
+    <cfRule type="expression" dxfId="19" priority="172">
       <formula>$F203="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="expression" dxfId="13" priority="147">
+    <cfRule type="expression" dxfId="18" priority="151">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G212">
-    <cfRule type="expression" dxfId="12" priority="146">
+    <cfRule type="expression" dxfId="17" priority="150">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B296">
-    <cfRule type="expression" dxfId="11" priority="140">
+    <cfRule type="expression" dxfId="16" priority="144">
       <formula>$F296="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296">
-    <cfRule type="expression" dxfId="10" priority="138">
+    <cfRule type="expression" dxfId="15" priority="142">
       <formula>$F296="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F211">
-    <cfRule type="expression" dxfId="9" priority="137">
+    <cfRule type="expression" dxfId="14" priority="141">
       <formula>$F211="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
-    <cfRule type="expression" dxfId="8" priority="114">
+    <cfRule type="expression" dxfId="13" priority="118">
       <formula>$F236="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F243">
-    <cfRule type="expression" dxfId="7" priority="113">
+    <cfRule type="expression" dxfId="12" priority="117">
       <formula>$F243="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250">
-    <cfRule type="expression" dxfId="6" priority="110">
+    <cfRule type="expression" dxfId="11" priority="114">
       <formula>$F250="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F276">
-    <cfRule type="expression" dxfId="5" priority="109">
+    <cfRule type="expression" dxfId="10" priority="113">
       <formula>$F276="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F232">
+    <cfRule type="expression" dxfId="7" priority="44">
+      <formula>$F232="ปิดชั่วคราว"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F212">
-    <cfRule type="expression" dxfId="4" priority="42">
+    <cfRule type="expression" dxfId="3" priority="4">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F213">
-    <cfRule type="expression" dxfId="3" priority="41">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>$F213="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F232">
-    <cfRule type="expression" dxfId="2" priority="40">
-      <formula>$F232="ปิดชั่วคราว"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F244">
-    <cfRule type="expression" dxfId="1" priority="39">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$F244="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F248">
-    <cfRule type="expression" dxfId="0" priority="38">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$F248="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/SmartLicense.xlsx
+++ b/SmartLicense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A972B4-E6D1-4B68-8ECA-B08DB140C9AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202127F5-0D99-4514-AB71-0FD90C7B2B6E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HardLock!$A$1:$G$296</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HardLock!$A$1:$G$297</definedName>
     <definedName name="Datalist">OFFSET('[1]Data-CPAC'!$A$1,0,0,COUNTA('[1]Data-CPAC'!$A:$A),COUNTA('[1]Data-CPAC'!$1:$1))</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="781">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="784">
   <si>
     <t>ชื่อโรงงาน</t>
   </si>
@@ -2370,6 +2370,15 @@
   </si>
   <si>
     <t>ติดปัญหาเรื่องเครื่องจักร</t>
+  </si>
+  <si>
+    <t>FC018</t>
+  </si>
+  <si>
+    <t>บึงกาฬ</t>
+  </si>
+  <si>
+    <t>หจก.เซ็นจูรี่บึงกาฬ</t>
   </si>
 </sst>
 </file>
@@ -2752,7 +2761,21 @@
     <cellStyle name="Percent 2" xfId="19" xr:uid="{52C74F60-A476-4152-873D-B4183CDD4F15}"/>
     <cellStyle name="Style 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -10612,7 +10635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:XEI296"/>
+  <dimension ref="A1:XEI297"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
@@ -14920,7 +14943,7 @@
         <v>775</v>
       </c>
       <c r="F203" s="22">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G203" s="28" t="s">
         <v>773</v>
@@ -15096,7 +15119,7 @@
         <v>775</v>
       </c>
       <c r="F211" s="32">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G211" s="33" t="s">
         <v>3</v>
@@ -15119,7 +15142,7 @@
         <v>775</v>
       </c>
       <c r="F212" s="32">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G212" s="33" t="s">
         <v>3</v>
@@ -15142,7 +15165,7 @@
         <v>775</v>
       </c>
       <c r="F213" s="32">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G213" s="33" t="s">
         <v>3</v>
@@ -15545,7 +15568,7 @@
         <v>775</v>
       </c>
       <c r="F232" s="32">
-        <v>244561</v>
+        <v>244592</v>
       </c>
       <c r="G232" s="33" t="s">
         <v>3</v>
@@ -16872,23 +16895,22 @@
       <c r="A295" s="15" t="s">
         <v>768</v>
       </c>
-      <c r="B295" s="13" t="s">
-        <v>761</v>
+      <c r="B295" s="8" t="s">
+        <v>783</v>
       </c>
       <c r="C295" s="11" t="s">
-        <v>708</v>
+        <v>781</v>
       </c>
       <c r="D295" s="11" t="s">
-        <v>709</v>
+        <v>782</v>
       </c>
       <c r="E295" s="7" t="s">
         <v>774</v>
       </c>
       <c r="F295" s="22">
-        <v>244653</v>
+        <v>244714</v>
       </c>
       <c r="G295" s="11"/>
-      <c r="XEI295" s="46"/>
     </row>
     <row r="296" spans="1:7 16363:16363" ht="17.5" thickBot="1">
       <c r="A296" s="15" t="s">
@@ -16898,10 +16920,10 @@
         <v>761</v>
       </c>
       <c r="C296" s="11" t="s">
-        <v>759</v>
+        <v>708</v>
       </c>
       <c r="D296" s="11" t="s">
-        <v>760</v>
+        <v>709</v>
       </c>
       <c r="E296" s="7" t="s">
         <v>774</v>
@@ -16910,155 +16932,182 @@
         <v>244653</v>
       </c>
       <c r="G296" s="11"/>
+      <c r="XEI296" s="46"/>
+    </row>
+    <row r="297" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+      <c r="A297" s="15" t="s">
+        <v>768</v>
+      </c>
+      <c r="B297" s="13" t="s">
+        <v>761</v>
+      </c>
+      <c r="C297" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="D297" s="11" t="s">
+        <v>760</v>
+      </c>
+      <c r="E297" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="F297" s="22">
+        <v>244653</v>
+      </c>
+      <c r="G297" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G296" xr:uid="{8617D22F-2FD7-43CE-8F40-2261BDA11212}"/>
-  <sortState ref="A2:G295">
-    <sortCondition ref="A2:A295"/>
+  <autoFilter ref="A1:G297" xr:uid="{8617D22F-2FD7-43CE-8F40-2261BDA11212}"/>
+  <sortState ref="A2:G296">
+    <sortCondition ref="A2:A296"/>
   </sortState>
-  <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G295 F261:G275 F277:F295 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204:F205 F4:F5 F51 F27:F28 F56 F65:G100 A3:D295 G203:G211 E3:E296 F102:G202">
-    <cfRule type="expression" dxfId="33" priority="345">
+  <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G293 F261:G275 F277:F293 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204:F205 F4:F5 F51 F27:F28 F56 F65:G100 G203:G211 A3:E293 F102:G202 E295:E297 A295:D296 F295:G296">
+    <cfRule type="expression" dxfId="35" priority="346">
       <formula>$F2="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G101">
-    <cfRule type="expression" dxfId="32" priority="256">
+    <cfRule type="expression" dxfId="34" priority="257">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="expression" dxfId="31" priority="231">
+    <cfRule type="expression" dxfId="33" priority="232">
       <formula>$F4="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="30" priority="230">
+    <cfRule type="expression" dxfId="32" priority="231">
       <formula>$F5="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="expression" dxfId="29" priority="229">
+    <cfRule type="expression" dxfId="31" priority="230">
       <formula>$F27="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41">
-    <cfRule type="expression" dxfId="28" priority="226">
+    <cfRule type="expression" dxfId="30" priority="227">
       <formula>$F41="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51">
-    <cfRule type="expression" dxfId="27" priority="224">
+    <cfRule type="expression" dxfId="29" priority="225">
       <formula>$F51="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64">
-    <cfRule type="expression" dxfId="26" priority="223">
+    <cfRule type="expression" dxfId="28" priority="224">
       <formula>$F64="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="25" priority="222">
+    <cfRule type="expression" dxfId="27" priority="223">
       <formula>$F56="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="expression" dxfId="24" priority="208">
+    <cfRule type="expression" dxfId="26" priority="209">
       <formula>$F28="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59">
-    <cfRule type="expression" dxfId="23" priority="202">
+    <cfRule type="expression" dxfId="25" priority="203">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="expression" dxfId="22" priority="184">
+    <cfRule type="expression" dxfId="24" priority="185">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A296">
-    <cfRule type="expression" dxfId="21" priority="182">
-      <formula>$F296="ปิดชั่วคราว"</formula>
+  <conditionalFormatting sqref="A297">
+    <cfRule type="expression" dxfId="23" priority="183">
+      <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F206">
-    <cfRule type="expression" dxfId="20" priority="177">
+    <cfRule type="expression" dxfId="22" priority="178">
       <formula>$F206="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F203">
-    <cfRule type="expression" dxfId="19" priority="172">
+    <cfRule type="expression" dxfId="21" priority="173">
       <formula>$F203="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="expression" dxfId="18" priority="151">
+    <cfRule type="expression" dxfId="20" priority="152">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G212">
-    <cfRule type="expression" dxfId="17" priority="150">
+    <cfRule type="expression" dxfId="19" priority="151">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B296">
-    <cfRule type="expression" dxfId="16" priority="144">
-      <formula>$F296="ปิดชั่วคราว"</formula>
+  <conditionalFormatting sqref="B297">
+    <cfRule type="expression" dxfId="18" priority="145">
+      <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F296">
-    <cfRule type="expression" dxfId="15" priority="142">
-      <formula>$F296="ปิดชั่วคราว"</formula>
+  <conditionalFormatting sqref="F297">
+    <cfRule type="expression" dxfId="17" priority="143">
+      <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F211">
-    <cfRule type="expression" dxfId="14" priority="141">
+    <cfRule type="expression" dxfId="16" priority="142">
       <formula>$F211="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
-    <cfRule type="expression" dxfId="13" priority="118">
+    <cfRule type="expression" dxfId="15" priority="119">
       <formula>$F236="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F243">
-    <cfRule type="expression" dxfId="12" priority="117">
+    <cfRule type="expression" dxfId="14" priority="118">
       <formula>$F243="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250">
-    <cfRule type="expression" dxfId="11" priority="114">
+    <cfRule type="expression" dxfId="13" priority="115">
       <formula>$F250="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F276">
-    <cfRule type="expression" dxfId="10" priority="113">
+    <cfRule type="expression" dxfId="12" priority="114">
       <formula>$F276="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F232">
-    <cfRule type="expression" dxfId="7" priority="44">
+    <cfRule type="expression" dxfId="9" priority="45">
       <formula>$F232="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F248">
+    <cfRule type="expression" dxfId="6" priority="2">
+      <formula>$F248="ปิดชั่วคราว"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F212">
-    <cfRule type="expression" dxfId="3" priority="4">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F213">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="4" priority="4">
       <formula>$F213="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F244">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="3">
       <formula>$F244="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F248">
+  <conditionalFormatting sqref="A294:G294">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$F248="ปิดชั่วคราว"</formula>
+      <formula>$F294="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SmartLicense.xlsx
+++ b/SmartLicense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202127F5-0D99-4514-AB71-0FD90C7B2B6E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D75DF2-5252-4175-9340-3C5F01B64152}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2761,49 +2761,7 @@
     <cellStyle name="Percent 2" xfId="19" xr:uid="{52C74F60-A476-4152-873D-B4183CDD4F15}"/>
     <cellStyle name="Style 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <fill>
         <patternFill>
@@ -14813,7 +14771,7 @@
         <v>775</v>
       </c>
       <c r="F197" s="22">
-        <v>244565</v>
+        <v>244592</v>
       </c>
       <c r="G197" s="13" t="s">
         <v>779</v>
@@ -15010,7 +14968,7 @@
         <v>775</v>
       </c>
       <c r="F206" s="32">
-        <v>244565</v>
+        <v>244592</v>
       </c>
       <c r="G206" s="33" t="s">
         <v>744</v>
@@ -16961,147 +16919,147 @@
     <sortCondition ref="A2:A296"/>
   </sortState>
   <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G293 F261:G275 F277:F293 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204:F205 F4:F5 F51 F27:F28 F56 F65:G100 G203:G211 A3:E293 F102:G202 E295:E297 A295:D296 F295:G296">
-    <cfRule type="expression" dxfId="35" priority="346">
+    <cfRule type="expression" dxfId="29" priority="346">
       <formula>$F2="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G101">
-    <cfRule type="expression" dxfId="34" priority="257">
+    <cfRule type="expression" dxfId="28" priority="257">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="expression" dxfId="33" priority="232">
+    <cfRule type="expression" dxfId="27" priority="232">
       <formula>$F4="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="32" priority="231">
+    <cfRule type="expression" dxfId="26" priority="231">
       <formula>$F5="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="expression" dxfId="31" priority="230">
+    <cfRule type="expression" dxfId="25" priority="230">
       <formula>$F27="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41">
-    <cfRule type="expression" dxfId="30" priority="227">
+    <cfRule type="expression" dxfId="24" priority="227">
       <formula>$F41="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51">
-    <cfRule type="expression" dxfId="29" priority="225">
+    <cfRule type="expression" dxfId="23" priority="225">
       <formula>$F51="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64">
-    <cfRule type="expression" dxfId="28" priority="224">
+    <cfRule type="expression" dxfId="22" priority="224">
       <formula>$F64="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="27" priority="223">
+    <cfRule type="expression" dxfId="21" priority="223">
       <formula>$F56="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="expression" dxfId="26" priority="209">
+    <cfRule type="expression" dxfId="20" priority="209">
       <formula>$F28="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59">
-    <cfRule type="expression" dxfId="25" priority="203">
+    <cfRule type="expression" dxfId="19" priority="203">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="expression" dxfId="24" priority="185">
+    <cfRule type="expression" dxfId="18" priority="185">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A297">
-    <cfRule type="expression" dxfId="23" priority="183">
+    <cfRule type="expression" dxfId="17" priority="183">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F206">
-    <cfRule type="expression" dxfId="22" priority="178">
+    <cfRule type="expression" dxfId="16" priority="178">
       <formula>$F206="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F203">
-    <cfRule type="expression" dxfId="21" priority="173">
+    <cfRule type="expression" dxfId="15" priority="173">
       <formula>$F203="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="expression" dxfId="20" priority="152">
+    <cfRule type="expression" dxfId="14" priority="152">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G212">
-    <cfRule type="expression" dxfId="19" priority="151">
+    <cfRule type="expression" dxfId="13" priority="151">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B297">
-    <cfRule type="expression" dxfId="18" priority="145">
+    <cfRule type="expression" dxfId="12" priority="145">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F297">
-    <cfRule type="expression" dxfId="17" priority="143">
+    <cfRule type="expression" dxfId="11" priority="143">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F211">
-    <cfRule type="expression" dxfId="16" priority="142">
+    <cfRule type="expression" dxfId="10" priority="142">
       <formula>$F211="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
-    <cfRule type="expression" dxfId="15" priority="119">
+    <cfRule type="expression" dxfId="9" priority="119">
       <formula>$F236="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F243">
-    <cfRule type="expression" dxfId="14" priority="118">
+    <cfRule type="expression" dxfId="8" priority="118">
       <formula>$F243="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250">
-    <cfRule type="expression" dxfId="13" priority="115">
+    <cfRule type="expression" dxfId="7" priority="115">
       <formula>$F250="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F276">
-    <cfRule type="expression" dxfId="12" priority="114">
+    <cfRule type="expression" dxfId="6" priority="114">
       <formula>$F276="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F232">
-    <cfRule type="expression" dxfId="9" priority="45">
+    <cfRule type="expression" dxfId="5" priority="45">
       <formula>$F232="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F248">
-    <cfRule type="expression" dxfId="6" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>$F248="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F212">
-    <cfRule type="expression" dxfId="5" priority="5">
+    <cfRule type="expression" dxfId="3" priority="5">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F213">
-    <cfRule type="expression" dxfId="4" priority="4">
+    <cfRule type="expression" dxfId="2" priority="4">
       <formula>$F213="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F244">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$F244="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/SmartLicense.xlsx
+++ b/SmartLicense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D75DF2-5252-4175-9340-3C5F01B64152}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A25A9DFD-16BF-4B39-A3FA-468C9EFC891D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HardLock!$A$1:$G$297</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">HardLock!$A$1:$I$297</definedName>
     <definedName name="Datalist">OFFSET('[1]Data-CPAC'!$A$1,0,0,COUNTA('[1]Data-CPAC'!$A:$A),COUNTA('[1]Data-CPAC'!$1:$1))</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1516" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="790">
   <si>
     <t>ชื่อโรงงาน</t>
   </si>
@@ -2379,6 +2379,24 @@
   </si>
   <si>
     <t>หจก.เซ็นจูรี่บึงกาฬ</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>สัญญา</t>
+  </si>
+  <si>
+    <t>วงเงินรวม SCG</t>
+  </si>
+  <si>
+    <t>ค้ำประกันรายได้</t>
+  </si>
+  <si>
+    <t>ค้ำเงินสด</t>
+  </si>
+  <si>
+    <t>31 มี.ค. 72</t>
   </si>
 </sst>
 </file>
@@ -2500,7 +2518,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2541,6 +2559,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -2609,7 +2633,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2737,6 +2761,10 @@
     <xf numFmtId="166" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="21">
     <cellStyle name="Comma 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2761,7 +2789,49 @@
     <cellStyle name="Percent 2" xfId="19" xr:uid="{52C74F60-A476-4152-873D-B4183CDD4F15}"/>
     <cellStyle name="Style 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
-  <dxfs count="30">
+  <dxfs count="36">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -10603,10 +10673,12 @@
     <col min="5" max="5" width="12.7265625" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.08984375" style="3" customWidth="1"/>
     <col min="7" max="7" width="27.54296875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.81640625" style="5"/>
+    <col min="8" max="8" width="12.90625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="13.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.81640625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="17.5" thickBot="1">
+    <row r="1" spans="1:9" ht="17.5" thickBot="1">
       <c r="A1" s="6" t="s">
         <v>398</v>
       </c>
@@ -10628,8 +10700,14 @@
       <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H1" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="I1" s="51" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A2" s="7" t="s">
         <v>771</v>
       </c>
@@ -10649,8 +10727,14 @@
         <v>244683</v>
       </c>
       <c r="G2" s="10"/>
-    </row>
-    <row r="3" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H2" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I2" s="52">
+        <v>245230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A3" s="7" t="s">
         <v>771</v>
       </c>
@@ -10670,8 +10754,14 @@
         <v>244683</v>
       </c>
       <c r="G3" s="10"/>
-    </row>
-    <row r="4" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H3" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I3" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A4" s="7" t="s">
         <v>771</v>
       </c>
@@ -10691,8 +10781,14 @@
         <v>244683</v>
       </c>
       <c r="G4" s="10"/>
-    </row>
-    <row r="5" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H4" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I4" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A5" s="7" t="s">
         <v>771</v>
       </c>
@@ -10712,8 +10808,14 @@
         <v>244683</v>
       </c>
       <c r="G5" s="10"/>
-    </row>
-    <row r="6" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H5" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I5" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A6" s="7" t="s">
         <v>769</v>
       </c>
@@ -10733,8 +10835,14 @@
         <v>244683</v>
       </c>
       <c r="G6" s="10"/>
-    </row>
-    <row r="7" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H6" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I6" s="52">
+        <v>244866</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A7" s="7" t="s">
         <v>769</v>
       </c>
@@ -10754,8 +10862,14 @@
         <v>244683</v>
       </c>
       <c r="G7" s="10"/>
-    </row>
-    <row r="8" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H7" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I7" s="52">
+        <v>244866</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A8" s="7" t="s">
         <v>769</v>
       </c>
@@ -10775,8 +10889,14 @@
         <v>244683</v>
       </c>
       <c r="G8" s="13"/>
-    </row>
-    <row r="9" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H8" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I8" s="52">
+        <v>244866</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A9" s="7" t="s">
         <v>769</v>
       </c>
@@ -10796,8 +10916,14 @@
         <v>244683</v>
       </c>
       <c r="G9" s="11"/>
-    </row>
-    <row r="10" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H9" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I9" s="52">
+        <v>244866</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A10" s="7" t="s">
         <v>769</v>
       </c>
@@ -10817,8 +10943,14 @@
         <v>244683</v>
       </c>
       <c r="G10" s="11"/>
-    </row>
-    <row r="11" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H10" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I10" s="52">
+        <v>245291</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A11" s="7" t="s">
         <v>769</v>
       </c>
@@ -10838,8 +10970,14 @@
         <v>244683</v>
       </c>
       <c r="G11" s="10"/>
-    </row>
-    <row r="12" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H11" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I11" s="52">
+        <v>245072</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A12" s="7" t="s">
         <v>769</v>
       </c>
@@ -10859,8 +10997,14 @@
         <v>244683</v>
       </c>
       <c r="G12" s="11"/>
-    </row>
-    <row r="13" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H12" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I12" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A13" s="7" t="s">
         <v>769</v>
       </c>
@@ -10880,8 +11024,14 @@
         <v>244683</v>
       </c>
       <c r="G13" s="10"/>
-    </row>
-    <row r="14" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H13" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I13" s="52">
+        <v>245048</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A14" s="7" t="s">
         <v>769</v>
       </c>
@@ -10901,8 +11051,14 @@
         <v>244683</v>
       </c>
       <c r="G14" s="10"/>
-    </row>
-    <row r="15" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H14" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I14" s="52">
+        <v>245048</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A15" s="7" t="s">
         <v>769</v>
       </c>
@@ -10922,8 +11078,14 @@
         <v>244683</v>
       </c>
       <c r="G15" s="10"/>
-    </row>
-    <row r="16" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H15" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I15" s="52">
+        <v>245048</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A16" s="7" t="s">
         <v>769</v>
       </c>
@@ -10943,8 +11105,14 @@
         <v>244683</v>
       </c>
       <c r="G16" s="10"/>
-    </row>
-    <row r="17" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H16" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I16" s="52">
+        <v>245048</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A17" s="7" t="s">
         <v>769</v>
       </c>
@@ -10964,8 +11132,14 @@
         <v>244683</v>
       </c>
       <c r="G17" s="10"/>
-    </row>
-    <row r="18" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H17" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I17" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A18" s="7" t="s">
         <v>769</v>
       </c>
@@ -10985,8 +11159,14 @@
         <v>244683</v>
       </c>
       <c r="G18" s="10"/>
-    </row>
-    <row r="19" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H18" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I18" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A19" s="7" t="s">
         <v>769</v>
       </c>
@@ -11006,8 +11186,14 @@
         <v>244683</v>
       </c>
       <c r="G19" s="11"/>
-    </row>
-    <row r="20" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H19" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I19" s="52">
+        <v>245535</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A20" s="7" t="s">
         <v>769</v>
       </c>
@@ -11027,8 +11213,14 @@
         <v>244683</v>
       </c>
       <c r="G20" s="10"/>
-    </row>
-    <row r="21" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H20" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I20" s="52">
+        <v>245019</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A21" s="7" t="s">
         <v>769</v>
       </c>
@@ -11048,8 +11240,14 @@
         <v>244683</v>
       </c>
       <c r="G21" s="11"/>
-    </row>
-    <row r="22" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H21" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I21" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A22" s="7" t="s">
         <v>769</v>
       </c>
@@ -11069,8 +11267,14 @@
         <v>244683</v>
       </c>
       <c r="G22" s="11"/>
-    </row>
-    <row r="23" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H22" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I22" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A23" s="7" t="s">
         <v>769</v>
       </c>
@@ -11090,8 +11294,14 @@
         <v>244683</v>
       </c>
       <c r="G23" s="14"/>
-    </row>
-    <row r="24" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H23" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I23" s="52">
+        <v>244877</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A24" s="7" t="s">
         <v>769</v>
       </c>
@@ -11111,8 +11321,14 @@
         <v>244683</v>
       </c>
       <c r="G24" s="14"/>
-    </row>
-    <row r="25" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H24" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I24" s="52">
+        <v>244877</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A25" s="7" t="s">
         <v>769</v>
       </c>
@@ -11132,8 +11348,14 @@
         <v>244683</v>
       </c>
       <c r="G25" s="14"/>
-    </row>
-    <row r="26" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H25" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I25" s="52">
+        <v>244877</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A26" s="7" t="s">
         <v>769</v>
       </c>
@@ -11153,8 +11375,14 @@
         <v>244683</v>
       </c>
       <c r="G26" s="10"/>
-    </row>
-    <row r="27" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H26" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I26" s="52">
+        <v>245533</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A27" s="7" t="s">
         <v>770</v>
       </c>
@@ -11174,8 +11402,14 @@
         <v>244683</v>
       </c>
       <c r="G27" s="10"/>
-    </row>
-    <row r="28" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H27" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I27" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A28" s="7" t="s">
         <v>770</v>
       </c>
@@ -11195,8 +11429,14 @@
         <v>244683</v>
       </c>
       <c r="G28" s="10"/>
-    </row>
-    <row r="29" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H28" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I28" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A29" s="7" t="s">
         <v>770</v>
       </c>
@@ -11216,8 +11456,14 @@
         <v>244622</v>
       </c>
       <c r="G29" s="10"/>
-    </row>
-    <row r="30" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H29" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I29" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A30" s="7" t="s">
         <v>770</v>
       </c>
@@ -11237,8 +11483,14 @@
         <v>244622</v>
       </c>
       <c r="G30" s="10"/>
-    </row>
-    <row r="31" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H30" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I30" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A31" s="7" t="s">
         <v>770</v>
       </c>
@@ -11258,8 +11510,14 @@
         <v>244683</v>
       </c>
       <c r="G31" s="10"/>
-    </row>
-    <row r="32" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H31" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I31" s="52">
+        <v>244675</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A32" s="7" t="s">
         <v>770</v>
       </c>
@@ -11279,8 +11537,14 @@
         <v>244683</v>
       </c>
       <c r="G32" s="10"/>
-    </row>
-    <row r="33" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H32" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I32" s="52">
+        <v>244675</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A33" s="7" t="s">
         <v>770</v>
       </c>
@@ -11300,8 +11564,14 @@
         <v>244683</v>
       </c>
       <c r="G33" s="10"/>
-    </row>
-    <row r="34" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H33" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I33" s="52">
+        <v>245048</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A34" s="7" t="s">
         <v>770</v>
       </c>
@@ -11321,8 +11591,14 @@
         <v>244683</v>
       </c>
       <c r="G34" s="11"/>
-    </row>
-    <row r="35" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H34" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I34" s="52">
+        <v>245048</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A35" s="15" t="s">
         <v>770</v>
       </c>
@@ -11342,8 +11618,14 @@
         <v>244683</v>
       </c>
       <c r="G35" s="10"/>
-    </row>
-    <row r="36" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H35" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I35" s="52">
+        <v>245048</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A36" s="7" t="s">
         <v>770</v>
       </c>
@@ -11363,8 +11645,14 @@
         <v>244683</v>
       </c>
       <c r="G36" s="11"/>
-    </row>
-    <row r="37" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H36" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I36" s="52">
+        <v>244865</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A37" s="7" t="s">
         <v>770</v>
       </c>
@@ -11384,8 +11672,14 @@
         <v>244683</v>
       </c>
       <c r="G37" s="11"/>
-    </row>
-    <row r="38" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H37" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I37" s="52">
+        <v>244865</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="7" t="s">
         <v>770</v>
       </c>
@@ -11405,8 +11699,14 @@
         <v>244683</v>
       </c>
       <c r="G38" s="11"/>
-    </row>
-    <row r="39" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H38" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I38" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A39" s="7" t="s">
         <v>770</v>
       </c>
@@ -11426,8 +11726,14 @@
         <v>244683</v>
       </c>
       <c r="G39" s="16"/>
-    </row>
-    <row r="40" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H39" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I39" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A40" s="7" t="s">
         <v>770</v>
       </c>
@@ -11447,8 +11753,14 @@
         <v>244683</v>
       </c>
       <c r="G40" s="10"/>
-    </row>
-    <row r="41" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H40" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I40" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A41" s="7" t="s">
         <v>770</v>
       </c>
@@ -11468,8 +11780,14 @@
         <v>244683</v>
       </c>
       <c r="G41" s="10"/>
-    </row>
-    <row r="42" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H41" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I41" s="52">
+        <v>245595</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A42" s="7" t="s">
         <v>770</v>
       </c>
@@ -11489,8 +11807,14 @@
         <v>244683</v>
       </c>
       <c r="G42" s="10"/>
-    </row>
-    <row r="43" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H42" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I42" s="52">
+        <v>245595</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A43" s="15" t="s">
         <v>770</v>
       </c>
@@ -11510,8 +11834,14 @@
         <v>244683</v>
       </c>
       <c r="G43" s="10"/>
-    </row>
-    <row r="44" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H43" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I43" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A44" s="15" t="s">
         <v>770</v>
       </c>
@@ -11531,8 +11861,14 @@
         <v>244683</v>
       </c>
       <c r="G44" s="11"/>
-    </row>
-    <row r="45" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H44" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I44" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A45" s="7" t="s">
         <v>770</v>
       </c>
@@ -11552,8 +11888,14 @@
         <v>244683</v>
       </c>
       <c r="G45" s="16"/>
-    </row>
-    <row r="46" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H45" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I45" s="52">
+        <v>245595</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A46" s="15" t="s">
         <v>770</v>
       </c>
@@ -11573,8 +11915,14 @@
         <v>244683</v>
       </c>
       <c r="G46" s="11"/>
-    </row>
-    <row r="47" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H46" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I46" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A47" s="7" t="s">
         <v>770</v>
       </c>
@@ -11594,8 +11942,14 @@
         <v>244683</v>
       </c>
       <c r="G47" s="10"/>
-    </row>
-    <row r="48" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H47" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I47" s="52">
+        <v>245107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A48" s="7" t="s">
         <v>770</v>
       </c>
@@ -11615,8 +11969,14 @@
         <v>244683</v>
       </c>
       <c r="G48" s="10"/>
-    </row>
-    <row r="49" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H48" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I48" s="52">
+        <v>245107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A49" s="15" t="s">
         <v>770</v>
       </c>
@@ -11636,8 +11996,14 @@
         <v>244683</v>
       </c>
       <c r="G49" s="10"/>
-    </row>
-    <row r="50" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H49" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I49" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A50" s="4" t="s">
         <v>770</v>
       </c>
@@ -11659,8 +12025,12 @@
       <c r="G50" s="20" t="s">
         <v>772</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H50" s="52"/>
+      <c r="I50" s="52" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A51" s="7" t="s">
         <v>770</v>
       </c>
@@ -11680,8 +12050,14 @@
         <v>244683</v>
       </c>
       <c r="G51" s="10"/>
-    </row>
-    <row r="52" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H51" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I51" s="52">
+        <v>245595</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A52" s="7" t="s">
         <v>770</v>
       </c>
@@ -11701,8 +12077,14 @@
         <v>244683</v>
       </c>
       <c r="G52" s="11"/>
-    </row>
-    <row r="53" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H52" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I52" s="52">
+        <v>244865</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A53" s="7" t="s">
         <v>770</v>
       </c>
@@ -11722,8 +12104,14 @@
         <v>244683</v>
       </c>
       <c r="G53" s="11"/>
-    </row>
-    <row r="54" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H53" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I53" s="52">
+        <v>244865</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A54" s="7" t="s">
         <v>770</v>
       </c>
@@ -11743,8 +12131,14 @@
         <v>244683</v>
       </c>
       <c r="G54" s="11"/>
-    </row>
-    <row r="55" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H54" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I54" s="52">
+        <v>244865</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A55" s="7" t="s">
         <v>770</v>
       </c>
@@ -11764,8 +12158,14 @@
         <v>244622</v>
       </c>
       <c r="G55" s="11"/>
-    </row>
-    <row r="56" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H55" s="52">
+        <v>244864</v>
+      </c>
+      <c r="I55" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A56" s="7" t="s">
         <v>770</v>
       </c>
@@ -11785,8 +12185,14 @@
         <v>244683</v>
       </c>
       <c r="G56" s="10"/>
-    </row>
-    <row r="57" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H56" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I56" s="52">
+        <v>245533</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A57" s="7" t="s">
         <v>770</v>
       </c>
@@ -11806,8 +12212,14 @@
         <v>244683</v>
       </c>
       <c r="G57" s="10"/>
-    </row>
-    <row r="58" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H57" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I57" s="52">
+        <v>245791</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A58" s="7" t="s">
         <v>770</v>
       </c>
@@ -11827,8 +12239,14 @@
         <v>244683</v>
       </c>
       <c r="G58" s="11"/>
-    </row>
-    <row r="59" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H58" s="52">
+        <v>245779</v>
+      </c>
+      <c r="I58" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A59" s="7" t="s">
         <v>770</v>
       </c>
@@ -11848,8 +12266,14 @@
         <v>244653</v>
       </c>
       <c r="G59" s="11"/>
-    </row>
-    <row r="60" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H59" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I59" s="52">
+        <v>244654</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A60" s="7" t="s">
         <v>770</v>
       </c>
@@ -11869,8 +12293,14 @@
         <v>244683</v>
       </c>
       <c r="G60" s="11"/>
-    </row>
-    <row r="61" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H60" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I60" s="52">
+        <v>244908</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A61" s="7" t="s">
         <v>770</v>
       </c>
@@ -11890,8 +12320,14 @@
         <v>244683</v>
       </c>
       <c r="G61" s="11"/>
-    </row>
-    <row r="62" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H61" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I61" s="52">
+        <v>245483</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A62" s="7" t="s">
         <v>770</v>
       </c>
@@ -11911,8 +12347,14 @@
         <v>244683</v>
       </c>
       <c r="G62" s="10"/>
-    </row>
-    <row r="63" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H62" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I62" s="52">
+        <v>244906</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A63" s="7" t="s">
         <v>770</v>
       </c>
@@ -11932,8 +12374,14 @@
         <v>244683</v>
       </c>
       <c r="G63" s="10"/>
-    </row>
-    <row r="64" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H63" s="52">
+        <v>245048</v>
+      </c>
+      <c r="I63" s="52">
+        <v>244779</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A64" s="7" t="s">
         <v>770</v>
       </c>
@@ -11953,8 +12401,14 @@
         <v>244683</v>
       </c>
       <c r="G64" s="10"/>
-    </row>
-    <row r="65" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H64" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I64" s="52">
+        <v>245644</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A65" s="15" t="s">
         <v>770</v>
       </c>
@@ -11974,8 +12428,14 @@
         <v>244683</v>
       </c>
       <c r="G65" s="11"/>
-    </row>
-    <row r="66" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H65" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I65" s="52">
+        <v>245157</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A66" s="7" t="s">
         <v>770</v>
       </c>
@@ -11995,8 +12455,14 @@
         <v>244683</v>
       </c>
       <c r="G66" s="10"/>
-    </row>
-    <row r="67" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H66" s="52">
+        <v>244683</v>
+      </c>
+      <c r="I66" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A67" s="15" t="s">
         <v>770</v>
       </c>
@@ -12016,8 +12482,14 @@
         <v>244683</v>
       </c>
       <c r="G67" s="11"/>
-    </row>
-    <row r="68" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H67" s="52">
+        <v>245413</v>
+      </c>
+      <c r="I67" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A68" s="7" t="s">
         <v>766</v>
       </c>
@@ -12037,8 +12509,14 @@
         <v>244622</v>
       </c>
       <c r="G68" s="13"/>
-    </row>
-    <row r="69" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H68" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I68" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A69" s="7" t="s">
         <v>766</v>
       </c>
@@ -12058,8 +12536,14 @@
         <v>244622</v>
       </c>
       <c r="G69" s="23"/>
-    </row>
-    <row r="70" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H69" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I69" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A70" s="7" t="s">
         <v>766</v>
       </c>
@@ -12079,8 +12563,14 @@
         <v>244622</v>
       </c>
       <c r="G70" s="13"/>
-    </row>
-    <row r="71" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H70" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I70" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A71" s="7" t="s">
         <v>766</v>
       </c>
@@ -12100,8 +12590,14 @@
         <v>244622</v>
       </c>
       <c r="G71" s="14"/>
-    </row>
-    <row r="72" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H71" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I71" s="52">
+        <v>244988</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A72" s="7" t="s">
         <v>766</v>
       </c>
@@ -12123,8 +12619,14 @@
       <c r="G72" s="14" t="s">
         <v>751</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H72" s="52">
+        <v>244257</v>
+      </c>
+      <c r="I72" s="52">
+        <v>244988</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A73" s="7" t="s">
         <v>766</v>
       </c>
@@ -12144,8 +12646,14 @@
         <v>244622</v>
       </c>
       <c r="G73" s="23"/>
-    </row>
-    <row r="74" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H73" s="52">
+        <v>244257</v>
+      </c>
+      <c r="I73" s="52">
+        <v>245535</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A74" s="7" t="s">
         <v>766</v>
       </c>
@@ -12165,8 +12673,14 @@
         <v>244622</v>
       </c>
       <c r="G74" s="13"/>
-    </row>
-    <row r="75" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H74" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I74" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A75" s="7" t="s">
         <v>766</v>
       </c>
@@ -12186,8 +12700,14 @@
         <v>244622</v>
       </c>
       <c r="G75" s="13"/>
-    </row>
-    <row r="76" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H75" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I75" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A76" s="7" t="s">
         <v>766</v>
       </c>
@@ -12207,8 +12727,14 @@
         <v>244622</v>
       </c>
       <c r="G76" s="23"/>
-    </row>
-    <row r="77" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H76" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I76" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A77" s="7" t="s">
         <v>766</v>
       </c>
@@ -12228,8 +12754,14 @@
         <v>244622</v>
       </c>
       <c r="G77" s="14"/>
-    </row>
-    <row r="78" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H77" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I77" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A78" s="7" t="s">
         <v>766</v>
       </c>
@@ -12249,8 +12781,14 @@
         <v>244622</v>
       </c>
       <c r="G78" s="11"/>
-    </row>
-    <row r="79" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H78" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I78" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A79" s="48" t="s">
         <v>766</v>
       </c>
@@ -12272,8 +12810,14 @@
       <c r="G79" s="20" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H79" s="52">
+        <v>242430</v>
+      </c>
+      <c r="I79" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A80" s="48" t="s">
         <v>766</v>
       </c>
@@ -12295,8 +12839,14 @@
       <c r="G80" s="20" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H80" s="52">
+        <v>242430</v>
+      </c>
+      <c r="I80" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A81" s="7" t="s">
         <v>766</v>
       </c>
@@ -12316,8 +12866,14 @@
         <v>244622</v>
       </c>
       <c r="G81" s="13"/>
-    </row>
-    <row r="82" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H81" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I81" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A82" s="15" t="s">
         <v>766</v>
       </c>
@@ -12337,8 +12893,14 @@
         <v>244622</v>
       </c>
       <c r="G82" s="14"/>
-    </row>
-    <row r="83" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H82" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I82" s="52">
+        <v>244714</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A83" s="7" t="s">
         <v>766</v>
       </c>
@@ -12358,8 +12920,14 @@
         <v>244622</v>
       </c>
       <c r="G83" s="14"/>
-    </row>
-    <row r="84" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H83" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I83" s="52">
+        <v>245535</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A84" s="7" t="s">
         <v>766</v>
       </c>
@@ -12379,8 +12947,14 @@
         <v>244622</v>
       </c>
       <c r="G84" s="13"/>
-    </row>
-    <row r="85" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H84" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I84" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A85" s="7" t="s">
         <v>766</v>
       </c>
@@ -12400,8 +12974,14 @@
         <v>244622</v>
       </c>
       <c r="G85" s="23"/>
-    </row>
-    <row r="86" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H85" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I85" s="52">
+        <v>245648</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A86" s="7" t="s">
         <v>766</v>
       </c>
@@ -12421,8 +13001,14 @@
         <v>244622</v>
       </c>
       <c r="G86" s="13"/>
-    </row>
-    <row r="87" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H86" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I86" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A87" s="7" t="s">
         <v>766</v>
       </c>
@@ -12442,8 +13028,14 @@
         <v>244622</v>
       </c>
       <c r="G87" s="13"/>
-    </row>
-    <row r="88" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H87" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I87" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A88" s="7" t="s">
         <v>766</v>
       </c>
@@ -12463,8 +13055,14 @@
         <v>244622</v>
       </c>
       <c r="G88" s="13"/>
-    </row>
-    <row r="89" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H88" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I88" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A89" s="7" t="s">
         <v>766</v>
       </c>
@@ -12484,8 +13082,14 @@
         <v>244622</v>
       </c>
       <c r="G89" s="14"/>
-    </row>
-    <row r="90" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H89" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I89" s="52">
+        <v>245317</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A90" s="7" t="s">
         <v>766</v>
       </c>
@@ -12505,8 +13109,14 @@
         <v>244622</v>
       </c>
       <c r="G90" s="14"/>
-    </row>
-    <row r="91" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H90" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I90" s="52">
+        <v>245317</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A91" s="24" t="s">
         <v>766</v>
       </c>
@@ -12528,8 +13138,14 @@
       <c r="G91" s="27" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H91" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I91" s="52">
+        <v>244987</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A92" s="7" t="s">
         <v>766</v>
       </c>
@@ -12549,8 +13165,14 @@
         <v>244622</v>
       </c>
       <c r="G92" s="13"/>
-    </row>
-    <row r="93" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H92" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I92" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A93" s="7" t="s">
         <v>766</v>
       </c>
@@ -12570,8 +13192,14 @@
         <v>244622</v>
       </c>
       <c r="G93" s="11"/>
-    </row>
-    <row r="94" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H93" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I93" s="52">
+        <v>244987</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A94" s="7" t="s">
         <v>766</v>
       </c>
@@ -12591,8 +13219,12 @@
         <v>244622</v>
       </c>
       <c r="G94" s="11"/>
-    </row>
-    <row r="95" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H94" s="52"/>
+      <c r="I94" s="52">
+        <v>245718</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A95" s="7" t="s">
         <v>766</v>
       </c>
@@ -12612,8 +13244,14 @@
         <v>244622</v>
       </c>
       <c r="G95" s="11"/>
-    </row>
-    <row r="96" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H95" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I95" s="52">
+        <v>244987</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A96" s="7" t="s">
         <v>766</v>
       </c>
@@ -12633,8 +13271,14 @@
         <v>244622</v>
       </c>
       <c r="G96" s="28"/>
-    </row>
-    <row r="97" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H96" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I96" s="52">
+        <v>244987</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A97" s="7" t="s">
         <v>766</v>
       </c>
@@ -12654,8 +13298,14 @@
         <v>244622</v>
       </c>
       <c r="G97" s="13"/>
-    </row>
-    <row r="98" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H97" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I97" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A98" s="7" t="s">
         <v>766</v>
       </c>
@@ -12675,8 +13325,14 @@
         <v>244622</v>
       </c>
       <c r="G98" s="13"/>
-    </row>
-    <row r="99" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H98" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I98" s="52">
+        <v>245535</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A99" s="7" t="s">
         <v>766</v>
       </c>
@@ -12696,8 +13352,14 @@
         <v>244622</v>
       </c>
       <c r="G99" s="14"/>
-    </row>
-    <row r="100" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H99" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I99" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A100" s="7" t="s">
         <v>766</v>
       </c>
@@ -12717,8 +13379,14 @@
         <v>244622</v>
       </c>
       <c r="G100" s="10"/>
-    </row>
-    <row r="101" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H100" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I100" s="52">
+        <v>245138</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A101" s="7" t="s">
         <v>766</v>
       </c>
@@ -12738,8 +13406,14 @@
         <v>244622</v>
       </c>
       <c r="G101" s="10"/>
-    </row>
-    <row r="102" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H101" s="52">
+        <v>245352</v>
+      </c>
+      <c r="I101" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A102" s="7" t="s">
         <v>766</v>
       </c>
@@ -12759,8 +13433,14 @@
         <v>244622</v>
       </c>
       <c r="G102" s="14"/>
-    </row>
-    <row r="103" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H102" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I102" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A103" s="7" t="s">
         <v>766</v>
       </c>
@@ -12780,8 +13460,14 @@
         <v>244622</v>
       </c>
       <c r="G103" s="23"/>
-    </row>
-    <row r="104" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H103" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I103" s="52">
+        <v>244730</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A104" s="7" t="s">
         <v>766</v>
       </c>
@@ -12801,8 +13487,14 @@
         <v>244622</v>
       </c>
       <c r="G104" s="23"/>
-    </row>
-    <row r="105" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H104" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I104" s="52">
+        <v>244730</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A105" s="48" t="s">
         <v>766</v>
       </c>
@@ -12824,8 +13516,14 @@
       <c r="G105" s="20" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H105" s="52">
+        <v>241465</v>
+      </c>
+      <c r="I105" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A106" s="7" t="s">
         <v>766</v>
       </c>
@@ -12845,8 +13543,14 @@
         <v>244622</v>
       </c>
       <c r="G106" s="13"/>
-    </row>
-    <row r="107" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H106" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I106" s="52">
+        <v>244865</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A107" s="7" t="s">
         <v>766</v>
       </c>
@@ -12866,8 +13570,14 @@
         <v>244622</v>
       </c>
       <c r="G107" s="13"/>
-    </row>
-    <row r="108" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H107" s="52">
+        <v>244987</v>
+      </c>
+      <c r="I107" s="52">
+        <v>244865</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A108" s="7" t="s">
         <v>766</v>
       </c>
@@ -12887,8 +13597,14 @@
         <v>244622</v>
       </c>
       <c r="G108" s="13"/>
-    </row>
-    <row r="109" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H108" s="52">
+        <v>244622</v>
+      </c>
+      <c r="I108" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A109" s="7" t="s">
         <v>767</v>
       </c>
@@ -12908,8 +13624,14 @@
         <v>244804</v>
       </c>
       <c r="G109" s="13"/>
-    </row>
-    <row r="110" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H109" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I109" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A110" s="7" t="s">
         <v>767</v>
       </c>
@@ -12929,8 +13651,14 @@
         <v>244804</v>
       </c>
       <c r="G110" s="13"/>
-    </row>
-    <row r="111" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H110" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I110" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A111" s="7" t="s">
         <v>767</v>
       </c>
@@ -12950,8 +13678,14 @@
         <v>244804</v>
       </c>
       <c r="G111" s="11"/>
-    </row>
-    <row r="112" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H111" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I111" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A112" s="7" t="s">
         <v>767</v>
       </c>
@@ -12971,8 +13705,14 @@
         <v>244804</v>
       </c>
       <c r="G112" s="11"/>
-    </row>
-    <row r="113" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H112" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I112" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A113" s="7" t="s">
         <v>767</v>
       </c>
@@ -12992,8 +13732,14 @@
         <v>244804</v>
       </c>
       <c r="G113" s="13"/>
-    </row>
-    <row r="114" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H113" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I113" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A114" s="7" t="s">
         <v>767</v>
       </c>
@@ -13013,8 +13759,14 @@
         <v>244804</v>
       </c>
       <c r="G114" s="23"/>
-    </row>
-    <row r="115" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H114" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I114" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A115" s="7" t="s">
         <v>767</v>
       </c>
@@ -13034,8 +13786,14 @@
         <v>244804</v>
       </c>
       <c r="G115" s="13"/>
-    </row>
-    <row r="116" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H115" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I115" s="52">
+        <v>246003</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A116" s="7" t="s">
         <v>767</v>
       </c>
@@ -13055,8 +13813,14 @@
         <v>244804</v>
       </c>
       <c r="G116" s="23"/>
-    </row>
-    <row r="117" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H116" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I116" s="52">
+        <v>245366</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A117" s="29" t="s">
         <v>767</v>
       </c>
@@ -13078,8 +13842,14 @@
       <c r="G117" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H117" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I117" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A118" s="15" t="s">
         <v>767</v>
       </c>
@@ -13099,8 +13869,14 @@
         <v>244804</v>
       </c>
       <c r="G118" s="28"/>
-    </row>
-    <row r="119" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H118" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I118" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A119" s="7" t="s">
         <v>767</v>
       </c>
@@ -13120,8 +13896,14 @@
         <v>244804</v>
       </c>
       <c r="G119" s="11"/>
-    </row>
-    <row r="120" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H119" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I119" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A120" s="7" t="s">
         <v>767</v>
       </c>
@@ -13141,8 +13923,14 @@
         <v>244804</v>
       </c>
       <c r="G120" s="10"/>
-    </row>
-    <row r="121" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H120" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I120" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A121" s="7" t="s">
         <v>767</v>
       </c>
@@ -13162,8 +13950,14 @@
         <v>244804</v>
       </c>
       <c r="G121" s="11"/>
-    </row>
-    <row r="122" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H121" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I121" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A122" s="7" t="s">
         <v>767</v>
       </c>
@@ -13183,8 +13977,14 @@
         <v>244804</v>
       </c>
       <c r="G122" s="28"/>
-    </row>
-    <row r="123" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H122" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I122" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A123" s="7" t="s">
         <v>767</v>
       </c>
@@ -13204,8 +14004,14 @@
         <v>244804</v>
       </c>
       <c r="G123" s="10"/>
-    </row>
-    <row r="124" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H123" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I123" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A124" s="7" t="s">
         <v>767</v>
       </c>
@@ -13225,8 +14031,14 @@
         <v>244804</v>
       </c>
       <c r="G124" s="23"/>
-    </row>
-    <row r="125" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H124" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I124" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A125" s="7" t="s">
         <v>767</v>
       </c>
@@ -13246,8 +14058,14 @@
         <v>244804</v>
       </c>
       <c r="G125" s="14"/>
-    </row>
-    <row r="126" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H125" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I125" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A126" s="7" t="s">
         <v>767</v>
       </c>
@@ -13267,8 +14085,14 @@
         <v>244804</v>
       </c>
       <c r="G126" s="11"/>
-    </row>
-    <row r="127" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H126" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I126" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A127" s="15" t="s">
         <v>767</v>
       </c>
@@ -13288,8 +14112,14 @@
         <v>244804</v>
       </c>
       <c r="G127" s="10"/>
-    </row>
-    <row r="128" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H127" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I127" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A128" s="15" t="s">
         <v>767</v>
       </c>
@@ -13309,8 +14139,14 @@
         <v>244804</v>
       </c>
       <c r="G128" s="11"/>
-    </row>
-    <row r="129" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H128" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I128" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A129" s="15" t="s">
         <v>767</v>
       </c>
@@ -13330,8 +14166,14 @@
         <v>244804</v>
       </c>
       <c r="G129" s="11"/>
-    </row>
-    <row r="130" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H129" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I129" s="52">
+        <v>245138</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A130" s="15" t="s">
         <v>767</v>
       </c>
@@ -13351,8 +14193,14 @@
         <v>244804</v>
       </c>
       <c r="G130" s="11"/>
-    </row>
-    <row r="131" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H130" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I130" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A131" s="15" t="s">
         <v>767</v>
       </c>
@@ -13372,8 +14220,14 @@
         <v>244804</v>
       </c>
       <c r="G131" s="11"/>
-    </row>
-    <row r="132" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H131" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I131" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A132" s="15" t="s">
         <v>767</v>
       </c>
@@ -13393,8 +14247,14 @@
         <v>244804</v>
       </c>
       <c r="G132" s="11"/>
-    </row>
-    <row r="133" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H132" s="52" t="s">
+        <v>789</v>
+      </c>
+      <c r="I132" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A133" s="15" t="s">
         <v>767</v>
       </c>
@@ -13414,8 +14274,14 @@
         <v>244804</v>
       </c>
       <c r="G133" s="11"/>
-    </row>
-    <row r="134" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H133" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I133" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A134" s="15" t="s">
         <v>767</v>
       </c>
@@ -13435,8 +14301,14 @@
         <v>244804</v>
       </c>
       <c r="G134" s="11"/>
-    </row>
-    <row r="135" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H134" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I134" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A135" s="15" t="s">
         <v>767</v>
       </c>
@@ -13456,8 +14328,14 @@
         <v>244804</v>
       </c>
       <c r="G135" s="11"/>
-    </row>
-    <row r="136" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H135" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I135" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A136" s="15" t="s">
         <v>767</v>
       </c>
@@ -13477,8 +14355,14 @@
         <v>244804</v>
       </c>
       <c r="G136" s="11"/>
-    </row>
-    <row r="137" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H136" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I136" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A137" s="7" t="s">
         <v>767</v>
       </c>
@@ -13498,8 +14382,14 @@
         <v>244804</v>
       </c>
       <c r="G137" s="23"/>
-    </row>
-    <row r="138" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H137" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I137" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A138" s="7" t="s">
         <v>767</v>
       </c>
@@ -13519,8 +14409,14 @@
         <v>244804</v>
       </c>
       <c r="G138" s="13"/>
-    </row>
-    <row r="139" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H138" s="52" t="s">
+        <v>789</v>
+      </c>
+      <c r="I138" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A139" s="7" t="s">
         <v>767</v>
       </c>
@@ -13540,8 +14436,14 @@
         <v>244622</v>
       </c>
       <c r="G139" s="11"/>
-    </row>
-    <row r="140" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H139" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I139" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A140" s="7" t="s">
         <v>767</v>
       </c>
@@ -13561,8 +14463,14 @@
         <v>244804</v>
       </c>
       <c r="G140" s="11"/>
-    </row>
-    <row r="141" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H140" s="52" t="s">
+        <v>789</v>
+      </c>
+      <c r="I140" s="52">
+        <v>245170</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A141" s="7" t="s">
         <v>767</v>
       </c>
@@ -13582,8 +14490,14 @@
         <v>244804</v>
       </c>
       <c r="G141" s="13"/>
-    </row>
-    <row r="142" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H141" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I141" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A142" s="7" t="s">
         <v>767</v>
       </c>
@@ -13603,8 +14517,14 @@
         <v>244804</v>
       </c>
       <c r="G142" s="11"/>
-    </row>
-    <row r="143" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H142" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I142" s="52">
+        <v>245029</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A143" s="7" t="s">
         <v>767</v>
       </c>
@@ -13624,8 +14544,14 @@
         <v>244804</v>
       </c>
       <c r="G143" s="11"/>
-    </row>
-    <row r="144" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H143" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I143" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A144" s="15" t="s">
         <v>767</v>
       </c>
@@ -13645,8 +14571,14 @@
         <v>244804</v>
       </c>
       <c r="G144" s="13"/>
-    </row>
-    <row r="145" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H144" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I144" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A145" s="15" t="s">
         <v>767</v>
       </c>
@@ -13666,8 +14598,14 @@
         <v>244804</v>
       </c>
       <c r="G145" s="10"/>
-    </row>
-    <row r="146" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H145" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I145" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A146" s="15" t="s">
         <v>767</v>
       </c>
@@ -13687,8 +14625,14 @@
         <v>244804</v>
       </c>
       <c r="G146" s="10"/>
-    </row>
-    <row r="147" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H146" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I146" s="52">
+        <v>244895</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A147" s="7" t="s">
         <v>767</v>
       </c>
@@ -13708,8 +14652,14 @@
         <v>244804</v>
       </c>
       <c r="G147" s="13"/>
-    </row>
-    <row r="148" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H147" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I147" s="52">
+        <v>244807</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A148" s="7" t="s">
         <v>767</v>
       </c>
@@ -13729,8 +14679,14 @@
         <v>244804</v>
       </c>
       <c r="G148" s="13"/>
-    </row>
-    <row r="149" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H148" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I148" s="52">
+        <v>244807</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A149" s="7" t="s">
         <v>767</v>
       </c>
@@ -13750,8 +14706,14 @@
         <v>244804</v>
       </c>
       <c r="G149" s="13"/>
-    </row>
-    <row r="150" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H149" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I149" s="52">
+        <v>244807</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A150" s="7" t="s">
         <v>767</v>
       </c>
@@ -13773,8 +14735,14 @@
       <c r="G150" s="13" t="s">
         <v>692</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H150" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I150" s="52">
+        <v>244807</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A151" s="7" t="s">
         <v>767</v>
       </c>
@@ -13794,8 +14762,14 @@
         <v>244804</v>
       </c>
       <c r="G151" s="13"/>
-    </row>
-    <row r="152" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H151" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I151" s="52">
+        <v>244807</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A152" s="7" t="s">
         <v>767</v>
       </c>
@@ -13815,8 +14789,14 @@
         <v>244804</v>
       </c>
       <c r="G152" s="11"/>
-    </row>
-    <row r="153" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H152" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I152" s="52">
+        <v>244916</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A153" s="7" t="s">
         <v>767</v>
       </c>
@@ -13836,8 +14816,14 @@
         <v>244804</v>
       </c>
       <c r="G153" s="10"/>
-    </row>
-    <row r="154" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H153" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I153" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A154" s="7" t="s">
         <v>767</v>
       </c>
@@ -13857,8 +14843,14 @@
         <v>244804</v>
       </c>
       <c r="G154" s="14"/>
-    </row>
-    <row r="155" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H154" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I154" s="52">
+        <v>245352</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A155" s="7" t="s">
         <v>767</v>
       </c>
@@ -13878,8 +14870,14 @@
         <v>244804</v>
       </c>
       <c r="G155" s="11"/>
-    </row>
-    <row r="156" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H155" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I155" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A156" s="7" t="s">
         <v>767</v>
       </c>
@@ -13899,8 +14897,14 @@
         <v>244804</v>
       </c>
       <c r="G156" s="11"/>
-    </row>
-    <row r="157" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H156" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I156" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A157" s="7" t="s">
         <v>767</v>
       </c>
@@ -13920,8 +14924,14 @@
         <v>244672</v>
       </c>
       <c r="G157" s="11"/>
-    </row>
-    <row r="158" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H157" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I157" s="52">
+        <v>244672</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A158" s="7" t="s">
         <v>767</v>
       </c>
@@ -13941,8 +14951,14 @@
         <v>244672</v>
       </c>
       <c r="G158" s="11"/>
-    </row>
-    <row r="159" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H158" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I158" s="52">
+        <v>244672</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A159" s="7" t="s">
         <v>767</v>
       </c>
@@ -13962,8 +14978,14 @@
         <v>244804</v>
       </c>
       <c r="G159" s="13"/>
-    </row>
-    <row r="160" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H159" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I159" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A160" s="7" t="s">
         <v>767</v>
       </c>
@@ -13983,8 +15005,14 @@
         <v>244804</v>
       </c>
       <c r="G160" s="13"/>
-    </row>
-    <row r="161" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H160" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I160" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A161" s="7" t="s">
         <v>767</v>
       </c>
@@ -14004,8 +15032,14 @@
         <v>244804</v>
       </c>
       <c r="G161" s="11"/>
-    </row>
-    <row r="162" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H161" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I161" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A162" s="7" t="s">
         <v>767</v>
       </c>
@@ -14025,8 +15059,14 @@
         <v>244804</v>
       </c>
       <c r="G162" s="11"/>
-    </row>
-    <row r="163" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H162" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I162" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A163" s="7" t="s">
         <v>767</v>
       </c>
@@ -14046,8 +15086,14 @@
         <v>244804</v>
       </c>
       <c r="G163" s="11"/>
-    </row>
-    <row r="164" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H163" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I163" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A164" s="7" t="s">
         <v>767</v>
       </c>
@@ -14067,8 +15113,14 @@
         <v>244646</v>
       </c>
       <c r="G164" s="13"/>
-    </row>
-    <row r="165" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H164" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I164" s="52">
+        <v>244646</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A165" s="7" t="s">
         <v>767</v>
       </c>
@@ -14088,8 +15140,14 @@
         <v>244646</v>
       </c>
       <c r="G165" s="13"/>
-    </row>
-    <row r="166" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H165" s="52">
+        <v>245535</v>
+      </c>
+      <c r="I165" s="52">
+        <v>244646</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A166" s="7" t="s">
         <v>767</v>
       </c>
@@ -14109,8 +15167,14 @@
         <v>244804</v>
       </c>
       <c r="G166" s="11"/>
-    </row>
-    <row r="167" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H166" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I166" s="52">
+        <v>244987</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A167" s="7" t="s">
         <v>767</v>
       </c>
@@ -14130,8 +15194,14 @@
         <v>244804</v>
       </c>
       <c r="G167" s="13"/>
-    </row>
-    <row r="168" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H167" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I167" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A168" s="24" t="s">
         <v>767</v>
       </c>
@@ -14153,8 +15223,14 @@
       <c r="G168" s="27" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="169" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H168" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I168" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A169" s="7" t="s">
         <v>767</v>
       </c>
@@ -14174,8 +15250,14 @@
         <v>244804</v>
       </c>
       <c r="G169" s="13"/>
-    </row>
-    <row r="170" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H169" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I169" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A170" s="7" t="s">
         <v>767</v>
       </c>
@@ -14195,8 +15277,14 @@
         <v>244804</v>
       </c>
       <c r="G170" s="11"/>
-    </row>
-    <row r="171" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H170" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I170" s="52">
+        <v>245043</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A171" s="7" t="s">
         <v>767</v>
       </c>
@@ -14216,8 +15304,14 @@
         <v>244804</v>
       </c>
       <c r="G171" s="10"/>
-    </row>
-    <row r="172" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H171" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I171" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A172" s="7" t="s">
         <v>767</v>
       </c>
@@ -14237,8 +15331,14 @@
         <v>244804</v>
       </c>
       <c r="G172" s="37"/>
-    </row>
-    <row r="173" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H172" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I172" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A173" s="7" t="s">
         <v>767</v>
       </c>
@@ -14258,8 +15358,14 @@
         <v>244804</v>
       </c>
       <c r="G173" s="23"/>
-    </row>
-    <row r="174" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H173" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I173" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A174" s="7" t="s">
         <v>767</v>
       </c>
@@ -14279,8 +15385,14 @@
         <v>244804</v>
       </c>
       <c r="G174" s="11"/>
-    </row>
-    <row r="175" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H174" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I174" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A175" s="7" t="s">
         <v>767</v>
       </c>
@@ -14300,8 +15412,14 @@
         <v>244804</v>
       </c>
       <c r="G175" s="10"/>
-    </row>
-    <row r="176" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H175" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I175" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A176" s="7" t="s">
         <v>767</v>
       </c>
@@ -14321,8 +15439,14 @@
         <v>244804</v>
       </c>
       <c r="G176" s="10"/>
-    </row>
-    <row r="177" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H176" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I176" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A177" s="7" t="s">
         <v>767</v>
       </c>
@@ -14342,8 +15466,14 @@
         <v>244804</v>
       </c>
       <c r="G177" s="10"/>
-    </row>
-    <row r="178" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H177" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I177" s="52">
+        <v>245169</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A178" s="7" t="s">
         <v>767</v>
       </c>
@@ -14363,8 +15493,14 @@
         <v>244804</v>
       </c>
       <c r="G178" s="11"/>
-    </row>
-    <row r="179" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H178" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I178" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A179" s="7" t="s">
         <v>767</v>
       </c>
@@ -14384,8 +15520,14 @@
         <v>244804</v>
       </c>
       <c r="G179" s="11"/>
-    </row>
-    <row r="180" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H179" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I179" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A180" s="7" t="s">
         <v>767</v>
       </c>
@@ -14405,8 +15547,14 @@
         <v>244804</v>
       </c>
       <c r="G180" s="10"/>
-    </row>
-    <row r="181" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H180" s="52">
+        <v>245169</v>
+      </c>
+      <c r="I180" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A181" s="15" t="s">
         <v>767</v>
       </c>
@@ -14426,8 +15574,14 @@
         <v>244804</v>
       </c>
       <c r="G181" s="10"/>
-    </row>
-    <row r="182" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H181" s="52">
+        <v>244804</v>
+      </c>
+      <c r="I181" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A182" s="15" t="s">
         <v>768</v>
       </c>
@@ -14447,8 +15601,14 @@
         <v>244895</v>
       </c>
       <c r="G182" s="13"/>
-    </row>
-    <row r="183" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H182" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I182" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A183" s="15" t="s">
         <v>768</v>
       </c>
@@ -14468,8 +15628,14 @@
         <v>244895</v>
       </c>
       <c r="G183" s="11"/>
-    </row>
-    <row r="184" spans="1:7" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H183" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I183" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="A184" s="15" t="s">
         <v>768</v>
       </c>
@@ -14489,8 +15655,14 @@
         <v>244895</v>
       </c>
       <c r="G184" s="13"/>
-    </row>
-    <row r="185" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H184" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I184" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A185" s="15" t="s">
         <v>768</v>
       </c>
@@ -14510,8 +15682,14 @@
         <v>244895</v>
       </c>
       <c r="G185" s="14"/>
-    </row>
-    <row r="186" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H185" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I185" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A186" s="15" t="s">
         <v>768</v>
       </c>
@@ -14531,8 +15709,14 @@
         <v>244895</v>
       </c>
       <c r="G186" s="38"/>
-    </row>
-    <row r="187" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H186" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I186" s="52">
+        <v>245305</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A187" s="15" t="s">
         <v>768</v>
       </c>
@@ -14552,8 +15736,14 @@
         <v>244895</v>
       </c>
       <c r="G187" s="11"/>
-    </row>
-    <row r="188" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H187" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I187" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A188" s="7" t="s">
         <v>768</v>
       </c>
@@ -14573,8 +15763,14 @@
         <v>244622</v>
       </c>
       <c r="G188" s="47"/>
-    </row>
-    <row r="189" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H188" s="52">
+        <v>244530</v>
+      </c>
+      <c r="I188" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A189" s="15" t="s">
         <v>768</v>
       </c>
@@ -14596,8 +15792,14 @@
       <c r="G189" s="11" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="190" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H189" s="52">
+        <v>243434</v>
+      </c>
+      <c r="I189" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A190" s="15" t="s">
         <v>768</v>
       </c>
@@ -14619,8 +15821,14 @@
       <c r="G190" s="11" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="191" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H190" s="52">
+        <v>243434</v>
+      </c>
+      <c r="I190" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A191" s="15" t="s">
         <v>768</v>
       </c>
@@ -14642,8 +15850,14 @@
       <c r="G191" s="11" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="192" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H191" s="52">
+        <v>243799</v>
+      </c>
+      <c r="I191" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A192" s="15" t="s">
         <v>768</v>
       </c>
@@ -14665,8 +15879,14 @@
       <c r="G192" s="11" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="193" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H192" s="52">
+        <v>243434</v>
+      </c>
+      <c r="I192" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A193" s="15" t="s">
         <v>768</v>
       </c>
@@ -14688,8 +15908,14 @@
       <c r="G193" s="11" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="194" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H193" s="52">
+        <v>243434</v>
+      </c>
+      <c r="I193" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A194" s="15" t="s">
         <v>768</v>
       </c>
@@ -14711,8 +15937,14 @@
       <c r="G194" s="11" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="195" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H194" s="52">
+        <v>243434</v>
+      </c>
+      <c r="I194" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A195" s="15" t="s">
         <v>768</v>
       </c>
@@ -14732,8 +15964,14 @@
         <v>244895</v>
       </c>
       <c r="G195" s="28"/>
-    </row>
-    <row r="196" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H195" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I195" s="52">
+        <v>245257</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A196" s="15" t="s">
         <v>768</v>
       </c>
@@ -14753,8 +15991,14 @@
         <v>244895</v>
       </c>
       <c r="G196" s="28"/>
-    </row>
-    <row r="197" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H196" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I196" s="52">
+        <v>245257</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A197" s="15" t="s">
         <v>768</v>
       </c>
@@ -14776,8 +16020,14 @@
       <c r="G197" s="13" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="198" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H197" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I197" s="52">
+        <v>245626</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A198" s="15" t="s">
         <v>768</v>
       </c>
@@ -14797,8 +16047,14 @@
         <v>244638</v>
       </c>
       <c r="G198" s="39"/>
-    </row>
-    <row r="199" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H198" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I198" s="52">
+        <v>244638</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A199" s="15" t="s">
         <v>768</v>
       </c>
@@ -14818,8 +16074,14 @@
         <v>244616</v>
       </c>
       <c r="G199" s="28"/>
-    </row>
-    <row r="200" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H199" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I199" s="52">
+        <v>244616</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A200" s="15" t="s">
         <v>768</v>
       </c>
@@ -14839,8 +16101,14 @@
         <v>244616</v>
       </c>
       <c r="G200" s="28"/>
-    </row>
-    <row r="201" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H200" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I200" s="52">
+        <v>244616</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A201" s="15" t="s">
         <v>768</v>
       </c>
@@ -14862,8 +16130,12 @@
       <c r="G201" s="28" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="202" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H201" s="52"/>
+      <c r="I201" s="52">
+        <v>244834</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A202" s="15" t="s">
         <v>768</v>
       </c>
@@ -14883,8 +16155,14 @@
         <v>244627</v>
       </c>
       <c r="G202" s="40"/>
-    </row>
-    <row r="203" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H202" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I202" s="52">
+        <v>244627</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A203" s="15" t="s">
         <v>768</v>
       </c>
@@ -14906,8 +16184,14 @@
       <c r="G203" s="28" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="204" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H203" s="52">
+        <v>242704</v>
+      </c>
+      <c r="I203" s="52">
+        <v>244834</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A204" s="15" t="s">
         <v>768</v>
       </c>
@@ -14927,8 +16211,14 @@
         <v>244895</v>
       </c>
       <c r="G204" s="10"/>
-    </row>
-    <row r="205" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H204" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I204" s="52">
+        <v>244834</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A205" s="15" t="s">
         <v>768</v>
       </c>
@@ -14942,16 +16232,20 @@
         <v>271</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F205" s="22">
-        <v>244592</v>
-      </c>
-      <c r="G205" s="28" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+        <v>244895</v>
+      </c>
+      <c r="G205" s="28"/>
+      <c r="H205" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I205" s="52">
+        <v>245718</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A206" s="41" t="s">
         <v>768</v>
       </c>
@@ -14973,8 +16267,14 @@
       <c r="G206" s="33" t="s">
         <v>744</v>
       </c>
-    </row>
-    <row r="207" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H206" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I206" s="52">
+        <v>244743</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A207" s="15" t="s">
         <v>768</v>
       </c>
@@ -14994,8 +16294,14 @@
         <v>244895</v>
       </c>
       <c r="G207" s="28"/>
-    </row>
-    <row r="208" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H207" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I207" s="52">
+        <v>245865</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A208" s="15" t="s">
         <v>768</v>
       </c>
@@ -15015,8 +16321,14 @@
         <v>244895</v>
       </c>
       <c r="G208" s="40"/>
-    </row>
-    <row r="209" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H208" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I208" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A209" s="15" t="s">
         <v>768</v>
       </c>
@@ -15038,8 +16350,14 @@
       <c r="G209" s="28" t="s">
         <v>773</v>
       </c>
-    </row>
-    <row r="210" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H209" s="52">
+        <v>243799</v>
+      </c>
+      <c r="I209" s="52">
+        <v>244652</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A210" s="15" t="s">
         <v>768</v>
       </c>
@@ -15059,8 +16377,14 @@
         <v>244895</v>
       </c>
       <c r="G210" s="11"/>
-    </row>
-    <row r="211" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H210" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I210" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A211" s="41" t="s">
         <v>768</v>
       </c>
@@ -15082,8 +16406,14 @@
       <c r="G211" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="212" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H211" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I211" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A212" s="41" t="s">
         <v>768</v>
       </c>
@@ -15105,8 +16435,14 @@
       <c r="G212" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="213" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H212" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I212" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A213" s="41" t="s">
         <v>768</v>
       </c>
@@ -15128,8 +16464,14 @@
       <c r="G213" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="214" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H213" s="52">
+        <v>243069</v>
+      </c>
+      <c r="I213" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A214" s="15" t="s">
         <v>768</v>
       </c>
@@ -15149,8 +16491,14 @@
         <v>244895</v>
       </c>
       <c r="G214" s="11"/>
-    </row>
-    <row r="215" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H214" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I214" s="52">
+        <v>244905</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A215" s="15" t="s">
         <v>768</v>
       </c>
@@ -15170,8 +16518,14 @@
         <v>244895</v>
       </c>
       <c r="G215" s="11"/>
-    </row>
-    <row r="216" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H215" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I215" s="52">
+        <v>245574</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A216" s="15" t="s">
         <v>768</v>
       </c>
@@ -15191,8 +16545,14 @@
         <v>244652</v>
       </c>
       <c r="G216" s="13"/>
-    </row>
-    <row r="217" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H216" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I216" s="52">
+        <v>245626</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A217" s="15" t="s">
         <v>768</v>
       </c>
@@ -15212,8 +16572,14 @@
         <v>244895</v>
       </c>
       <c r="G217" s="11"/>
-    </row>
-    <row r="218" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H217" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I217" s="52">
+        <v>245626</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A218" s="15" t="s">
         <v>768</v>
       </c>
@@ -15233,8 +16599,14 @@
         <v>244895</v>
       </c>
       <c r="G218" s="10"/>
-    </row>
-    <row r="219" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H218" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I218" s="52">
+        <v>245769</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A219" s="15" t="s">
         <v>768</v>
       </c>
@@ -15254,8 +16626,14 @@
         <v>244895</v>
       </c>
       <c r="G219" s="38"/>
-    </row>
-    <row r="220" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H219" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I219" s="52">
+        <v>245416</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A220" s="15" t="s">
         <v>768</v>
       </c>
@@ -15275,8 +16653,14 @@
         <v>244895</v>
       </c>
       <c r="G220" s="11"/>
-    </row>
-    <row r="221" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H220" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I220" s="52">
+        <v>245292</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A221" s="15" t="s">
         <v>768</v>
       </c>
@@ -15296,8 +16680,14 @@
         <v>244612</v>
       </c>
       <c r="G221" s="11"/>
-    </row>
-    <row r="222" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H221" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I221" s="52">
+        <v>244612</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A222" s="15" t="s">
         <v>768</v>
       </c>
@@ -15317,8 +16707,14 @@
         <v>244612</v>
       </c>
       <c r="G222" s="11"/>
-    </row>
-    <row r="223" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H222" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I222" s="52">
+        <v>244612</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A223" s="15" t="s">
         <v>768</v>
       </c>
@@ -15338,8 +16734,14 @@
         <v>244895</v>
       </c>
       <c r="G223" s="28"/>
-    </row>
-    <row r="224" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H223" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I223" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A224" s="15" t="s">
         <v>768</v>
       </c>
@@ -15359,8 +16761,14 @@
         <v>244612</v>
       </c>
       <c r="G224" s="11"/>
-    </row>
-    <row r="225" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H224" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I224" s="52">
+        <v>244612</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A225" s="15" t="s">
         <v>768</v>
       </c>
@@ -15380,8 +16788,14 @@
         <v>244895</v>
       </c>
       <c r="G225" s="13"/>
-    </row>
-    <row r="226" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H225" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I225" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A226" s="15" t="s">
         <v>768</v>
       </c>
@@ -15401,8 +16815,14 @@
         <v>244895</v>
       </c>
       <c r="G226" s="39"/>
-    </row>
-    <row r="227" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H226" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I226" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A227" s="15" t="s">
         <v>768</v>
       </c>
@@ -15422,8 +16842,14 @@
         <v>244895</v>
       </c>
       <c r="G227" s="11"/>
-    </row>
-    <row r="228" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H227" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I227" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A228" s="15" t="s">
         <v>768</v>
       </c>
@@ -15443,8 +16869,14 @@
         <v>244590</v>
       </c>
       <c r="G228" s="11"/>
-    </row>
-    <row r="229" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H228" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I228" s="52">
+        <v>244590</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A229" s="15" t="s">
         <v>768</v>
       </c>
@@ -15464,8 +16896,14 @@
         <v>244590</v>
       </c>
       <c r="G229" s="39"/>
-    </row>
-    <row r="230" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H229" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I229" s="52">
+        <v>244590</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A230" s="15" t="s">
         <v>768</v>
       </c>
@@ -15485,8 +16923,14 @@
         <v>244895</v>
       </c>
       <c r="G230" s="39"/>
-    </row>
-    <row r="231" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H230" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I230" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A231" s="15" t="s">
         <v>768</v>
       </c>
@@ -15508,8 +16952,14 @@
       <c r="G231" s="42" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="232" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H231" s="52">
+        <v>244530</v>
+      </c>
+      <c r="I231" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A232" s="41" t="s">
         <v>768</v>
       </c>
@@ -15531,8 +16981,14 @@
       <c r="G232" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="233" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H232" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I232" s="52">
+        <v>245290</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A233" s="15" t="s">
         <v>768</v>
       </c>
@@ -15552,8 +17008,14 @@
         <v>244895</v>
       </c>
       <c r="G233" s="11"/>
-    </row>
-    <row r="234" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H233" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I233" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A234" s="15" t="s">
         <v>768</v>
       </c>
@@ -15573,8 +17035,14 @@
         <v>244895</v>
       </c>
       <c r="G234" s="11"/>
-    </row>
-    <row r="235" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H234" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I234" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A235" s="15" t="s">
         <v>768</v>
       </c>
@@ -15594,8 +17062,14 @@
         <v>244895</v>
       </c>
       <c r="G235" s="39"/>
-    </row>
-    <row r="236" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H235" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I235" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A236" s="41" t="s">
         <v>768</v>
       </c>
@@ -15617,8 +17091,14 @@
       <c r="G236" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="237" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H236" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I236" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A237" s="15" t="s">
         <v>768</v>
       </c>
@@ -15638,8 +17118,14 @@
         <v>244895</v>
       </c>
       <c r="G237" s="39"/>
-    </row>
-    <row r="238" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H237" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I237" s="52">
+        <v>245260</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A238" s="15" t="s">
         <v>768</v>
       </c>
@@ -15659,8 +17145,14 @@
         <v>244637</v>
       </c>
       <c r="G238" s="11"/>
-    </row>
-    <row r="239" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H238" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I238" s="52">
+        <v>244637</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A239" s="15" t="s">
         <v>768</v>
       </c>
@@ -15680,8 +17172,14 @@
         <v>244637</v>
       </c>
       <c r="G239" s="39"/>
-    </row>
-    <row r="240" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H239" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I239" s="52">
+        <v>244637</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A240" s="15" t="s">
         <v>768</v>
       </c>
@@ -15701,8 +17199,14 @@
         <v>244622</v>
       </c>
       <c r="G240" s="11"/>
-    </row>
-    <row r="241" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H240" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I240" s="52">
+        <v>244622</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A241" s="15" t="s">
         <v>768</v>
       </c>
@@ -15722,8 +17226,14 @@
         <v>244895</v>
       </c>
       <c r="G241" s="11"/>
-    </row>
-    <row r="242" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H241" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I241" s="52">
+        <v>245101</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A242" s="15" t="s">
         <v>768</v>
       </c>
@@ -15743,8 +17253,14 @@
         <v>244895</v>
       </c>
       <c r="G242" s="10"/>
-    </row>
-    <row r="243" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H242" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I242" s="52">
+        <v>245101</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A243" s="41" t="s">
         <v>768</v>
       </c>
@@ -15766,8 +17282,14 @@
       <c r="G243" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="244" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H243" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I243" s="52">
+        <v>245626</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A244" s="41" t="s">
         <v>768</v>
       </c>
@@ -15789,8 +17311,14 @@
       <c r="G244" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="245" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H244" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I244" s="52">
+        <v>245626</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A245" s="15" t="s">
         <v>768</v>
       </c>
@@ -15810,8 +17338,14 @@
         <v>244895</v>
       </c>
       <c r="G245" s="11"/>
-    </row>
-    <row r="246" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H245" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I245" s="52">
+        <v>245385</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A246" s="15" t="s">
         <v>768</v>
       </c>
@@ -15831,8 +17365,14 @@
         <v>244895</v>
       </c>
       <c r="G246" s="28"/>
-    </row>
-    <row r="247" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H246" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I246" s="52">
+        <v>244853</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A247" s="15" t="s">
         <v>768</v>
       </c>
@@ -15852,8 +17392,14 @@
         <v>244895</v>
       </c>
       <c r="G247" s="40"/>
-    </row>
-    <row r="248" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H247" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I247" s="52">
+        <v>245260</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A248" s="41" t="s">
         <v>768</v>
       </c>
@@ -15875,8 +17421,14 @@
       <c r="G248" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="249" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H248" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I248" s="52">
+        <v>245626</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A249" s="15" t="s">
         <v>768</v>
       </c>
@@ -15896,8 +17448,14 @@
         <v>244895</v>
       </c>
       <c r="G249" s="11"/>
-    </row>
-    <row r="250" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H249" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I249" s="52">
+        <v>244939</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A250" s="41" t="s">
         <v>768</v>
       </c>
@@ -15919,8 +17477,14 @@
       <c r="G250" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="251" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H250" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I250" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A251" s="15" t="s">
         <v>768</v>
       </c>
@@ -15940,8 +17504,14 @@
         <v>244895</v>
       </c>
       <c r="G251" s="11"/>
-    </row>
-    <row r="252" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H251" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I251" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A252" s="15" t="s">
         <v>768</v>
       </c>
@@ -15961,8 +17531,14 @@
         <v>244895</v>
       </c>
       <c r="G252" s="14"/>
-    </row>
-    <row r="253" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H252" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I252" s="52">
+        <v>244895</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A253" s="15" t="s">
         <v>768</v>
       </c>
@@ -15982,8 +17558,14 @@
         <v>244895</v>
       </c>
       <c r="G253" s="14"/>
-    </row>
-    <row r="254" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H253" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I253" s="52">
+        <v>244895</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A254" s="15" t="s">
         <v>768</v>
       </c>
@@ -16003,8 +17585,14 @@
         <v>244895</v>
       </c>
       <c r="G254" s="14"/>
-    </row>
-    <row r="255" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H254" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I254" s="52">
+        <v>244895</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A255" s="15" t="s">
         <v>768</v>
       </c>
@@ -16024,8 +17612,14 @@
         <v>244895</v>
       </c>
       <c r="G255" s="14"/>
-    </row>
-    <row r="256" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H255" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I255" s="52">
+        <v>244895</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A256" s="15" t="s">
         <v>768</v>
       </c>
@@ -16045,8 +17639,14 @@
         <v>244895</v>
       </c>
       <c r="G256" s="14"/>
-    </row>
-    <row r="257" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H256" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I256" s="52">
+        <v>244895</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A257" s="15" t="s">
         <v>768</v>
       </c>
@@ -16066,8 +17666,14 @@
         <v>244895</v>
       </c>
       <c r="G257" s="13"/>
-    </row>
-    <row r="258" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H257" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I257" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A258" s="15" t="s">
         <v>768</v>
       </c>
@@ -16087,8 +17693,14 @@
         <v>244895</v>
       </c>
       <c r="G258" s="14"/>
-    </row>
-    <row r="259" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H258" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I258" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A259" s="15" t="s">
         <v>768</v>
       </c>
@@ -16108,8 +17720,14 @@
         <v>244895</v>
       </c>
       <c r="G259" s="14"/>
-    </row>
-    <row r="260" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H259" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I259" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A260" s="15" t="s">
         <v>768</v>
       </c>
@@ -16129,8 +17747,14 @@
         <v>244895</v>
       </c>
       <c r="G260" s="10"/>
-    </row>
-    <row r="261" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H260" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I260" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A261" s="15" t="s">
         <v>768</v>
       </c>
@@ -16150,8 +17774,14 @@
         <v>244804</v>
       </c>
       <c r="G261" s="10"/>
-    </row>
-    <row r="262" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H261" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I261" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A262" s="15" t="s">
         <v>768</v>
       </c>
@@ -16171,8 +17801,14 @@
         <v>244895</v>
       </c>
       <c r="G262" s="10"/>
-    </row>
-    <row r="263" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H262" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I262" s="52">
+        <v>244804</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A263" s="15" t="s">
         <v>768</v>
       </c>
@@ -16192,8 +17828,14 @@
         <v>244631</v>
       </c>
       <c r="G263" s="14"/>
-    </row>
-    <row r="264" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H263" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I263" s="52">
+        <v>244631</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A264" s="15" t="s">
         <v>768</v>
       </c>
@@ -16213,8 +17855,14 @@
         <v>244895</v>
       </c>
       <c r="G264" s="14"/>
-    </row>
-    <row r="265" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H264" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I264" s="52">
+        <v>245324</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A265" s="15" t="s">
         <v>768</v>
       </c>
@@ -16234,8 +17882,14 @@
         <v>244895</v>
       </c>
       <c r="G265" s="14"/>
-    </row>
-    <row r="266" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H265" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I265" s="52">
+        <v>245324</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A266" s="15" t="s">
         <v>768</v>
       </c>
@@ -16255,8 +17909,14 @@
         <v>244895</v>
       </c>
       <c r="G266" s="14"/>
-    </row>
-    <row r="267" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H266" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I266" s="52">
+        <v>245810</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A267" s="7" t="s">
         <v>768</v>
       </c>
@@ -16276,8 +17936,14 @@
         <v>244895</v>
       </c>
       <c r="G267" s="11"/>
-    </row>
-    <row r="268" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H267" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I267" s="52">
+        <v>245147</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A268" s="15" t="s">
         <v>768</v>
       </c>
@@ -16297,8 +17963,14 @@
         <v>244895</v>
       </c>
       <c r="G268" s="43"/>
-    </row>
-    <row r="269" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H268" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I268" s="52">
+        <v>245079</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A269" s="15" t="s">
         <v>768</v>
       </c>
@@ -16318,8 +17990,14 @@
         <v>244895</v>
       </c>
       <c r="G269" s="43"/>
-    </row>
-    <row r="270" spans="1:7" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H269" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I269" s="52">
+        <v>245079</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="21.75" customHeight="1" thickBot="1">
       <c r="A270" s="15" t="s">
         <v>768</v>
       </c>
@@ -16339,8 +18017,14 @@
         <v>244895</v>
       </c>
       <c r="G270" s="39"/>
-    </row>
-    <row r="271" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H270" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I270" s="52">
+        <v>245444</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A271" s="15" t="s">
         <v>768</v>
       </c>
@@ -16360,8 +18044,14 @@
         <v>244895</v>
       </c>
       <c r="G271" s="28"/>
-    </row>
-    <row r="272" spans="1:7" ht="20.25" customHeight="1" thickBot="1">
+      <c r="H271" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I271" s="52">
+        <v>244793</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
       <c r="A272" s="15" t="s">
         <v>768</v>
       </c>
@@ -16381,8 +18071,14 @@
         <v>244713</v>
       </c>
       <c r="G272" s="11"/>
-    </row>
-    <row r="273" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H272" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I272" s="52">
+        <v>244713</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A273" s="15" t="s">
         <v>768</v>
       </c>
@@ -16402,8 +18098,14 @@
         <v>244895</v>
       </c>
       <c r="G273" s="11"/>
-    </row>
-    <row r="274" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H273" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I273" s="52">
+        <v>245443</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A274" s="15" t="s">
         <v>768</v>
       </c>
@@ -16423,8 +18125,14 @@
         <v>244895</v>
       </c>
       <c r="G274" s="11"/>
-    </row>
-    <row r="275" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H274" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I274" s="52">
+        <v>245443</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A275" s="15" t="s">
         <v>768</v>
       </c>
@@ -16444,8 +18152,14 @@
         <v>244895</v>
       </c>
       <c r="G275" s="11"/>
-    </row>
-    <row r="276" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H275" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I275" s="52">
+        <v>245443</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A276" s="41" t="s">
         <v>768</v>
       </c>
@@ -16467,8 +18181,14 @@
       <c r="G276" s="33" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="277" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H276" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I276" s="52">
+        <v>245231</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A277" s="15" t="s">
         <v>768</v>
       </c>
@@ -16488,8 +18208,14 @@
         <v>244895</v>
       </c>
       <c r="G277" s="44"/>
-    </row>
-    <row r="278" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H277" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I277" s="52" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A278" s="15" t="s">
         <v>768</v>
       </c>
@@ -16509,8 +18235,14 @@
         <v>244864</v>
       </c>
       <c r="G278" s="11"/>
-    </row>
-    <row r="279" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H278" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I278" s="52">
+        <v>244864</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A279" s="15" t="s">
         <v>768</v>
       </c>
@@ -16530,8 +18262,14 @@
         <v>244895</v>
       </c>
       <c r="G279" s="11"/>
-    </row>
-    <row r="280" spans="1:7" ht="21" customHeight="1" thickBot="1">
+      <c r="H279" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I279" s="52">
+        <v>244864</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" ht="21" customHeight="1" thickBot="1">
       <c r="A280" s="15" t="s">
         <v>768</v>
       </c>
@@ -16551,8 +18289,14 @@
         <v>244895</v>
       </c>
       <c r="G280" s="39"/>
-    </row>
-    <row r="281" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H280" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I280" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="17.5" thickBot="1">
       <c r="A281" s="15" t="s">
         <v>768</v>
       </c>
@@ -16572,8 +18316,14 @@
         <v>244895</v>
       </c>
       <c r="G281" s="45"/>
-    </row>
-    <row r="282" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H281" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I281" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" ht="17.5" thickBot="1">
       <c r="A282" s="15" t="s">
         <v>768</v>
       </c>
@@ -16593,8 +18343,14 @@
         <v>244895</v>
       </c>
       <c r="G282" s="45"/>
-    </row>
-    <row r="283" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H282" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I282" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" ht="17.5" thickBot="1">
       <c r="A283" s="15" t="s">
         <v>768</v>
       </c>
@@ -16614,8 +18370,14 @@
         <v>244895</v>
       </c>
       <c r="G283" s="45"/>
-    </row>
-    <row r="284" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H283" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I283" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" ht="17.5" thickBot="1">
       <c r="A284" s="15" t="s">
         <v>768</v>
       </c>
@@ -16635,8 +18397,14 @@
         <v>244895</v>
       </c>
       <c r="G284" s="45"/>
-    </row>
-    <row r="285" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H284" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I284" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" ht="17.5" thickBot="1">
       <c r="A285" s="15" t="s">
         <v>768</v>
       </c>
@@ -16656,8 +18424,14 @@
         <v>244895</v>
       </c>
       <c r="G285" s="11"/>
-    </row>
-    <row r="286" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H285" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I285" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" ht="17.5" thickBot="1">
       <c r="A286" s="15" t="s">
         <v>768</v>
       </c>
@@ -16677,8 +18451,14 @@
         <v>244895</v>
       </c>
       <c r="G286" s="11"/>
-    </row>
-    <row r="287" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H286" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I286" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" ht="17.5" thickBot="1">
       <c r="A287" s="15" t="s">
         <v>768</v>
       </c>
@@ -16698,8 +18478,14 @@
         <v>244895</v>
       </c>
       <c r="G287" s="11"/>
-    </row>
-    <row r="288" spans="1:7" ht="17.5" thickBot="1">
+      <c r="H287" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I287" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" ht="17.5" thickBot="1">
       <c r="A288" s="15" t="s">
         <v>768</v>
       </c>
@@ -16719,8 +18505,14 @@
         <v>244895</v>
       </c>
       <c r="G288" s="13"/>
-    </row>
-    <row r="289" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+      <c r="H288" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I288" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9 16363:16363" ht="17.5" thickBot="1">
       <c r="A289" s="15" t="s">
         <v>768</v>
       </c>
@@ -16740,8 +18532,14 @@
         <v>244895</v>
       </c>
       <c r="G289" s="13"/>
-    </row>
-    <row r="290" spans="1:7 16363:16363" ht="21.75" customHeight="1" thickBot="1">
+      <c r="H289" s="52">
+        <v>244895</v>
+      </c>
+      <c r="I289" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9 16363:16363" ht="21.75" customHeight="1" thickBot="1">
       <c r="A290" s="15" t="s">
         <v>768</v>
       </c>
@@ -16761,8 +18559,14 @@
         <v>244895</v>
       </c>
       <c r="G290" s="11"/>
-    </row>
-    <row r="291" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+      <c r="H290" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I290" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9 16363:16363" ht="17.5" thickBot="1">
       <c r="A291" s="15" t="s">
         <v>768</v>
       </c>
@@ -16782,9 +18586,15 @@
         <v>244895</v>
       </c>
       <c r="G291" s="11"/>
+      <c r="H291" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I291" s="52" t="s">
+        <v>787</v>
+      </c>
       <c r="XEI291" s="46"/>
     </row>
-    <row r="292" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+    <row r="292" spans="1:9 16363:16363" ht="17.5" thickBot="1">
       <c r="A292" s="15" t="s">
         <v>768</v>
       </c>
@@ -16804,9 +18614,15 @@
         <v>244648</v>
       </c>
       <c r="G292" s="12"/>
+      <c r="H292" s="52">
+        <v>245626</v>
+      </c>
+      <c r="I292" s="52">
+        <v>244648</v>
+      </c>
       <c r="XEI292" s="46"/>
     </row>
-    <row r="293" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+    <row r="293" spans="1:9 16363:16363" ht="17.5" thickBot="1">
       <c r="A293" s="15" t="s">
         <v>768</v>
       </c>
@@ -16826,9 +18642,15 @@
         <v>244895</v>
       </c>
       <c r="G293" s="11"/>
+      <c r="H293" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I293" s="52" t="s">
+        <v>786</v>
+      </c>
       <c r="XEI293" s="46"/>
     </row>
-    <row r="294" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+    <row r="294" spans="1:9 16363:16363" ht="17.5" thickBot="1">
       <c r="A294" s="15" t="s">
         <v>768</v>
       </c>
@@ -16848,8 +18670,14 @@
         <v>244895</v>
       </c>
       <c r="G294" s="11"/>
-    </row>
-    <row r="295" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+      <c r="H294" s="52">
+        <v>245260</v>
+      </c>
+      <c r="I294" s="52" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9 16363:16363" ht="17.5" thickBot="1">
       <c r="A295" s="15" t="s">
         <v>768</v>
       </c>
@@ -16869,8 +18697,12 @@
         <v>244714</v>
       </c>
       <c r="G295" s="11"/>
-    </row>
-    <row r="296" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+      <c r="H295" s="52"/>
+      <c r="I295" s="52" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9 16363:16363" ht="17.5" thickBot="1">
       <c r="A296" s="15" t="s">
         <v>768</v>
       </c>
@@ -16890,9 +18722,11 @@
         <v>244653</v>
       </c>
       <c r="G296" s="11"/>
+      <c r="H296" s="52"/>
+      <c r="I296" s="52"/>
       <c r="XEI296" s="46"/>
     </row>
-    <row r="297" spans="1:7 16363:16363" ht="17.5" thickBot="1">
+    <row r="297" spans="1:9 16363:16363" ht="17.5" thickBot="1">
       <c r="A297" s="15" t="s">
         <v>768</v>
       </c>
@@ -16912,159 +18746,161 @@
         <v>244653</v>
       </c>
       <c r="G297" s="11"/>
+      <c r="H297" s="52"/>
+      <c r="I297" s="52"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G297" xr:uid="{8617D22F-2FD7-43CE-8F40-2261BDA11212}"/>
+  <autoFilter ref="A1:I297" xr:uid="{2ADD9999-E05E-4DFC-9ACA-F5F92389CAD8}"/>
   <sortState ref="A2:G296">
     <sortCondition ref="A2:A296"/>
   </sortState>
-  <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G293 F261:G275 F277:F293 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204:F205 F4:F5 F51 F27:F28 F56 F65:G100 G203:G211 A3:E293 F102:G202 E295:E297 A295:D296 F295:G296">
-    <cfRule type="expression" dxfId="29" priority="346">
+  <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G293 F261:G275 F277:F293 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204:F205 F4:F5 F51 F27:F28 F56 F65:G100 G203:G211 F102:G202 E295:E297 A295:D296 F295:G296 A3:E293">
+    <cfRule type="expression" dxfId="35" priority="346">
       <formula>$F2="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G101">
-    <cfRule type="expression" dxfId="28" priority="257">
+    <cfRule type="expression" dxfId="34" priority="257">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="expression" dxfId="27" priority="232">
+    <cfRule type="expression" dxfId="33" priority="232">
       <formula>$F4="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="26" priority="231">
+    <cfRule type="expression" dxfId="32" priority="231">
       <formula>$F5="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="expression" dxfId="25" priority="230">
+    <cfRule type="expression" dxfId="31" priority="230">
       <formula>$F27="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41">
-    <cfRule type="expression" dxfId="24" priority="227">
+    <cfRule type="expression" dxfId="30" priority="227">
       <formula>$F41="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51">
-    <cfRule type="expression" dxfId="23" priority="225">
+    <cfRule type="expression" dxfId="29" priority="225">
       <formula>$F51="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64">
-    <cfRule type="expression" dxfId="22" priority="224">
+    <cfRule type="expression" dxfId="28" priority="224">
       <formula>$F64="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="21" priority="223">
+    <cfRule type="expression" dxfId="27" priority="223">
       <formula>$F56="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="expression" dxfId="20" priority="209">
+    <cfRule type="expression" dxfId="26" priority="209">
       <formula>$F28="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59">
-    <cfRule type="expression" dxfId="19" priority="203">
+    <cfRule type="expression" dxfId="25" priority="203">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="expression" dxfId="18" priority="185">
+    <cfRule type="expression" dxfId="24" priority="185">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A297">
-    <cfRule type="expression" dxfId="17" priority="183">
+    <cfRule type="expression" dxfId="23" priority="183">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F206">
-    <cfRule type="expression" dxfId="16" priority="178">
+    <cfRule type="expression" dxfId="22" priority="178">
       <formula>$F206="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F203">
-    <cfRule type="expression" dxfId="15" priority="173">
+    <cfRule type="expression" dxfId="21" priority="173">
       <formula>$F203="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="expression" dxfId="14" priority="152">
+    <cfRule type="expression" dxfId="20" priority="152">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G212">
-    <cfRule type="expression" dxfId="13" priority="151">
+    <cfRule type="expression" dxfId="19" priority="151">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B297">
-    <cfRule type="expression" dxfId="12" priority="145">
+    <cfRule type="expression" dxfId="18" priority="145">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F297">
-    <cfRule type="expression" dxfId="11" priority="143">
+    <cfRule type="expression" dxfId="17" priority="143">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F211">
-    <cfRule type="expression" dxfId="10" priority="142">
+    <cfRule type="expression" dxfId="16" priority="142">
       <formula>$F211="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
-    <cfRule type="expression" dxfId="9" priority="119">
+    <cfRule type="expression" dxfId="15" priority="119">
       <formula>$F236="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F243">
-    <cfRule type="expression" dxfId="8" priority="118">
+    <cfRule type="expression" dxfId="14" priority="118">
       <formula>$F243="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250">
-    <cfRule type="expression" dxfId="7" priority="115">
+    <cfRule type="expression" dxfId="13" priority="115">
       <formula>$F250="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F276">
-    <cfRule type="expression" dxfId="6" priority="114">
+    <cfRule type="expression" dxfId="12" priority="114">
       <formula>$F276="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F232">
-    <cfRule type="expression" dxfId="5" priority="45">
+    <cfRule type="expression" dxfId="11" priority="45">
       <formula>$F232="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F248">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$F248="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F212">
-    <cfRule type="expression" dxfId="3" priority="5">
+    <cfRule type="expression" dxfId="9" priority="5">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F213">
-    <cfRule type="expression" dxfId="2" priority="4">
+    <cfRule type="expression" dxfId="8" priority="4">
       <formula>$F213="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F244">
-    <cfRule type="expression" dxfId="1" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$F244="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A294:G294">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>$F294="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/SmartLicense.xlsx
+++ b/SmartLicense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{367C0ECF-11A0-4308-A2AA-797DF403F323}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01A7243-39D0-416A-ACFF-ABD1879DA886}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1609" uniqueCount="791">
   <si>
     <t>ชื่อโรงงาน</t>
   </si>
@@ -2410,7 +2410,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="[$-101041E]d\ mmm\ yy;@"/>
     <numFmt numFmtId="166" formatCode="dd/ดดด/yy"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="19">
     <font>
@@ -2796,7 +2796,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="3" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2826,1704 +2826,7 @@
     <cellStyle name="Percent 2" xfId="19" xr:uid="{52C74F60-A476-4152-873D-B4183CDD4F15}"/>
     <cellStyle name="Style 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
-  <dxfs count="335">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="44">
     <dxf>
       <fill>
         <patternFill>
@@ -4586,210 +2889,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4806,207 +2913,21 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -12894,7 +10815,7 @@
       </c>
       <c r="K1" s="54">
         <f ca="1" xml:space="preserve"> EDATE(TODAY(),543*12)</f>
-        <v>244587</v>
+        <v>244589</v>
       </c>
       <c r="M1" s="55"/>
       <c r="N1" s="55"/>
@@ -12927,11 +10848,11 @@
       </c>
       <c r="J2" s="56">
         <f ca="1">IFERROR((H2-$K$1),0)</f>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K2" s="56">
         <f ca="1">IF(I2="ยังไม่ได้ทำ BG",-9999,IF(OR(I2="ค้ำเงินสด",I2="ค้ำประกันรายได้",I2="วงเงินรวม SCG"),999,IFERROR((I2-$K$1),0)))</f>
-        <v>643</v>
+        <v>641</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -12962,7 +10883,7 @@
       </c>
       <c r="J3" s="56">
         <f t="shared" ref="J3:J66" ca="1" si="0">IFERROR((H3-$K$1),0)</f>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K3" s="56">
         <f t="shared" ref="K3:K66" si="1">IF(I3="ยังไม่ได้ทำ BG",-9999,IF(OR(I3="ค้ำเงินสด",I3="ค้ำประกันรายได้",I3="วงเงินรวม SCG"),999,IFERROR((I3-$K$1),0)))</f>
@@ -12997,7 +10918,7 @@
       </c>
       <c r="J4" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K4" s="56">
         <f t="shared" si="1"/>
@@ -13032,7 +10953,7 @@
       </c>
       <c r="J5" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K5" s="56">
         <f t="shared" si="1"/>
@@ -13067,11 +10988,11 @@
       </c>
       <c r="J6" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K6" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13102,11 +11023,11 @@
       </c>
       <c r="J7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K7" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13137,11 +11058,11 @@
       </c>
       <c r="J8" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K8" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13172,11 +11093,11 @@
       </c>
       <c r="J9" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K9" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13207,11 +11128,11 @@
       </c>
       <c r="J10" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K10" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13242,11 +11163,11 @@
       </c>
       <c r="J11" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K11" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13277,7 +11198,7 @@
       </c>
       <c r="J12" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K12" s="56">
         <f t="shared" si="1"/>
@@ -13312,11 +11233,11 @@
       </c>
       <c r="J13" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K13" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13347,11 +11268,11 @@
       </c>
       <c r="J14" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K14" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13382,11 +11303,11 @@
       </c>
       <c r="J15" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K15" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13417,11 +11338,11 @@
       </c>
       <c r="J16" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K16" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13452,11 +11373,11 @@
       </c>
       <c r="J17" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K17" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13487,11 +11408,11 @@
       </c>
       <c r="J18" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K18" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13522,11 +11443,11 @@
       </c>
       <c r="J19" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K19" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13557,11 +11478,11 @@
       </c>
       <c r="J20" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K20" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13592,7 +11513,7 @@
       </c>
       <c r="J21" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K21" s="56">
         <f t="shared" si="1"/>
@@ -13627,7 +11548,7 @@
       </c>
       <c r="J22" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K22" s="56">
         <f t="shared" si="1"/>
@@ -13662,11 +11583,11 @@
       </c>
       <c r="J23" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K23" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13697,11 +11618,11 @@
       </c>
       <c r="J24" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K24" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -13732,11 +11653,11 @@
       </c>
       <c r="J25" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K25" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13767,11 +11688,11 @@
       </c>
       <c r="J26" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K26" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13802,11 +11723,11 @@
       </c>
       <c r="J27" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K27" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13837,11 +11758,11 @@
       </c>
       <c r="J28" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13872,11 +11793,11 @@
       </c>
       <c r="J29" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K29" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13907,11 +11828,11 @@
       </c>
       <c r="J30" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K30" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13942,11 +11863,11 @@
       </c>
       <c r="J31" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K31" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -13977,11 +11898,11 @@
       </c>
       <c r="J32" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K32" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14012,11 +11933,11 @@
       </c>
       <c r="J33" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K33" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14047,11 +11968,11 @@
       </c>
       <c r="J34" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K34" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14082,11 +12003,11 @@
       </c>
       <c r="J35" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K35" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>461</v>
+        <v>459</v>
       </c>
     </row>
     <row r="36" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14117,11 +12038,11 @@
       </c>
       <c r="J36" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K36" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="37" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -14152,11 +12073,11 @@
       </c>
       <c r="J37" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K37" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -14187,7 +12108,7 @@
       </c>
       <c r="J38" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K38" s="56">
         <f t="shared" si="1"/>
@@ -14222,7 +12143,7 @@
       </c>
       <c r="J39" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K39" s="56">
         <f t="shared" si="1"/>
@@ -14257,7 +12178,7 @@
       </c>
       <c r="J40" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K40" s="56">
         <f t="shared" si="1"/>
@@ -14292,11 +12213,11 @@
       </c>
       <c r="J41" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K41" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14327,11 +12248,11 @@
       </c>
       <c r="J42" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K42" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14362,7 +12283,7 @@
       </c>
       <c r="J43" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K43" s="56">
         <f t="shared" si="1"/>
@@ -14397,7 +12318,7 @@
       </c>
       <c r="J44" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K44" s="56">
         <f t="shared" si="1"/>
@@ -14432,11 +12353,11 @@
       </c>
       <c r="J45" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K45" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14467,7 +12388,7 @@
       </c>
       <c r="J46" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K46" s="56">
         <f t="shared" si="1"/>
@@ -14502,11 +12423,11 @@
       </c>
       <c r="J47" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K47" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="48" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14537,11 +12458,11 @@
       </c>
       <c r="J48" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K48" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="49" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14572,7 +12493,7 @@
       </c>
       <c r="J49" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K49" s="56">
         <f t="shared" si="1"/>
@@ -14607,7 +12528,7 @@
       </c>
       <c r="J50" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>-244587</v>
+        <v>-244589</v>
       </c>
       <c r="K50" s="56" t="e">
         <f t="shared" si="1"/>
@@ -14642,11 +12563,11 @@
       </c>
       <c r="J51" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K51" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14677,11 +12598,11 @@
       </c>
       <c r="J52" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K52" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="53" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14712,11 +12633,11 @@
       </c>
       <c r="J53" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K53" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="54" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -14747,11 +12668,11 @@
       </c>
       <c r="J54" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K54" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="55" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14782,11 +12703,11 @@
       </c>
       <c r="J55" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="K55" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14817,11 +12738,11 @@
       </c>
       <c r="J56" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K56" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="57" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14852,11 +12773,11 @@
       </c>
       <c r="J57" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K57" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1204</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="58" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14887,7 +12808,7 @@
       </c>
       <c r="J58" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="K58" s="56">
         <f t="shared" si="1"/>
@@ -14922,11 +12843,11 @@
       </c>
       <c r="J59" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K59" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -14957,11 +12878,11 @@
       </c>
       <c r="J60" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K60" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -14992,11 +12913,11 @@
       </c>
       <c r="J61" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K61" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>896</v>
+        <v>894</v>
       </c>
     </row>
     <row r="62" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15027,11 +12948,11 @@
       </c>
       <c r="J62" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K62" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="63" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -15062,11 +12983,11 @@
       </c>
       <c r="J63" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="K63" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -15097,11 +13018,11 @@
       </c>
       <c r="J64" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K64" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="65" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -15132,11 +13053,11 @@
       </c>
       <c r="J65" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K65" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="66" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -15167,7 +13088,7 @@
       </c>
       <c r="J66" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K66" s="56">
         <f t="shared" si="1"/>
@@ -15202,7 +13123,7 @@
       </c>
       <c r="J67" s="56">
         <f t="shared" ref="J67:J130" ca="1" si="2">IFERROR((H67-$K$1),0)</f>
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="K67" s="56">
         <f t="shared" ref="K67:K130" si="3">IF(I67="ยังไม่ได้ทำ BG",-9999,IF(OR(I67="ค้ำเงินสด",I67="ค้ำประกันรายได้",I67="วงเงินรวม SCG"),999,IFERROR((I67-$K$1),0)))</f>
@@ -15237,11 +13158,11 @@
       </c>
       <c r="J68" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K68" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15272,11 +13193,11 @@
       </c>
       <c r="J69" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K69" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15307,11 +13228,11 @@
       </c>
       <c r="J70" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K70" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15342,11 +13263,11 @@
       </c>
       <c r="J71" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K71" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15379,11 +13300,11 @@
       </c>
       <c r="J72" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-330</v>
+        <v>-332</v>
       </c>
       <c r="K72" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="73" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15414,11 +13335,11 @@
       </c>
       <c r="J73" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-330</v>
+        <v>-332</v>
       </c>
       <c r="K73" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="74" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -15449,11 +13370,11 @@
       </c>
       <c r="J74" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K74" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="75" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -15484,11 +13405,11 @@
       </c>
       <c r="J75" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K75" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15519,11 +13440,11 @@
       </c>
       <c r="J76" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K76" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="77" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15554,7 +13475,7 @@
       </c>
       <c r="J77" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K77" s="56">
         <f t="shared" si="3"/>
@@ -15589,7 +13510,7 @@
       </c>
       <c r="J78" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K78" s="56">
         <f t="shared" si="3"/>
@@ -15626,7 +13547,7 @@
       </c>
       <c r="J79" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-2157</v>
+        <v>-2159</v>
       </c>
       <c r="K79" s="56">
         <f t="shared" si="3"/>
@@ -15663,7 +13584,7 @@
       </c>
       <c r="J80" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-2157</v>
+        <v>-2159</v>
       </c>
       <c r="K80" s="56">
         <f t="shared" si="3"/>
@@ -15698,7 +13619,7 @@
       </c>
       <c r="J81" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K81" s="56">
         <f t="shared" si="3"/>
@@ -15733,11 +13654,11 @@
       </c>
       <c r="J82" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K82" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="83" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15768,11 +13689,11 @@
       </c>
       <c r="J83" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K83" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="84" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15803,11 +13724,11 @@
       </c>
       <c r="J84" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K84" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="85" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15838,11 +13759,11 @@
       </c>
       <c r="J85" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K85" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="86" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15873,7 +13794,7 @@
       </c>
       <c r="J86" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K86" s="56">
         <f t="shared" si="3"/>
@@ -15908,11 +13829,11 @@
       </c>
       <c r="J87" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K87" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="88" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -15943,11 +13864,11 @@
       </c>
       <c r="J88" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K88" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="89" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -15978,11 +13899,11 @@
       </c>
       <c r="J89" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K89" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="90" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16013,11 +13934,11 @@
       </c>
       <c r="J90" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K90" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>730</v>
+        <v>728</v>
       </c>
     </row>
     <row r="91" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16050,11 +13971,11 @@
       </c>
       <c r="J91" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K91" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16085,11 +14006,11 @@
       </c>
       <c r="J92" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K92" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="93" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16120,11 +14041,11 @@
       </c>
       <c r="J93" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K93" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="94" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16153,11 +14074,11 @@
       </c>
       <c r="J94" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-244587</v>
+        <v>-244589</v>
       </c>
       <c r="K94" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>1131</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="95" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16188,11 +14109,11 @@
       </c>
       <c r="J95" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K95" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="96" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16223,11 +14144,11 @@
       </c>
       <c r="J96" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K96" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="97" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16258,11 +14179,11 @@
       </c>
       <c r="J97" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K97" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16293,11 +14214,11 @@
       </c>
       <c r="J98" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K98" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16328,11 +14249,11 @@
       </c>
       <c r="J99" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K99" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16363,11 +14284,11 @@
       </c>
       <c r="J100" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K100" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16398,11 +14319,11 @@
       </c>
       <c r="J101" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="K101" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16433,11 +14354,11 @@
       </c>
       <c r="J102" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K102" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16468,11 +14389,11 @@
       </c>
       <c r="J103" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K103" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="104" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16503,11 +14424,11 @@
       </c>
       <c r="J104" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K104" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16540,7 +14461,7 @@
       </c>
       <c r="J105" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-3122</v>
+        <v>-3124</v>
       </c>
       <c r="K105" s="56">
         <f t="shared" si="3"/>
@@ -16575,11 +14496,11 @@
       </c>
       <c r="J106" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K106" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="107" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16610,11 +14531,11 @@
       </c>
       <c r="J107" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="K107" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="108" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16645,7 +14566,7 @@
       </c>
       <c r="J108" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="K108" s="56">
         <f t="shared" si="3"/>
@@ -16680,11 +14601,11 @@
       </c>
       <c r="J109" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K109" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="110" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16715,11 +14636,11 @@
       </c>
       <c r="J110" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K110" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="111" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16750,7 +14671,7 @@
       </c>
       <c r="J111" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K111" s="56">
         <f t="shared" si="3"/>
@@ -16785,11 +14706,11 @@
       </c>
       <c r="J112" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K112" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="113" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16820,11 +14741,11 @@
       </c>
       <c r="J113" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K113" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="114" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16855,11 +14776,11 @@
       </c>
       <c r="J114" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K114" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="115" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -16890,11 +14811,11 @@
       </c>
       <c r="J115" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K115" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>1416</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="116" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -16925,14 +14846,14 @@
       </c>
       <c r="J116" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K116" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>779</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A117" s="29" t="s">
         <v>767</v>
       </c>
@@ -16962,7 +14883,7 @@
       </c>
       <c r="J117" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K117" s="56">
         <f t="shared" si="3"/>
@@ -16997,11 +14918,11 @@
       </c>
       <c r="J118" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K118" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="119" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17032,11 +14953,11 @@
       </c>
       <c r="J119" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K119" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="120" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17067,11 +14988,11 @@
       </c>
       <c r="J120" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K120" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="121" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17102,11 +15023,11 @@
       </c>
       <c r="J121" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K121" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="122" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -17137,7 +15058,7 @@
       </c>
       <c r="J122" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K122" s="56">
         <f t="shared" si="3"/>
@@ -17172,7 +15093,7 @@
       </c>
       <c r="J123" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K123" s="56">
         <f t="shared" si="3"/>
@@ -17207,11 +15128,11 @@
       </c>
       <c r="J124" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K124" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="125" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17242,7 +15163,7 @@
       </c>
       <c r="J125" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K125" s="56">
         <f t="shared" si="3"/>
@@ -17277,7 +15198,7 @@
       </c>
       <c r="J126" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K126" s="56">
         <f t="shared" si="3"/>
@@ -17312,7 +15233,7 @@
       </c>
       <c r="J127" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K127" s="56">
         <f t="shared" si="3"/>
@@ -17347,7 +15268,7 @@
       </c>
       <c r="J128" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K128" s="56">
         <f t="shared" si="3"/>
@@ -17382,11 +15303,11 @@
       </c>
       <c r="J129" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K129" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="130" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -17417,7 +15338,7 @@
       </c>
       <c r="J130" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K130" s="56">
         <f t="shared" si="3"/>
@@ -17452,7 +15373,7 @@
       </c>
       <c r="J131" s="56">
         <f t="shared" ref="J131:J194" ca="1" si="4">IFERROR((H131-$K$1),0)</f>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K131" s="56">
         <f t="shared" ref="K131:K194" si="5">IF(I131="ยังไม่ได้ทำ BG",-9999,IF(OR(I131="ค้ำเงินสด",I131="ค้ำประกันรายได้",I131="วงเงินรวม SCG"),999,IFERROR((I131-$K$1),0)))</f>
@@ -17522,7 +15443,7 @@
       </c>
       <c r="J133" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K133" s="56">
         <f t="shared" si="5"/>
@@ -17557,7 +15478,7 @@
       </c>
       <c r="J134" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K134" s="56">
         <f t="shared" si="5"/>
@@ -17592,7 +15513,7 @@
       </c>
       <c r="J135" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K135" s="56">
         <f t="shared" si="5"/>
@@ -17627,7 +15548,7 @@
       </c>
       <c r="J136" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K136" s="56">
         <f t="shared" si="5"/>
@@ -17662,11 +15583,11 @@
       </c>
       <c r="J137" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K137" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="138" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17701,7 +15622,7 @@
       </c>
       <c r="K138" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="139" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -17732,11 +15653,11 @@
       </c>
       <c r="J139" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K139" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="140" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17771,7 +15692,7 @@
       </c>
       <c r="K140" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="141" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17802,11 +15723,11 @@
       </c>
       <c r="J141" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K141" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="142" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17837,11 +15758,11 @@
       </c>
       <c r="J142" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K142" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="143" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -17872,7 +15793,7 @@
       </c>
       <c r="J143" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K143" s="56">
         <f t="shared" si="5"/>
@@ -17907,11 +15828,11 @@
       </c>
       <c r="J144" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K144" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="145" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -17942,7 +15863,7 @@
       </c>
       <c r="J145" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K145" s="56">
         <f t="shared" si="5"/>
@@ -17977,11 +15898,11 @@
       </c>
       <c r="J146" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K146" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="147" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18012,11 +15933,11 @@
       </c>
       <c r="J147" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K147" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="148" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18047,11 +15968,11 @@
       </c>
       <c r="J148" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K148" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="149" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18082,11 +16003,11 @@
       </c>
       <c r="J149" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K149" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="150" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18119,11 +16040,11 @@
       </c>
       <c r="J150" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K150" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18154,11 +16075,11 @@
       </c>
       <c r="J151" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K151" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="152" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18189,11 +16110,11 @@
       </c>
       <c r="J152" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K152" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="153" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18224,11 +16145,11 @@
       </c>
       <c r="J153" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K153" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="154" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18259,11 +16180,11 @@
       </c>
       <c r="J154" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K154" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="155" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18294,11 +16215,11 @@
       </c>
       <c r="J155" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K155" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="156" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18329,11 +16250,11 @@
       </c>
       <c r="J156" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K156" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="157" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18364,11 +16285,11 @@
       </c>
       <c r="J157" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K157" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="158" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18399,11 +16320,11 @@
       </c>
       <c r="J158" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K158" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="159" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18434,11 +16355,11 @@
       </c>
       <c r="J159" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K159" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="160" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18469,11 +16390,11 @@
       </c>
       <c r="J160" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K160" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="161" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18504,11 +16425,11 @@
       </c>
       <c r="J161" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K161" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="162" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18539,11 +16460,11 @@
       </c>
       <c r="J162" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K162" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="163" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18574,11 +16495,11 @@
       </c>
       <c r="J163" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K163" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="164" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18609,11 +16530,11 @@
       </c>
       <c r="J164" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K164" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="165" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18644,11 +16565,11 @@
       </c>
       <c r="J165" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="K165" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="166" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18679,11 +16600,11 @@
       </c>
       <c r="J166" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K166" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="167" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18714,11 +16635,11 @@
       </c>
       <c r="J167" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K167" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="168" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18751,11 +16672,11 @@
       </c>
       <c r="J168" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K168" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="169" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18786,11 +16707,11 @@
       </c>
       <c r="J169" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K169" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="170" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18821,11 +16742,11 @@
       </c>
       <c r="J170" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K170" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>456</v>
+        <v>454</v>
       </c>
     </row>
     <row r="171" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -18856,11 +16777,11 @@
       </c>
       <c r="J171" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K171" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="172" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18891,11 +16812,11 @@
       </c>
       <c r="J172" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K172" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="173" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18926,11 +16847,11 @@
       </c>
       <c r="J173" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K173" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="174" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -18961,7 +16882,7 @@
       </c>
       <c r="J174" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K174" s="56">
         <f t="shared" si="5"/>
@@ -18996,11 +16917,11 @@
       </c>
       <c r="J175" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K175" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="176" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19031,11 +16952,11 @@
       </c>
       <c r="J176" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K176" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="177" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19066,11 +16987,11 @@
       </c>
       <c r="J177" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K177" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="178" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19101,11 +17022,11 @@
       </c>
       <c r="J178" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K178" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="179" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19136,11 +17057,11 @@
       </c>
       <c r="J179" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K179" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="180" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19171,11 +17092,11 @@
       </c>
       <c r="J180" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="K180" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="181" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -19206,7 +17127,7 @@
       </c>
       <c r="J181" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="K181" s="56">
         <f t="shared" si="5"/>
@@ -19241,7 +17162,7 @@
       </c>
       <c r="J182" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K182" s="56">
         <f t="shared" si="5"/>
@@ -19276,7 +17197,7 @@
       </c>
       <c r="J183" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K183" s="56">
         <f t="shared" si="5"/>
@@ -19311,7 +17232,7 @@
       </c>
       <c r="J184" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K184" s="56">
         <f t="shared" si="5"/>
@@ -19346,7 +17267,7 @@
       </c>
       <c r="J185" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K185" s="56">
         <f t="shared" si="5"/>
@@ -19381,11 +17302,11 @@
       </c>
       <c r="J186" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K186" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="187" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -19416,7 +17337,7 @@
       </c>
       <c r="J187" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K187" s="56">
         <f t="shared" si="5"/>
@@ -19451,7 +17372,7 @@
       </c>
       <c r="J188" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-57</v>
+        <v>-59</v>
       </c>
       <c r="K188" s="56">
         <f t="shared" si="5"/>
@@ -19488,7 +17409,7 @@
       </c>
       <c r="J189" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1153</v>
+        <v>-1155</v>
       </c>
       <c r="K189" s="56">
         <f t="shared" si="5"/>
@@ -19525,7 +17446,7 @@
       </c>
       <c r="J190" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1153</v>
+        <v>-1155</v>
       </c>
       <c r="K190" s="56">
         <f t="shared" si="5"/>
@@ -19562,7 +17483,7 @@
       </c>
       <c r="J191" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-788</v>
+        <v>-790</v>
       </c>
       <c r="K191" s="56">
         <f t="shared" si="5"/>
@@ -19599,7 +17520,7 @@
       </c>
       <c r="J192" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1153</v>
+        <v>-1155</v>
       </c>
       <c r="K192" s="56">
         <f t="shared" si="5"/>
@@ -19636,7 +17557,7 @@
       </c>
       <c r="J193" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1153</v>
+        <v>-1155</v>
       </c>
       <c r="K193" s="56">
         <f t="shared" si="5"/>
@@ -19673,7 +17594,7 @@
       </c>
       <c r="J194" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1153</v>
+        <v>-1155</v>
       </c>
       <c r="K194" s="56">
         <f t="shared" si="5"/>
@@ -19708,11 +17629,11 @@
       </c>
       <c r="J195" s="56">
         <f t="shared" ref="J195:J258" ca="1" si="6">IFERROR((H195-$K$1),0)</f>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K195" s="56">
         <f t="shared" ref="K195:K258" ca="1" si="7">IF(I195="ยังไม่ได้ทำ BG",-9999,IF(OR(I195="ค้ำเงินสด",I195="ค้ำประกันรายได้",I195="วงเงินรวม SCG"),999,IFERROR((I195-$K$1),0)))</f>
-        <v>670</v>
+        <v>668</v>
       </c>
     </row>
     <row r="196" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19743,14 +17664,14 @@
       </c>
       <c r="J196" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K196" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>670</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" ht="21" customHeight="1" thickBot="1">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
       <c r="A197" s="15" t="s">
         <v>768</v>
       </c>
@@ -19767,7 +17688,7 @@
         <v>775</v>
       </c>
       <c r="F197" s="22">
-        <v>244592</v>
+        <v>244622</v>
       </c>
       <c r="G197" s="13" t="s">
         <v>779</v>
@@ -19780,11 +17701,11 @@
       </c>
       <c r="J197" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K197" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="198" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19815,11 +17736,11 @@
       </c>
       <c r="J198" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K198" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="199" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19850,11 +17771,11 @@
       </c>
       <c r="J199" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K199" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="200" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -19885,11 +17806,11 @@
       </c>
       <c r="J200" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K200" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="201" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -19920,11 +17841,11 @@
       </c>
       <c r="J201" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-244587</v>
+        <v>-244589</v>
       </c>
       <c r="K201" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="202" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -19955,14 +17876,14 @@
       </c>
       <c r="J202" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K202" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>40</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A203" s="15" t="s">
         <v>768</v>
       </c>
@@ -19979,7 +17900,7 @@
         <v>775</v>
       </c>
       <c r="F203" s="22">
-        <v>244592</v>
+        <v>244683</v>
       </c>
       <c r="G203" s="28" t="s">
         <v>773</v>
@@ -19992,11 +17913,11 @@
       </c>
       <c r="J203" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-1883</v>
+        <v>-1885</v>
       </c>
       <c r="K203" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="204" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -20027,33 +17948,35 @@
       </c>
       <c r="J204" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K204" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="205" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
-      <c r="A205" s="15" t="s">
+      <c r="A205" s="41" t="s">
         <v>768</v>
       </c>
-      <c r="B205" s="8" t="s">
+      <c r="B205" s="30" t="s">
         <v>543</v>
       </c>
-      <c r="C205" s="8" t="s">
+      <c r="C205" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="D205" s="8" t="s">
+      <c r="D205" s="30" t="s">
         <v>271</v>
       </c>
-      <c r="E205" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="F205" s="22">
-        <v>244895</v>
-      </c>
-      <c r="G205" s="28"/>
+      <c r="E205" s="29" t="s">
+        <v>775</v>
+      </c>
+      <c r="F205" s="32">
+        <v>244622</v>
+      </c>
+      <c r="G205" s="33" t="s">
+        <v>744</v>
+      </c>
       <c r="H205" s="57">
         <v>245626</v>
       </c>
@@ -20062,14 +17985,14 @@
       </c>
       <c r="J205" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K205" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A206" s="41" t="s">
         <v>768</v>
       </c>
@@ -20086,7 +18009,7 @@
         <v>775</v>
       </c>
       <c r="F206" s="32">
-        <v>244592</v>
+        <v>244622</v>
       </c>
       <c r="G206" s="33" t="s">
         <v>744</v>
@@ -20099,11 +18022,11 @@
       </c>
       <c r="J206" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K206" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="207" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -20134,11 +18057,11 @@
       </c>
       <c r="J207" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K207" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="208" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -20169,7 +18092,7 @@
       </c>
       <c r="J208" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K208" s="56">
         <f t="shared" si="7"/>
@@ -20206,11 +18129,11 @@
       </c>
       <c r="J209" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-788</v>
+        <v>-790</v>
       </c>
       <c r="K209" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="210" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -20241,14 +18164,14 @@
       </c>
       <c r="J210" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K210" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+    <row r="211" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A211" s="41" t="s">
         <v>768</v>
       </c>
@@ -20265,7 +18188,7 @@
         <v>775</v>
       </c>
       <c r="F211" s="32">
-        <v>244592</v>
+        <v>244622</v>
       </c>
       <c r="G211" s="33" t="s">
         <v>3</v>
@@ -20278,14 +18201,14 @@
       </c>
       <c r="J211" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K211" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+    <row r="212" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A212" s="41" t="s">
         <v>768</v>
       </c>
@@ -20302,7 +18225,7 @@
         <v>775</v>
       </c>
       <c r="F212" s="32">
-        <v>244592</v>
+        <v>244622</v>
       </c>
       <c r="G212" s="33" t="s">
         <v>3</v>
@@ -20315,14 +18238,14 @@
       </c>
       <c r="J212" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K212" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+    <row r="213" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
       <c r="A213" s="41" t="s">
         <v>768</v>
       </c>
@@ -20339,7 +18262,7 @@
         <v>775</v>
       </c>
       <c r="F213" s="32">
-        <v>244592</v>
+        <v>244622</v>
       </c>
       <c r="G213" s="33" t="s">
         <v>3</v>
@@ -20352,7 +18275,7 @@
       </c>
       <c r="J213" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-1518</v>
+        <v>-1520</v>
       </c>
       <c r="K213" s="56">
         <f t="shared" si="7"/>
@@ -20387,11 +18310,11 @@
       </c>
       <c r="J214" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K214" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="215" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -20422,11 +18345,11 @@
       </c>
       <c r="J215" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K215" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="216" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -20457,11 +18380,11 @@
       </c>
       <c r="J216" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K216" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="217" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -20492,11 +18415,11 @@
       </c>
       <c r="J217" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K217" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="218" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -20527,11 +18450,11 @@
       </c>
       <c r="J218" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K218" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1182</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="219" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -20562,11 +18485,11 @@
       </c>
       <c r="J219" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K219" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="220" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -20597,11 +18520,11 @@
       </c>
       <c r="J220" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K220" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="221" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -20632,11 +18555,11 @@
       </c>
       <c r="J221" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K221" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="222" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -20667,11 +18590,11 @@
       </c>
       <c r="J222" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K222" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="223" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -20702,7 +18625,7 @@
       </c>
       <c r="J223" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K223" s="56">
         <f t="shared" si="7"/>
@@ -20737,11 +18660,11 @@
       </c>
       <c r="J224" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K224" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="225" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -20772,7 +18695,7 @@
       </c>
       <c r="J225" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K225" s="56">
         <f t="shared" si="7"/>
@@ -20807,7 +18730,7 @@
       </c>
       <c r="J226" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K226" s="56">
         <f t="shared" si="7"/>
@@ -20842,7 +18765,7 @@
       </c>
       <c r="J227" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K227" s="56">
         <f t="shared" si="7"/>
@@ -20877,11 +18800,11 @@
       </c>
       <c r="J228" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K228" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
@@ -20912,11 +18835,11 @@
       </c>
       <c r="J229" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K229" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -20947,7 +18870,7 @@
       </c>
       <c r="J230" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K230" s="56">
         <f t="shared" si="7"/>
@@ -20984,14 +18907,14 @@
       </c>
       <c r="J231" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-57</v>
+        <v>-59</v>
       </c>
       <c r="K231" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
+    <row r="232" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
       <c r="A232" s="41" t="s">
         <v>768</v>
       </c>
@@ -21008,7 +18931,7 @@
         <v>775</v>
       </c>
       <c r="F232" s="32">
-        <v>244592</v>
+        <v>244622</v>
       </c>
       <c r="G232" s="33" t="s">
         <v>3</v>
@@ -21021,11 +18944,11 @@
       </c>
       <c r="J232" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K232" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="233" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21056,7 +18979,7 @@
       </c>
       <c r="J233" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K233" s="56">
         <f t="shared" si="7"/>
@@ -21091,7 +19014,7 @@
       </c>
       <c r="J234" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K234" s="56">
         <f t="shared" si="7"/>
@@ -21126,7 +19049,7 @@
       </c>
       <c r="J235" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K235" s="56">
         <f t="shared" si="7"/>
@@ -21163,7 +19086,7 @@
       </c>
       <c r="J236" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K236" s="56">
         <f t="shared" si="7"/>
@@ -21198,11 +19121,11 @@
       </c>
       <c r="J237" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K237" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="238" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21233,11 +19156,11 @@
       </c>
       <c r="J238" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K238" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="239" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21268,11 +19191,11 @@
       </c>
       <c r="J239" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K239" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="240" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21303,11 +19226,11 @@
       </c>
       <c r="J240" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K240" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="241" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21338,11 +19261,11 @@
       </c>
       <c r="J241" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K241" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="242" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21373,11 +19296,11 @@
       </c>
       <c r="J242" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K242" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="243" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21410,11 +19333,11 @@
       </c>
       <c r="J243" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K243" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="244" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21447,11 +19370,11 @@
       </c>
       <c r="J244" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K244" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="245" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21482,11 +19405,11 @@
       </c>
       <c r="J245" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K245" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="246" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21517,11 +19440,11 @@
       </c>
       <c r="J246" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K246" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="247" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21552,11 +19475,11 @@
       </c>
       <c r="J247" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K247" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="248" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21589,11 +19512,11 @@
       </c>
       <c r="J248" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K248" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="249" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21624,11 +19547,11 @@
       </c>
       <c r="J249" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K249" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="250" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21659,7 +19582,7 @@
       </c>
       <c r="J250" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K250" s="56">
         <f t="shared" si="7"/>
@@ -21694,7 +19617,7 @@
       </c>
       <c r="J251" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K251" s="56">
         <f t="shared" si="7"/>
@@ -21729,11 +19652,11 @@
       </c>
       <c r="J252" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K252" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="253" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21764,11 +19687,11 @@
       </c>
       <c r="J253" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K253" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="254" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21799,11 +19722,11 @@
       </c>
       <c r="J254" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K254" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="255" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21834,11 +19757,11 @@
       </c>
       <c r="J255" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K255" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="256" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21869,11 +19792,11 @@
       </c>
       <c r="J256" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K256" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="257" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -21904,11 +19827,11 @@
       </c>
       <c r="J257" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K257" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="258" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21939,11 +19862,11 @@
       </c>
       <c r="J258" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K258" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="259" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -21974,11 +19897,11 @@
       </c>
       <c r="J259" s="56">
         <f t="shared" ref="J259:J297" ca="1" si="8">IFERROR((H259-$K$1),0)</f>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K259" s="56">
         <f t="shared" ref="K259:K297" ca="1" si="9">IF(I259="ยังไม่ได้ทำ BG",-9999,IF(OR(I259="ค้ำเงินสด",I259="ค้ำประกันรายได้",I259="วงเงินรวม SCG"),999,IFERROR((I259-$K$1),0)))</f>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="260" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -22009,11 +19932,11 @@
       </c>
       <c r="J260" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K260" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="261" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -22044,11 +19967,11 @@
       </c>
       <c r="J261" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K261" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="262" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -22079,11 +20002,11 @@
       </c>
       <c r="J262" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K262" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="263" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -22114,11 +20037,11 @@
       </c>
       <c r="J263" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K263" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="264" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -22149,11 +20072,11 @@
       </c>
       <c r="J264" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K264" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="265" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -22184,11 +20107,11 @@
       </c>
       <c r="J265" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K265" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="266" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -22219,11 +20142,11 @@
       </c>
       <c r="J266" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K266" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>1223</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="267" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -22254,11 +20177,11 @@
       </c>
       <c r="J267" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K267" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="268" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -22289,11 +20212,11 @@
       </c>
       <c r="J268" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K268" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="269" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -22324,11 +20247,11 @@
       </c>
       <c r="J269" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K269" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="270" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
@@ -22359,11 +20282,11 @@
       </c>
       <c r="J270" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K270" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>857</v>
+        <v>855</v>
       </c>
     </row>
     <row r="271" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -22394,11 +20317,11 @@
       </c>
       <c r="J271" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K271" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="272" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
@@ -22429,11 +20352,11 @@
       </c>
       <c r="J272" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K272" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="273" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -22464,11 +20387,11 @@
       </c>
       <c r="J273" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K273" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="274" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -22499,11 +20422,11 @@
       </c>
       <c r="J274" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K274" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>856</v>
+        <v>854</v>
       </c>
     </row>
     <row r="275" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -22534,14 +20457,14 @@
       </c>
       <c r="J275" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K275" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>856</v>
-      </c>
-    </row>
-    <row r="276" spans="1:11" ht="21" customHeight="1" thickBot="1">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
       <c r="A276" s="41" t="s">
         <v>768</v>
       </c>
@@ -22558,7 +20481,7 @@
         <v>775</v>
       </c>
       <c r="F276" s="32">
-        <v>244592</v>
+        <v>244622</v>
       </c>
       <c r="G276" s="33" t="s">
         <v>3</v>
@@ -22571,11 +20494,11 @@
       </c>
       <c r="J276" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K276" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="277" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -22606,7 +20529,7 @@
       </c>
       <c r="J277" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K277" s="56">
         <f t="shared" si="9"/>
@@ -22641,11 +20564,11 @@
       </c>
       <c r="J278" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K278" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="279" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -22676,11 +20599,11 @@
       </c>
       <c r="J279" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K279" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="280" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
@@ -22711,7 +20634,7 @@
       </c>
       <c r="J280" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K280" s="56">
         <f t="shared" si="9"/>
@@ -22746,7 +20669,7 @@
       </c>
       <c r="J281" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K281" s="56">
         <f t="shared" si="9"/>
@@ -22781,7 +20704,7 @@
       </c>
       <c r="J282" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K282" s="56">
         <f t="shared" si="9"/>
@@ -22816,7 +20739,7 @@
       </c>
       <c r="J283" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K283" s="56">
         <f t="shared" si="9"/>
@@ -22851,7 +20774,7 @@
       </c>
       <c r="J284" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K284" s="56">
         <f t="shared" si="9"/>
@@ -22886,7 +20809,7 @@
       </c>
       <c r="J285" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K285" s="56">
         <f t="shared" si="9"/>
@@ -22921,7 +20844,7 @@
       </c>
       <c r="J286" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K286" s="56">
         <f t="shared" si="9"/>
@@ -22956,7 +20879,7 @@
       </c>
       <c r="J287" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K287" s="56">
         <f t="shared" si="9"/>
@@ -22991,7 +20914,7 @@
       </c>
       <c r="J288" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K288" s="56">
         <f t="shared" si="9"/>
@@ -23026,7 +20949,7 @@
       </c>
       <c r="J289" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="K289" s="56">
         <f t="shared" si="9"/>
@@ -23061,7 +20984,7 @@
       </c>
       <c r="J290" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K290" s="56">
         <f t="shared" si="9"/>
@@ -23096,7 +21019,7 @@
       </c>
       <c r="J291" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K291" s="56">
         <f t="shared" si="9"/>
@@ -23132,11 +21055,11 @@
       </c>
       <c r="J292" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="K292" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="XEG292" s="46"/>
     </row>
@@ -23168,7 +21091,7 @@
       </c>
       <c r="J293" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K293" s="56">
         <f t="shared" si="9"/>
@@ -23204,7 +21127,7 @@
       </c>
       <c r="J294" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="K294" s="56">
         <f t="shared" si="9"/>
@@ -23237,7 +21160,7 @@
       </c>
       <c r="J295" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>-244587</v>
+        <v>-244589</v>
       </c>
       <c r="K295" s="56">
         <f t="shared" si="9"/>
@@ -23268,11 +21191,11 @@
       <c r="I296" s="57"/>
       <c r="J296" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>-244587</v>
+        <v>-244589</v>
       </c>
       <c r="K296" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>-244587</v>
+        <v>-244589</v>
       </c>
       <c r="XEG296" s="46"/>
     </row>
@@ -23300,15 +21223,20 @@
       <c r="I297" s="57"/>
       <c r="J297" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>-244587</v>
+        <v>-244589</v>
       </c>
       <c r="K297" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>-244587</v>
+        <v>-244589</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:I297" xr:uid="{2ADD9999-E05E-4DFC-9ACA-F5F92389CAD8}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="NORTHEAST"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="5">
       <filters>
         <dateGroupItem year="2569" month="8" dateTimeGrouping="month"/>
@@ -23318,181 +21246,191 @@
   <sortState ref="A2:G296">
     <sortCondition ref="A2:A296"/>
   </sortState>
-  <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G293 F261:G275 F277:F293 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204:F205 F4:F5 F51 F27:F28 F56 F65:G100 G203:G211 F102:G202 E295:E297 A295:D296 F295:G296 A3:E293">
-    <cfRule type="expression" dxfId="73" priority="359">
+  <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G293 F261:G275 F277:F293 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204 F4:F5 F51 F27:F28 F56 F65:G100 G203:G204 F102:G202 E295:E297 A295:D296 F295:G296 A3:E204 A206:E293 A205:D205 G206:G211">
+    <cfRule type="expression" dxfId="43" priority="366">
       <formula>$F2="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G101">
-    <cfRule type="expression" dxfId="72" priority="270">
+    <cfRule type="expression" dxfId="42" priority="277">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="expression" dxfId="71" priority="245">
+    <cfRule type="expression" dxfId="41" priority="252">
       <formula>$F4="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="70" priority="244">
+    <cfRule type="expression" dxfId="40" priority="251">
       <formula>$F5="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="expression" dxfId="69" priority="243">
+    <cfRule type="expression" dxfId="39" priority="250">
       <formula>$F27="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41">
-    <cfRule type="expression" dxfId="68" priority="240">
+    <cfRule type="expression" dxfId="38" priority="247">
       <formula>$F41="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51">
-    <cfRule type="expression" dxfId="67" priority="238">
+    <cfRule type="expression" dxfId="37" priority="245">
       <formula>$F51="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64">
-    <cfRule type="expression" dxfId="66" priority="237">
+    <cfRule type="expression" dxfId="36" priority="244">
       <formula>$F64="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="65" priority="236">
+    <cfRule type="expression" dxfId="35" priority="243">
       <formula>$F56="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="expression" dxfId="64" priority="222">
+    <cfRule type="expression" dxfId="34" priority="229">
       <formula>$F28="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59">
-    <cfRule type="expression" dxfId="63" priority="216">
+    <cfRule type="expression" dxfId="33" priority="223">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="expression" dxfId="62" priority="198">
+    <cfRule type="expression" dxfId="32" priority="205">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A297">
-    <cfRule type="expression" dxfId="61" priority="196">
+    <cfRule type="expression" dxfId="31" priority="203">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F206">
-    <cfRule type="expression" dxfId="60" priority="191">
-      <formula>$F206="ปิดชั่วคราว"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F203">
-    <cfRule type="expression" dxfId="59" priority="186">
+    <cfRule type="expression" dxfId="29" priority="193">
       <formula>$F203="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="expression" dxfId="58" priority="165">
+    <cfRule type="expression" dxfId="28" priority="172">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G212">
-    <cfRule type="expression" dxfId="57" priority="164">
+    <cfRule type="expression" dxfId="27" priority="171">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B297">
-    <cfRule type="expression" dxfId="56" priority="158">
+    <cfRule type="expression" dxfId="26" priority="165">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F297">
-    <cfRule type="expression" dxfId="55" priority="156">
+    <cfRule type="expression" dxfId="25" priority="163">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F211">
-    <cfRule type="expression" dxfId="54" priority="155">
-      <formula>$F211="ปิดชั่วคราว"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F236">
-    <cfRule type="expression" dxfId="53" priority="132">
+    <cfRule type="expression" dxfId="23" priority="139">
       <formula>$F236="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250">
-    <cfRule type="expression" dxfId="52" priority="128">
+    <cfRule type="expression" dxfId="22" priority="135">
       <formula>$F250="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F276">
-    <cfRule type="expression" dxfId="51" priority="127">
-      <formula>$F276="ปิดชั่วคราว"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F232">
-    <cfRule type="expression" dxfId="50" priority="58">
-      <formula>$F232="ปิดชั่วคราว"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F212">
-    <cfRule type="expression" dxfId="49" priority="18">
-      <formula>$F212="ปิดชั่วคราว"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F213">
-    <cfRule type="expression" dxfId="48" priority="17">
+    <cfRule type="expression" dxfId="18" priority="24">
       <formula>$F213="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A294:G294">
-    <cfRule type="expression" dxfId="47" priority="14">
+    <cfRule type="expression" dxfId="17" priority="21">
       <formula>$F294="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F243">
-    <cfRule type="expression" dxfId="46" priority="13">
+    <cfRule type="expression" dxfId="16" priority="20">
       <formula>$F243="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F244">
-    <cfRule type="expression" dxfId="45" priority="12">
+    <cfRule type="expression" dxfId="15" priority="19">
       <formula>$F244="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F248">
-    <cfRule type="expression" dxfId="44" priority="11">
+    <cfRule type="expression" dxfId="14" priority="18">
       <formula>$F248="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H297">
-    <cfRule type="expression" dxfId="43" priority="9">
+    <cfRule type="expression" dxfId="13" priority="16">
       <formula>$J3&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H297">
-    <cfRule type="expression" dxfId="42" priority="4">
+    <cfRule type="expression" dxfId="12" priority="11">
       <formula>$J2&gt;=180</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="5">
+    <cfRule type="expression" dxfId="11" priority="12">
       <formula>$J2&gt;=90</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="6">
+    <cfRule type="expression" dxfId="10" priority="13">
       <formula>$J2&lt;90</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I297">
-    <cfRule type="expression" dxfId="40" priority="1">
+    <cfRule type="expression" dxfId="9" priority="8">
       <formula>$K2&gt;=180</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="2">
+    <cfRule type="expression" dxfId="8" priority="9">
       <formula>$K2&gt;=90</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="3">
+    <cfRule type="expression" dxfId="7" priority="10">
       <formula>$K2&lt;90</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F211">
+    <cfRule type="expression" dxfId="6" priority="7">
+      <formula>$F211="ปิดชั่วคราว"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F212">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>$F212="ปิดชั่วคราว"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F232">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>$F232="ปิดชั่วคราว"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F206">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>$F206="ปิดชั่วคราว"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F276">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$F276="ปิดชั่วคราว"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E205 G205">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$F205="ปิดชั่วคราว"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F205">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$F205="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SmartLicense.xlsx
+++ b/SmartLicense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01A7243-39D0-416A-ACFF-ABD1879DA886}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E6BF2C-0286-4F65-9DEF-B4618129367E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2826,7 +2826,7 @@
     <cellStyle name="Percent 2" xfId="19" xr:uid="{52C74F60-A476-4152-873D-B4183CDD4F15}"/>
     <cellStyle name="Style 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="39">
     <dxf>
       <fill>
         <patternFill>
@@ -2928,41 +2928,6 @@
       <font>
         <color theme="0"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -10765,7 +10730,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:XEG297"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="17"/>
   <cols>
@@ -10815,12 +10779,12 @@
       </c>
       <c r="K1" s="54">
         <f ca="1" xml:space="preserve"> EDATE(TODAY(),543*12)</f>
-        <v>244589</v>
+        <v>244594</v>
       </c>
       <c r="M1" s="55"/>
       <c r="N1" s="55"/>
     </row>
-    <row r="2" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="2" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A2" s="7" t="s">
         <v>771</v>
       </c>
@@ -10848,14 +10812,14 @@
       </c>
       <c r="J2" s="56">
         <f ca="1">IFERROR((H2-$K$1),0)</f>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K2" s="56">
         <f ca="1">IF(I2="ยังไม่ได้ทำ BG",-9999,IF(OR(I2="ค้ำเงินสด",I2="ค้ำประกันรายได้",I2="วงเงินรวม SCG"),999,IFERROR((I2-$K$1),0)))</f>
-        <v>641</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="21.75" customHeight="1" thickBot="1">
       <c r="A3" s="7" t="s">
         <v>771</v>
       </c>
@@ -10883,14 +10847,14 @@
       </c>
       <c r="J3" s="56">
         <f t="shared" ref="J3:J66" ca="1" si="0">IFERROR((H3-$K$1),0)</f>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K3" s="56">
         <f t="shared" ref="K3:K66" si="1">IF(I3="ยังไม่ได้ทำ BG",-9999,IF(OR(I3="ค้ำเงินสด",I3="ค้ำประกันรายได้",I3="วงเงินรวม SCG"),999,IFERROR((I3-$K$1),0)))</f>
         <v>999</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="4" spans="1:14" ht="21.75" customHeight="1" thickBot="1">
       <c r="A4" s="7" t="s">
         <v>771</v>
       </c>
@@ -10918,14 +10882,14 @@
       </c>
       <c r="J4" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K4" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="5" spans="1:14" ht="21.75" customHeight="1" thickBot="1">
       <c r="A5" s="7" t="s">
         <v>771</v>
       </c>
@@ -10953,14 +10917,14 @@
       </c>
       <c r="J5" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K5" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="21" hidden="1" customHeight="1" thickBot="1">
+    <row r="6" spans="1:14" ht="21" customHeight="1" thickBot="1">
       <c r="A6" s="7" t="s">
         <v>769</v>
       </c>
@@ -10988,14 +10952,14 @@
       </c>
       <c r="J6" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K6" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A7" s="7" t="s">
         <v>769</v>
       </c>
@@ -11023,14 +10987,14 @@
       </c>
       <c r="J7" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K7" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1" thickBot="1">
       <c r="A8" s="7" t="s">
         <v>769</v>
       </c>
@@ -11058,14 +11022,14 @@
       </c>
       <c r="J8" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K8" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A9" s="7" t="s">
         <v>769</v>
       </c>
@@ -11093,14 +11057,14 @@
       </c>
       <c r="J9" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K9" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A10" s="7" t="s">
         <v>769</v>
       </c>
@@ -11128,14 +11092,14 @@
       </c>
       <c r="J10" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K10" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>702</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="21.75" customHeight="1" thickBot="1">
       <c r="A11" s="7" t="s">
         <v>769</v>
       </c>
@@ -11163,14 +11127,14 @@
       </c>
       <c r="J11" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K11" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>483</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A12" s="7" t="s">
         <v>769</v>
       </c>
@@ -11198,14 +11162,14 @@
       </c>
       <c r="J12" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K12" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="13" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A13" s="7" t="s">
         <v>769</v>
       </c>
@@ -11233,14 +11197,14 @@
       </c>
       <c r="J13" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K13" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>459</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A14" s="7" t="s">
         <v>769</v>
       </c>
@@ -11268,14 +11232,14 @@
       </c>
       <c r="J14" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K14" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>459</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A15" s="7" t="s">
         <v>769</v>
       </c>
@@ -11303,14 +11267,14 @@
       </c>
       <c r="J15" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K15" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>459</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="20.25" customHeight="1" thickBot="1">
       <c r="A16" s="7" t="s">
         <v>769</v>
       </c>
@@ -11338,14 +11302,14 @@
       </c>
       <c r="J16" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K16" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>459</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A17" s="7" t="s">
         <v>769</v>
       </c>
@@ -11373,14 +11337,14 @@
       </c>
       <c r="J17" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K17" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A18" s="7" t="s">
         <v>769</v>
       </c>
@@ -11408,14 +11372,14 @@
       </c>
       <c r="J18" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K18" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A19" s="7" t="s">
         <v>769</v>
       </c>
@@ -11443,14 +11407,14 @@
       </c>
       <c r="J19" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K19" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>946</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A20" s="7" t="s">
         <v>769</v>
       </c>
@@ -11478,14 +11442,14 @@
       </c>
       <c r="J20" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K20" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>430</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A21" s="7" t="s">
         <v>769</v>
       </c>
@@ -11513,14 +11477,14 @@
       </c>
       <c r="J21" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K21" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="22" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A22" s="7" t="s">
         <v>769</v>
       </c>
@@ -11548,14 +11512,14 @@
       </c>
       <c r="J22" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K22" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="23" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A23" s="7" t="s">
         <v>769</v>
       </c>
@@ -11583,14 +11547,14 @@
       </c>
       <c r="J23" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K23" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>288</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A24" s="7" t="s">
         <v>769</v>
       </c>
@@ -11618,14 +11582,14 @@
       </c>
       <c r="J24" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K24" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>288</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A25" s="7" t="s">
         <v>769</v>
       </c>
@@ -11653,14 +11617,14 @@
       </c>
       <c r="J25" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K25" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>288</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A26" s="7" t="s">
         <v>769</v>
       </c>
@@ -11688,14 +11652,14 @@
       </c>
       <c r="J26" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K26" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>944</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A27" s="7" t="s">
         <v>770</v>
       </c>
@@ -11723,14 +11687,14 @@
       </c>
       <c r="J27" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K27" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A28" s="7" t="s">
         <v>770</v>
       </c>
@@ -11758,14 +11722,14 @@
       </c>
       <c r="J28" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A29" s="7" t="s">
         <v>770</v>
       </c>
@@ -11793,14 +11757,14 @@
       </c>
       <c r="J29" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K29" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A30" s="7" t="s">
         <v>770</v>
       </c>
@@ -11828,14 +11792,14 @@
       </c>
       <c r="J30" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K30" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A31" s="7" t="s">
         <v>770</v>
       </c>
@@ -11863,14 +11827,14 @@
       </c>
       <c r="J31" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K31" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A32" s="7" t="s">
         <v>770</v>
       </c>
@@ -11898,14 +11862,14 @@
       </c>
       <c r="J32" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K32" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A33" s="7" t="s">
         <v>770</v>
       </c>
@@ -11933,14 +11897,14 @@
       </c>
       <c r="J33" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K33" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>459</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A34" s="7" t="s">
         <v>770</v>
       </c>
@@ -11968,14 +11932,14 @@
       </c>
       <c r="J34" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K34" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>459</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A35" s="15" t="s">
         <v>770</v>
       </c>
@@ -12003,14 +11967,14 @@
       </c>
       <c r="J35" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K35" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>459</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A36" s="7" t="s">
         <v>770</v>
       </c>
@@ -12038,14 +12002,14 @@
       </c>
       <c r="J36" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K36" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A37" s="7" t="s">
         <v>770</v>
       </c>
@@ -12073,14 +12037,14 @@
       </c>
       <c r="J37" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K37" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A38" s="7" t="s">
         <v>770</v>
       </c>
@@ -12108,14 +12072,14 @@
       </c>
       <c r="J38" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K38" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="39" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A39" s="7" t="s">
         <v>770</v>
       </c>
@@ -12143,14 +12107,14 @@
       </c>
       <c r="J39" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K39" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="40" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A40" s="7" t="s">
         <v>770</v>
       </c>
@@ -12178,14 +12142,14 @@
       </c>
       <c r="J40" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K40" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="41" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A41" s="7" t="s">
         <v>770</v>
       </c>
@@ -12213,14 +12177,14 @@
       </c>
       <c r="J41" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K41" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A42" s="7" t="s">
         <v>770</v>
       </c>
@@ -12248,14 +12212,14 @@
       </c>
       <c r="J42" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K42" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A43" s="15" t="s">
         <v>770</v>
       </c>
@@ -12283,14 +12247,14 @@
       </c>
       <c r="J43" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K43" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="44" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A44" s="15" t="s">
         <v>770</v>
       </c>
@@ -12318,14 +12282,14 @@
       </c>
       <c r="J44" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K44" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="45" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A45" s="7" t="s">
         <v>770</v>
       </c>
@@ -12353,14 +12317,14 @@
       </c>
       <c r="J45" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K45" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A46" s="15" t="s">
         <v>770</v>
       </c>
@@ -12388,14 +12352,14 @@
       </c>
       <c r="J46" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K46" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="47" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A47" s="7" t="s">
         <v>770</v>
       </c>
@@ -12423,14 +12387,14 @@
       </c>
       <c r="J47" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K47" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>518</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A48" s="7" t="s">
         <v>770</v>
       </c>
@@ -12458,14 +12422,14 @@
       </c>
       <c r="J48" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K48" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>518</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A49" s="15" t="s">
         <v>770</v>
       </c>
@@ -12493,14 +12457,14 @@
       </c>
       <c r="J49" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K49" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="50" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A50" s="4" t="s">
         <v>770</v>
       </c>
@@ -12528,14 +12492,14 @@
       </c>
       <c r="J50" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>-244589</v>
+        <v>-244594</v>
       </c>
       <c r="K50" s="56" t="e">
         <f t="shared" si="1"/>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="51" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A51" s="7" t="s">
         <v>770</v>
       </c>
@@ -12563,14 +12527,14 @@
       </c>
       <c r="J51" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K51" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A52" s="7" t="s">
         <v>770</v>
       </c>
@@ -12598,14 +12562,14 @@
       </c>
       <c r="J52" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K52" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A53" s="7" t="s">
         <v>770</v>
       </c>
@@ -12633,14 +12597,14 @@
       </c>
       <c r="J53" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K53" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A54" s="7" t="s">
         <v>770</v>
       </c>
@@ -12668,14 +12632,14 @@
       </c>
       <c r="J54" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K54" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A55" s="7" t="s">
         <v>770</v>
       </c>
@@ -12703,14 +12667,14 @@
       </c>
       <c r="J55" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="K55" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A56" s="7" t="s">
         <v>770</v>
       </c>
@@ -12738,14 +12702,14 @@
       </c>
       <c r="J56" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K56" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>944</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A57" s="7" t="s">
         <v>770</v>
       </c>
@@ -12773,14 +12737,14 @@
       </c>
       <c r="J57" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K57" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1202</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A58" s="7" t="s">
         <v>770</v>
       </c>
@@ -12808,14 +12772,14 @@
       </c>
       <c r="J58" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="K58" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="59" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A59" s="7" t="s">
         <v>770</v>
       </c>
@@ -12843,14 +12807,14 @@
       </c>
       <c r="J59" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K59" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A60" s="7" t="s">
         <v>770</v>
       </c>
@@ -12878,14 +12842,14 @@
       </c>
       <c r="J60" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K60" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>319</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A61" s="7" t="s">
         <v>770</v>
       </c>
@@ -12913,14 +12877,14 @@
       </c>
       <c r="J61" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K61" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>894</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A62" s="7" t="s">
         <v>770</v>
       </c>
@@ -12948,14 +12912,14 @@
       </c>
       <c r="J62" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K62" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>317</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A63" s="7" t="s">
         <v>770</v>
       </c>
@@ -12983,14 +12947,14 @@
       </c>
       <c r="J63" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K63" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>190</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A64" s="7" t="s">
         <v>770</v>
       </c>
@@ -13018,14 +12982,14 @@
       </c>
       <c r="J64" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K64" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A65" s="15" t="s">
         <v>770</v>
       </c>
@@ -13053,14 +13017,14 @@
       </c>
       <c r="J65" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K65" s="56">
         <f t="shared" ca="1" si="1"/>
-        <v>568</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A66" s="7" t="s">
         <v>770</v>
       </c>
@@ -13088,14 +13052,14 @@
       </c>
       <c r="J66" s="56">
         <f t="shared" ca="1" si="0"/>
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="K66" s="56">
         <f t="shared" si="1"/>
         <v>999</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="67" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A67" s="15" t="s">
         <v>770</v>
       </c>
@@ -13123,14 +13087,14 @@
       </c>
       <c r="J67" s="56">
         <f t="shared" ref="J67:J130" ca="1" si="2">IFERROR((H67-$K$1),0)</f>
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="K67" s="56">
         <f t="shared" ref="K67:K130" si="3">IF(I67="ยังไม่ได้ทำ BG",-9999,IF(OR(I67="ค้ำเงินสด",I67="ค้ำประกันรายได้",I67="วงเงินรวม SCG"),999,IFERROR((I67-$K$1),0)))</f>
         <v>999</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="68" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A68" s="7" t="s">
         <v>766</v>
       </c>
@@ -13158,14 +13122,14 @@
       </c>
       <c r="J68" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K68" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A69" s="7" t="s">
         <v>766</v>
       </c>
@@ -13193,14 +13157,14 @@
       </c>
       <c r="J69" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K69" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A70" s="7" t="s">
         <v>766</v>
       </c>
@@ -13228,14 +13192,14 @@
       </c>
       <c r="J70" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K70" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A71" s="7" t="s">
         <v>766</v>
       </c>
@@ -13263,14 +13227,14 @@
       </c>
       <c r="J71" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K71" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>399</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A72" s="7" t="s">
         <v>766</v>
       </c>
@@ -13300,14 +13264,14 @@
       </c>
       <c r="J72" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-332</v>
+        <v>-337</v>
       </c>
       <c r="K72" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>399</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A73" s="7" t="s">
         <v>766</v>
       </c>
@@ -13335,14 +13299,14 @@
       </c>
       <c r="J73" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-332</v>
+        <v>-337</v>
       </c>
       <c r="K73" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>946</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A74" s="7" t="s">
         <v>766</v>
       </c>
@@ -13370,14 +13334,14 @@
       </c>
       <c r="J74" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K74" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A75" s="7" t="s">
         <v>766</v>
       </c>
@@ -13405,14 +13369,14 @@
       </c>
       <c r="J75" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K75" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A76" s="7" t="s">
         <v>766</v>
       </c>
@@ -13440,14 +13404,14 @@
       </c>
       <c r="J76" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K76" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A77" s="7" t="s">
         <v>766</v>
       </c>
@@ -13475,14 +13439,14 @@
       </c>
       <c r="J77" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K77" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="78" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A78" s="7" t="s">
         <v>766</v>
       </c>
@@ -13510,14 +13474,14 @@
       </c>
       <c r="J78" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K78" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="79" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A79" s="48" t="s">
         <v>766</v>
       </c>
@@ -13547,14 +13511,14 @@
       </c>
       <c r="J79" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-2159</v>
+        <v>-2164</v>
       </c>
       <c r="K79" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="80" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A80" s="48" t="s">
         <v>766</v>
       </c>
@@ -13584,14 +13548,14 @@
       </c>
       <c r="J80" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-2159</v>
+        <v>-2164</v>
       </c>
       <c r="K80" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="81" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A81" s="7" t="s">
         <v>766</v>
       </c>
@@ -13619,14 +13583,14 @@
       </c>
       <c r="J81" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K81" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="82" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A82" s="15" t="s">
         <v>766</v>
       </c>
@@ -13654,14 +13618,14 @@
       </c>
       <c r="J82" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K82" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>125</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A83" s="7" t="s">
         <v>766</v>
       </c>
@@ -13689,14 +13653,14 @@
       </c>
       <c r="J83" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K83" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>946</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A84" s="7" t="s">
         <v>766</v>
       </c>
@@ -13724,14 +13688,14 @@
       </c>
       <c r="J84" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K84" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A85" s="7" t="s">
         <v>766</v>
       </c>
@@ -13759,14 +13723,14 @@
       </c>
       <c r="J85" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K85" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A86" s="7" t="s">
         <v>766</v>
       </c>
@@ -13794,14 +13758,14 @@
       </c>
       <c r="J86" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K86" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="87" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A87" s="7" t="s">
         <v>766</v>
       </c>
@@ -13829,14 +13793,14 @@
       </c>
       <c r="J87" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K87" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A88" s="7" t="s">
         <v>766</v>
       </c>
@@ -13864,14 +13828,14 @@
       </c>
       <c r="J88" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K88" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A89" s="7" t="s">
         <v>766</v>
       </c>
@@ -13899,14 +13863,14 @@
       </c>
       <c r="J89" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K89" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>728</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A90" s="7" t="s">
         <v>766</v>
       </c>
@@ -13934,14 +13898,14 @@
       </c>
       <c r="J90" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K90" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>728</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A91" s="24" t="s">
         <v>766</v>
       </c>
@@ -13971,14 +13935,14 @@
       </c>
       <c r="J91" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K91" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A92" s="7" t="s">
         <v>766</v>
       </c>
@@ -14006,14 +13970,14 @@
       </c>
       <c r="J92" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K92" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A93" s="7" t="s">
         <v>766</v>
       </c>
@@ -14041,14 +14005,14 @@
       </c>
       <c r="J93" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K93" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A94" s="7" t="s">
         <v>766</v>
       </c>
@@ -14074,14 +14038,14 @@
       </c>
       <c r="J94" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-244589</v>
+        <v>-244594</v>
       </c>
       <c r="K94" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A95" s="7" t="s">
         <v>766</v>
       </c>
@@ -14109,14 +14073,14 @@
       </c>
       <c r="J95" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K95" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A96" s="7" t="s">
         <v>766</v>
       </c>
@@ -14144,14 +14108,14 @@
       </c>
       <c r="J96" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K96" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A97" s="7" t="s">
         <v>766</v>
       </c>
@@ -14179,14 +14143,14 @@
       </c>
       <c r="J97" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K97" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A98" s="7" t="s">
         <v>766</v>
       </c>
@@ -14214,14 +14178,14 @@
       </c>
       <c r="J98" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K98" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>946</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A99" s="7" t="s">
         <v>766</v>
       </c>
@@ -14249,14 +14213,14 @@
       </c>
       <c r="J99" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K99" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A100" s="7" t="s">
         <v>766</v>
       </c>
@@ -14284,14 +14248,14 @@
       </c>
       <c r="J100" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K100" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>549</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A101" s="7" t="s">
         <v>766</v>
       </c>
@@ -14319,14 +14283,14 @@
       </c>
       <c r="J101" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="K101" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A102" s="7" t="s">
         <v>766</v>
       </c>
@@ -14354,14 +14318,14 @@
       </c>
       <c r="J102" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K102" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A103" s="7" t="s">
         <v>766</v>
       </c>
@@ -14389,14 +14353,14 @@
       </c>
       <c r="J103" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K103" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>141</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A104" s="7" t="s">
         <v>766</v>
       </c>
@@ -14424,14 +14388,14 @@
       </c>
       <c r="J104" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K104" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>141</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A105" s="48" t="s">
         <v>766</v>
       </c>
@@ -14461,14 +14425,14 @@
       </c>
       <c r="J105" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>-3124</v>
+        <v>-3129</v>
       </c>
       <c r="K105" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="106" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A106" s="7" t="s">
         <v>766</v>
       </c>
@@ -14496,14 +14460,14 @@
       </c>
       <c r="J106" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K106" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A107" s="7" t="s">
         <v>766</v>
       </c>
@@ -14531,14 +14495,14 @@
       </c>
       <c r="J107" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="K107" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A108" s="7" t="s">
         <v>766</v>
       </c>
@@ -14566,14 +14530,14 @@
       </c>
       <c r="J108" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K108" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="109" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A109" s="7" t="s">
         <v>767</v>
       </c>
@@ -14601,14 +14565,14 @@
       </c>
       <c r="J109" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K109" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A110" s="7" t="s">
         <v>767</v>
       </c>
@@ -14636,14 +14600,14 @@
       </c>
       <c r="J110" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K110" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A111" s="7" t="s">
         <v>767</v>
       </c>
@@ -14671,14 +14635,14 @@
       </c>
       <c r="J111" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K111" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="112" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A112" s="7" t="s">
         <v>767</v>
       </c>
@@ -14706,14 +14670,14 @@
       </c>
       <c r="J112" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K112" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A113" s="7" t="s">
         <v>767</v>
       </c>
@@ -14741,14 +14705,14 @@
       </c>
       <c r="J113" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K113" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A114" s="7" t="s">
         <v>767</v>
       </c>
@@ -14776,14 +14740,14 @@
       </c>
       <c r="J114" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K114" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A115" s="7" t="s">
         <v>767</v>
       </c>
@@ -14811,14 +14775,14 @@
       </c>
       <c r="J115" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K115" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A116" s="7" t="s">
         <v>767</v>
       </c>
@@ -14846,14 +14810,14 @@
       </c>
       <c r="J116" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K116" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>777</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A117" s="29" t="s">
         <v>767</v>
       </c>
@@ -14883,14 +14847,14 @@
       </c>
       <c r="J117" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K117" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="118" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A118" s="15" t="s">
         <v>767</v>
       </c>
@@ -14918,14 +14882,14 @@
       </c>
       <c r="J118" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K118" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A119" s="7" t="s">
         <v>767</v>
       </c>
@@ -14953,14 +14917,14 @@
       </c>
       <c r="J119" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K119" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A120" s="7" t="s">
         <v>767</v>
       </c>
@@ -14988,14 +14952,14 @@
       </c>
       <c r="J120" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K120" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A121" s="7" t="s">
         <v>767</v>
       </c>
@@ -15023,14 +14987,14 @@
       </c>
       <c r="J121" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K121" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A122" s="7" t="s">
         <v>767</v>
       </c>
@@ -15058,14 +15022,14 @@
       </c>
       <c r="J122" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K122" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="123" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A123" s="7" t="s">
         <v>767</v>
       </c>
@@ -15093,14 +15057,14 @@
       </c>
       <c r="J123" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K123" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="124" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A124" s="7" t="s">
         <v>767</v>
       </c>
@@ -15128,14 +15092,14 @@
       </c>
       <c r="J124" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K124" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A125" s="7" t="s">
         <v>767</v>
       </c>
@@ -15163,14 +15127,14 @@
       </c>
       <c r="J125" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K125" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="126" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A126" s="7" t="s">
         <v>767</v>
       </c>
@@ -15198,14 +15162,14 @@
       </c>
       <c r="J126" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K126" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="127" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A127" s="15" t="s">
         <v>767</v>
       </c>
@@ -15233,14 +15197,14 @@
       </c>
       <c r="J127" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K127" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="128" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A128" s="15" t="s">
         <v>767</v>
       </c>
@@ -15268,14 +15232,14 @@
       </c>
       <c r="J128" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K128" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="129" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A129" s="15" t="s">
         <v>767</v>
       </c>
@@ -15303,14 +15267,14 @@
       </c>
       <c r="J129" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K129" s="56">
         <f t="shared" ca="1" si="3"/>
-        <v>549</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A130" s="15" t="s">
         <v>767</v>
       </c>
@@ -15338,14 +15302,14 @@
       </c>
       <c r="J130" s="56">
         <f t="shared" ca="1" si="2"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K130" s="56">
         <f t="shared" si="3"/>
         <v>999</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="131" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A131" s="15" t="s">
         <v>767</v>
       </c>
@@ -15373,14 +15337,14 @@
       </c>
       <c r="J131" s="56">
         <f t="shared" ref="J131:J194" ca="1" si="4">IFERROR((H131-$K$1),0)</f>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K131" s="56">
         <f t="shared" ref="K131:K194" si="5">IF(I131="ยังไม่ได้ทำ BG",-9999,IF(OR(I131="ค้ำเงินสด",I131="ค้ำประกันรายได้",I131="วงเงินรวม SCG"),999,IFERROR((I131-$K$1),0)))</f>
         <v>999</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="132" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A132" s="15" t="s">
         <v>767</v>
       </c>
@@ -15415,7 +15379,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="133" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A133" s="15" t="s">
         <v>767</v>
       </c>
@@ -15443,14 +15407,14 @@
       </c>
       <c r="J133" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K133" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="134" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A134" s="15" t="s">
         <v>767</v>
       </c>
@@ -15478,14 +15442,14 @@
       </c>
       <c r="J134" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K134" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="135" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A135" s="15" t="s">
         <v>767</v>
       </c>
@@ -15513,14 +15477,14 @@
       </c>
       <c r="J135" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K135" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="136" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A136" s="15" t="s">
         <v>767</v>
       </c>
@@ -15548,14 +15512,14 @@
       </c>
       <c r="J136" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K136" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="137" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A137" s="7" t="s">
         <v>767</v>
       </c>
@@ -15583,14 +15547,14 @@
       </c>
       <c r="J137" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K137" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A138" s="7" t="s">
         <v>767</v>
       </c>
@@ -15622,10 +15586,10 @@
       </c>
       <c r="K138" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A139" s="7" t="s">
         <v>767</v>
       </c>
@@ -15653,14 +15617,14 @@
       </c>
       <c r="J139" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K139" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A140" s="7" t="s">
         <v>767</v>
       </c>
@@ -15692,10 +15656,10 @@
       </c>
       <c r="K140" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>581</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A141" s="7" t="s">
         <v>767</v>
       </c>
@@ -15723,14 +15687,14 @@
       </c>
       <c r="J141" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K141" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A142" s="7" t="s">
         <v>767</v>
       </c>
@@ -15758,14 +15722,14 @@
       </c>
       <c r="J142" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K142" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>440</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A143" s="7" t="s">
         <v>767</v>
       </c>
@@ -15793,14 +15757,14 @@
       </c>
       <c r="J143" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K143" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="144" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A144" s="15" t="s">
         <v>767</v>
       </c>
@@ -15828,14 +15792,14 @@
       </c>
       <c r="J144" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K144" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A145" s="15" t="s">
         <v>767</v>
       </c>
@@ -15863,14 +15827,14 @@
       </c>
       <c r="J145" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K145" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="146" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A146" s="15" t="s">
         <v>767</v>
       </c>
@@ -15898,14 +15862,14 @@
       </c>
       <c r="J146" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K146" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="147" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A147" s="7" t="s">
         <v>767</v>
       </c>
@@ -15933,14 +15897,14 @@
       </c>
       <c r="J147" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K147" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="148" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A148" s="7" t="s">
         <v>767</v>
       </c>
@@ -15968,14 +15932,14 @@
       </c>
       <c r="J148" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K148" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="149" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A149" s="7" t="s">
         <v>767</v>
       </c>
@@ -16003,14 +15967,14 @@
       </c>
       <c r="J149" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K149" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="150" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A150" s="7" t="s">
         <v>767</v>
       </c>
@@ -16040,14 +16004,14 @@
       </c>
       <c r="J150" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K150" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="151" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A151" s="7" t="s">
         <v>767</v>
       </c>
@@ -16075,14 +16039,14 @@
       </c>
       <c r="J151" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K151" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="152" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A152" s="7" t="s">
         <v>767</v>
       </c>
@@ -16110,14 +16074,14 @@
       </c>
       <c r="J152" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K152" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>327</v>
-      </c>
-    </row>
-    <row r="153" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A153" s="7" t="s">
         <v>767</v>
       </c>
@@ -16145,14 +16109,14 @@
       </c>
       <c r="J153" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K153" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="154" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A154" s="7" t="s">
         <v>767</v>
       </c>
@@ -16180,14 +16144,14 @@
       </c>
       <c r="J154" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K154" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>763</v>
-      </c>
-    </row>
-    <row r="155" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A155" s="7" t="s">
         <v>767</v>
       </c>
@@ -16215,14 +16179,14 @@
       </c>
       <c r="J155" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K155" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="156" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A156" s="7" t="s">
         <v>767</v>
       </c>
@@ -16250,14 +16214,14 @@
       </c>
       <c r="J156" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K156" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="157" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A157" s="7" t="s">
         <v>767</v>
       </c>
@@ -16285,14 +16249,14 @@
       </c>
       <c r="J157" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K157" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A158" s="7" t="s">
         <v>767</v>
       </c>
@@ -16320,14 +16284,14 @@
       </c>
       <c r="J158" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K158" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>83</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A159" s="7" t="s">
         <v>767</v>
       </c>
@@ -16355,14 +16319,14 @@
       </c>
       <c r="J159" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K159" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="160" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A160" s="7" t="s">
         <v>767</v>
       </c>
@@ -16390,14 +16354,14 @@
       </c>
       <c r="J160" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K160" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="161" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A161" s="7" t="s">
         <v>767</v>
       </c>
@@ -16425,14 +16389,14 @@
       </c>
       <c r="J161" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K161" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="162" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A162" s="7" t="s">
         <v>767</v>
       </c>
@@ -16460,14 +16424,14 @@
       </c>
       <c r="J162" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K162" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="163" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A163" s="7" t="s">
         <v>767</v>
       </c>
@@ -16495,14 +16459,14 @@
       </c>
       <c r="J163" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K163" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A164" s="7" t="s">
         <v>767</v>
       </c>
@@ -16530,14 +16494,14 @@
       </c>
       <c r="J164" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K164" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="165" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A165" s="7" t="s">
         <v>767</v>
       </c>
@@ -16565,14 +16529,14 @@
       </c>
       <c r="J165" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="K165" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="166" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A166" s="7" t="s">
         <v>767</v>
       </c>
@@ -16600,14 +16564,14 @@
       </c>
       <c r="J166" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K166" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>398</v>
-      </c>
-    </row>
-    <row r="167" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A167" s="7" t="s">
         <v>767</v>
       </c>
@@ -16635,14 +16599,14 @@
       </c>
       <c r="J167" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K167" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="168" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A168" s="24" t="s">
         <v>767</v>
       </c>
@@ -16672,14 +16636,14 @@
       </c>
       <c r="J168" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K168" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="169" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A169" s="7" t="s">
         <v>767</v>
       </c>
@@ -16707,14 +16671,14 @@
       </c>
       <c r="J169" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K169" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="170" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A170" s="7" t="s">
         <v>767</v>
       </c>
@@ -16742,14 +16706,14 @@
       </c>
       <c r="J170" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K170" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>454</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A171" s="7" t="s">
         <v>767</v>
       </c>
@@ -16777,14 +16741,14 @@
       </c>
       <c r="J171" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K171" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="172" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A172" s="7" t="s">
         <v>767</v>
       </c>
@@ -16812,14 +16776,14 @@
       </c>
       <c r="J172" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K172" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="173" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A173" s="7" t="s">
         <v>767</v>
       </c>
@@ -16847,14 +16811,14 @@
       </c>
       <c r="J173" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K173" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="174" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A174" s="7" t="s">
         <v>767</v>
       </c>
@@ -16882,14 +16846,14 @@
       </c>
       <c r="J174" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K174" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="175" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A175" s="7" t="s">
         <v>767</v>
       </c>
@@ -16917,14 +16881,14 @@
       </c>
       <c r="J175" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K175" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="176" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A176" s="7" t="s">
         <v>767</v>
       </c>
@@ -16952,14 +16916,14 @@
       </c>
       <c r="J176" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K176" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A177" s="7" t="s">
         <v>767</v>
       </c>
@@ -16987,14 +16951,14 @@
       </c>
       <c r="J177" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K177" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>580</v>
-      </c>
-    </row>
-    <row r="178" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A178" s="7" t="s">
         <v>767</v>
       </c>
@@ -17022,14 +16986,14 @@
       </c>
       <c r="J178" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K178" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="179" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A179" s="7" t="s">
         <v>767</v>
       </c>
@@ -17057,14 +17021,14 @@
       </c>
       <c r="J179" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K179" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="180" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A180" s="7" t="s">
         <v>767</v>
       </c>
@@ -17092,14 +17056,14 @@
       </c>
       <c r="J180" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="K180" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="181" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A181" s="15" t="s">
         <v>767</v>
       </c>
@@ -17127,14 +17091,14 @@
       </c>
       <c r="J181" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="K181" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="182" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A182" s="15" t="s">
         <v>768</v>
       </c>
@@ -17162,14 +17126,14 @@
       </c>
       <c r="J182" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K182" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="183" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A183" s="15" t="s">
         <v>768</v>
       </c>
@@ -17197,14 +17161,14 @@
       </c>
       <c r="J183" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K183" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="184" spans="1:11" s="2" customFormat="1" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="184" spans="1:11" s="2" customFormat="1" ht="20.25" customHeight="1" thickBot="1">
       <c r="A184" s="15" t="s">
         <v>768</v>
       </c>
@@ -17232,14 +17196,14 @@
       </c>
       <c r="J184" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K184" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="185" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A185" s="15" t="s">
         <v>768</v>
       </c>
@@ -17267,14 +17231,14 @@
       </c>
       <c r="J185" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K185" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="186" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A186" s="15" t="s">
         <v>768</v>
       </c>
@@ -17302,14 +17266,14 @@
       </c>
       <c r="J186" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K186" s="56">
         <f t="shared" ca="1" si="5"/>
-        <v>716</v>
-      </c>
-    </row>
-    <row r="187" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A187" s="15" t="s">
         <v>768</v>
       </c>
@@ -17337,14 +17301,14 @@
       </c>
       <c r="J187" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K187" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="188" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A188" s="7" t="s">
         <v>768</v>
       </c>
@@ -17372,14 +17336,14 @@
       </c>
       <c r="J188" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-59</v>
+        <v>-64</v>
       </c>
       <c r="K188" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="189" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+    <row r="189" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A189" s="15" t="s">
         <v>768</v>
       </c>
@@ -17409,14 +17373,14 @@
       </c>
       <c r="J189" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1155</v>
+        <v>-1160</v>
       </c>
       <c r="K189" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="190" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+    <row r="190" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A190" s="15" t="s">
         <v>768</v>
       </c>
@@ -17446,14 +17410,14 @@
       </c>
       <c r="J190" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1155</v>
+        <v>-1160</v>
       </c>
       <c r="K190" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="191" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A191" s="15" t="s">
         <v>768</v>
       </c>
@@ -17483,14 +17447,14 @@
       </c>
       <c r="J191" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-790</v>
+        <v>-795</v>
       </c>
       <c r="K191" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="192" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A192" s="15" t="s">
         <v>768</v>
       </c>
@@ -17520,14 +17484,14 @@
       </c>
       <c r="J192" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1155</v>
+        <v>-1160</v>
       </c>
       <c r="K192" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="193" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="193" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A193" s="15" t="s">
         <v>768</v>
       </c>
@@ -17557,14 +17521,14 @@
       </c>
       <c r="J193" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1155</v>
+        <v>-1160</v>
       </c>
       <c r="K193" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="194" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="194" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A194" s="15" t="s">
         <v>768</v>
       </c>
@@ -17594,14 +17558,14 @@
       </c>
       <c r="J194" s="56">
         <f t="shared" ca="1" si="4"/>
-        <v>-1155</v>
+        <v>-1160</v>
       </c>
       <c r="K194" s="56">
         <f t="shared" si="5"/>
         <v>999</v>
       </c>
     </row>
-    <row r="195" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="195" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A195" s="15" t="s">
         <v>768</v>
       </c>
@@ -17629,14 +17593,14 @@
       </c>
       <c r="J195" s="56">
         <f t="shared" ref="J195:J258" ca="1" si="6">IFERROR((H195-$K$1),0)</f>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K195" s="56">
         <f t="shared" ref="K195:K258" ca="1" si="7">IF(I195="ยังไม่ได้ทำ BG",-9999,IF(OR(I195="ค้ำเงินสด",I195="ค้ำประกันรายได้",I195="วงเงินรวม SCG"),999,IFERROR((I195-$K$1),0)))</f>
-        <v>668</v>
-      </c>
-    </row>
-    <row r="196" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A196" s="15" t="s">
         <v>768</v>
       </c>
@@ -17664,14 +17628,14 @@
       </c>
       <c r="J196" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K196" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>668</v>
-      </c>
-    </row>
-    <row r="197" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A197" s="15" t="s">
         <v>768</v>
       </c>
@@ -17701,14 +17665,14 @@
       </c>
       <c r="J197" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K197" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="198" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A198" s="15" t="s">
         <v>768</v>
       </c>
@@ -17736,14 +17700,14 @@
       </c>
       <c r="J198" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K198" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>49</v>
-      </c>
-    </row>
-    <row r="199" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A199" s="15" t="s">
         <v>768</v>
       </c>
@@ -17771,14 +17735,14 @@
       </c>
       <c r="J199" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K199" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="200" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A200" s="15" t="s">
         <v>768</v>
       </c>
@@ -17806,14 +17770,14 @@
       </c>
       <c r="J200" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K200" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="201" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A201" s="15" t="s">
         <v>768</v>
       </c>
@@ -17841,14 +17805,14 @@
       </c>
       <c r="J201" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-244589</v>
+        <v>-244594</v>
       </c>
       <c r="K201" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>245</v>
-      </c>
-    </row>
-    <row r="202" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A202" s="15" t="s">
         <v>768</v>
       </c>
@@ -17876,14 +17840,14 @@
       </c>
       <c r="J202" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K202" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>38</v>
-      </c>
-    </row>
-    <row r="203" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A203" s="15" t="s">
         <v>768</v>
       </c>
@@ -17913,14 +17877,14 @@
       </c>
       <c r="J203" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-1885</v>
+        <v>-1890</v>
       </c>
       <c r="K203" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>245</v>
-      </c>
-    </row>
-    <row r="204" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A204" s="15" t="s">
         <v>768</v>
       </c>
@@ -17948,14 +17912,14 @@
       </c>
       <c r="J204" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K204" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>245</v>
-      </c>
-    </row>
-    <row r="205" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A205" s="41" t="s">
         <v>768</v>
       </c>
@@ -17985,14 +17949,14 @@
       </c>
       <c r="J205" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K205" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1129</v>
-      </c>
-    </row>
-    <row r="206" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A206" s="41" t="s">
         <v>768</v>
       </c>
@@ -18022,14 +17986,14 @@
       </c>
       <c r="J206" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K206" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>154</v>
-      </c>
-    </row>
-    <row r="207" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A207" s="15" t="s">
         <v>768</v>
       </c>
@@ -18057,14 +18021,14 @@
       </c>
       <c r="J207" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K207" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="208" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A208" s="15" t="s">
         <v>768</v>
       </c>
@@ -18092,14 +18056,14 @@
       </c>
       <c r="J208" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K208" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="209" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="209" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A209" s="15" t="s">
         <v>768</v>
       </c>
@@ -18129,14 +18093,14 @@
       </c>
       <c r="J209" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-790</v>
+        <v>-795</v>
       </c>
       <c r="K209" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="210" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A210" s="15" t="s">
         <v>768</v>
       </c>
@@ -18164,14 +18128,14 @@
       </c>
       <c r="J210" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K210" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="211" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="211" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A211" s="41" t="s">
         <v>768</v>
       </c>
@@ -18201,14 +18165,14 @@
       </c>
       <c r="J211" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K211" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="212" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="212" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A212" s="41" t="s">
         <v>768</v>
       </c>
@@ -18238,14 +18202,14 @@
       </c>
       <c r="J212" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K212" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="213" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="213" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A213" s="41" t="s">
         <v>768</v>
       </c>
@@ -18275,14 +18239,14 @@
       </c>
       <c r="J213" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-1520</v>
+        <v>-1525</v>
       </c>
       <c r="K213" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="214" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="214" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A214" s="15" t="s">
         <v>768</v>
       </c>
@@ -18310,14 +18274,14 @@
       </c>
       <c r="J214" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K214" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>316</v>
-      </c>
-    </row>
-    <row r="215" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A215" s="15" t="s">
         <v>768</v>
       </c>
@@ -18345,14 +18309,14 @@
       </c>
       <c r="J215" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K215" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>985</v>
-      </c>
-    </row>
-    <row r="216" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A216" s="15" t="s">
         <v>768</v>
       </c>
@@ -18380,14 +18344,14 @@
       </c>
       <c r="J216" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K216" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="217" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A217" s="15" t="s">
         <v>768</v>
       </c>
@@ -18415,14 +18379,14 @@
       </c>
       <c r="J217" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K217" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="218" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A218" s="15" t="s">
         <v>768</v>
       </c>
@@ -18450,14 +18414,14 @@
       </c>
       <c r="J218" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K218" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1180</v>
-      </c>
-    </row>
-    <row r="219" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A219" s="15" t="s">
         <v>768</v>
       </c>
@@ -18485,14 +18449,14 @@
       </c>
       <c r="J219" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K219" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>827</v>
-      </c>
-    </row>
-    <row r="220" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A220" s="15" t="s">
         <v>768</v>
       </c>
@@ -18520,14 +18484,14 @@
       </c>
       <c r="J220" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K220" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>703</v>
-      </c>
-    </row>
-    <row r="221" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A221" s="15" t="s">
         <v>768</v>
       </c>
@@ -18555,14 +18519,14 @@
       </c>
       <c r="J221" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K221" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="222" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A222" s="15" t="s">
         <v>768</v>
       </c>
@@ -18590,14 +18554,14 @@
       </c>
       <c r="J222" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K222" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="223" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A223" s="15" t="s">
         <v>768</v>
       </c>
@@ -18625,14 +18589,14 @@
       </c>
       <c r="J223" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K223" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="224" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="224" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A224" s="15" t="s">
         <v>768</v>
       </c>
@@ -18660,14 +18624,14 @@
       </c>
       <c r="J224" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K224" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="225" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A225" s="15" t="s">
         <v>768</v>
       </c>
@@ -18695,14 +18659,14 @@
       </c>
       <c r="J225" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K225" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="226" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="226" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A226" s="15" t="s">
         <v>768</v>
       </c>
@@ -18730,14 +18694,14 @@
       </c>
       <c r="J226" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K226" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="227" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+    <row r="227" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A227" s="15" t="s">
         <v>768</v>
       </c>
@@ -18765,7 +18729,7 @@
       </c>
       <c r="J227" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K227" s="56">
         <f t="shared" si="7"/>
@@ -18789,7 +18753,7 @@
         <v>774</v>
       </c>
       <c r="F228" s="9">
-        <v>244590</v>
+        <v>244895</v>
       </c>
       <c r="G228" s="11"/>
       <c r="H228" s="57">
@@ -18800,11 +18764,11 @@
       </c>
       <c r="J228" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K228" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="229" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
@@ -18823,8 +18787,8 @@
       <c r="E229" s="7" t="s">
         <v>774</v>
       </c>
-      <c r="F229" s="22">
-        <v>244590</v>
+      <c r="F229" s="9">
+        <v>244895</v>
       </c>
       <c r="G229" s="39"/>
       <c r="H229" s="57">
@@ -18835,14 +18799,14 @@
       </c>
       <c r="J229" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K229" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="230" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A230" s="15" t="s">
         <v>768</v>
       </c>
@@ -18870,14 +18834,14 @@
       </c>
       <c r="J230" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K230" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="231" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="231" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A231" s="15" t="s">
         <v>768</v>
       </c>
@@ -18907,14 +18871,14 @@
       </c>
       <c r="J231" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>-59</v>
+        <v>-64</v>
       </c>
       <c r="K231" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="232" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A232" s="41" t="s">
         <v>768</v>
       </c>
@@ -18944,14 +18908,14 @@
       </c>
       <c r="J232" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K232" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>701</v>
-      </c>
-    </row>
-    <row r="233" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A233" s="15" t="s">
         <v>768</v>
       </c>
@@ -18979,14 +18943,14 @@
       </c>
       <c r="J233" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K233" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="234" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="234" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A234" s="15" t="s">
         <v>768</v>
       </c>
@@ -19014,14 +18978,14 @@
       </c>
       <c r="J234" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K234" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="235" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A235" s="15" t="s">
         <v>768</v>
       </c>
@@ -19049,14 +19013,14 @@
       </c>
       <c r="J235" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K235" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="236" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A236" s="41" t="s">
         <v>768</v>
       </c>
@@ -19086,14 +19050,14 @@
       </c>
       <c r="J236" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K236" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="237" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A237" s="15" t="s">
         <v>768</v>
       </c>
@@ -19121,14 +19085,14 @@
       </c>
       <c r="J237" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K237" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>671</v>
-      </c>
-    </row>
-    <row r="238" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A238" s="15" t="s">
         <v>768</v>
       </c>
@@ -19156,14 +19120,14 @@
       </c>
       <c r="J238" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K238" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="239" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A239" s="15" t="s">
         <v>768</v>
       </c>
@@ -19191,14 +19155,14 @@
       </c>
       <c r="J239" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K239" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>48</v>
-      </c>
-    </row>
-    <row r="240" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A240" s="15" t="s">
         <v>768</v>
       </c>
@@ -19226,14 +19190,14 @@
       </c>
       <c r="J240" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K240" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>33</v>
-      </c>
-    </row>
-    <row r="241" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A241" s="15" t="s">
         <v>768</v>
       </c>
@@ -19261,14 +19225,14 @@
       </c>
       <c r="J241" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K241" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>512</v>
-      </c>
-    </row>
-    <row r="242" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A242" s="15" t="s">
         <v>768</v>
       </c>
@@ -19296,14 +19260,14 @@
       </c>
       <c r="J242" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K242" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>512</v>
-      </c>
-    </row>
-    <row r="243" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A243" s="41" t="s">
         <v>768</v>
       </c>
@@ -19333,14 +19297,14 @@
       </c>
       <c r="J243" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K243" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="244" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A244" s="41" t="s">
         <v>768</v>
       </c>
@@ -19370,14 +19334,14 @@
       </c>
       <c r="J244" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K244" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="245" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A245" s="15" t="s">
         <v>768</v>
       </c>
@@ -19405,14 +19369,14 @@
       </c>
       <c r="J245" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K245" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>796</v>
-      </c>
-    </row>
-    <row r="246" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A246" s="15" t="s">
         <v>768</v>
       </c>
@@ -19440,14 +19404,14 @@
       </c>
       <c r="J246" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K246" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>264</v>
-      </c>
-    </row>
-    <row r="247" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A247" s="15" t="s">
         <v>768</v>
       </c>
@@ -19475,14 +19439,14 @@
       </c>
       <c r="J247" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K247" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>671</v>
-      </c>
-    </row>
-    <row r="248" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A248" s="41" t="s">
         <v>768</v>
       </c>
@@ -19512,14 +19476,14 @@
       </c>
       <c r="J248" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K248" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="249" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A249" s="15" t="s">
         <v>768</v>
       </c>
@@ -19547,14 +19511,14 @@
       </c>
       <c r="J249" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K249" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>350</v>
-      </c>
-    </row>
-    <row r="250" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A250" s="15" t="s">
         <v>768</v>
       </c>
@@ -19582,14 +19546,14 @@
       </c>
       <c r="J250" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K250" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="251" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="251" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A251" s="15" t="s">
         <v>768</v>
       </c>
@@ -19617,14 +19581,14 @@
       </c>
       <c r="J251" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K251" s="56">
         <f t="shared" si="7"/>
         <v>999</v>
       </c>
     </row>
-    <row r="252" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+    <row r="252" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A252" s="15" t="s">
         <v>768</v>
       </c>
@@ -19652,14 +19616,14 @@
       </c>
       <c r="J252" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K252" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="253" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A253" s="15" t="s">
         <v>768</v>
       </c>
@@ -19687,14 +19651,14 @@
       </c>
       <c r="J253" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K253" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="254" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A254" s="15" t="s">
         <v>768</v>
       </c>
@@ -19722,14 +19686,14 @@
       </c>
       <c r="J254" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K254" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="255" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A255" s="15" t="s">
         <v>768</v>
       </c>
@@ -19757,14 +19721,14 @@
       </c>
       <c r="J255" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K255" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="256" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A256" s="15" t="s">
         <v>768</v>
       </c>
@@ -19792,14 +19756,14 @@
       </c>
       <c r="J256" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K256" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>306</v>
-      </c>
-    </row>
-    <row r="257" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A257" s="15" t="s">
         <v>768</v>
       </c>
@@ -19827,14 +19791,14 @@
       </c>
       <c r="J257" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K257" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="258" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A258" s="15" t="s">
         <v>768</v>
       </c>
@@ -19862,14 +19826,14 @@
       </c>
       <c r="J258" s="56">
         <f t="shared" ca="1" si="6"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K258" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="259" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A259" s="15" t="s">
         <v>768</v>
       </c>
@@ -19897,14 +19861,14 @@
       </c>
       <c r="J259" s="56">
         <f t="shared" ref="J259:J297" ca="1" si="8">IFERROR((H259-$K$1),0)</f>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K259" s="56">
         <f t="shared" ref="K259:K297" ca="1" si="9">IF(I259="ยังไม่ได้ทำ BG",-9999,IF(OR(I259="ค้ำเงินสด",I259="ค้ำประกันรายได้",I259="วงเงินรวม SCG"),999,IFERROR((I259-$K$1),0)))</f>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="260" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A260" s="15" t="s">
         <v>768</v>
       </c>
@@ -19932,14 +19896,14 @@
       </c>
       <c r="J260" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K260" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="261" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A261" s="15" t="s">
         <v>768</v>
       </c>
@@ -19967,14 +19931,14 @@
       </c>
       <c r="J261" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K261" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="262" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A262" s="15" t="s">
         <v>768</v>
       </c>
@@ -20002,14 +19966,14 @@
       </c>
       <c r="J262" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K262" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="263" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A263" s="15" t="s">
         <v>768</v>
       </c>
@@ -20037,14 +20001,14 @@
       </c>
       <c r="J263" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K263" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>42</v>
-      </c>
-    </row>
-    <row r="264" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A264" s="15" t="s">
         <v>768</v>
       </c>
@@ -20072,14 +20036,14 @@
       </c>
       <c r="J264" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K264" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>735</v>
-      </c>
-    </row>
-    <row r="265" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A265" s="15" t="s">
         <v>768</v>
       </c>
@@ -20107,14 +20071,14 @@
       </c>
       <c r="J265" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K265" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>735</v>
-      </c>
-    </row>
-    <row r="266" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A266" s="15" t="s">
         <v>768</v>
       </c>
@@ -20142,14 +20106,14 @@
       </c>
       <c r="J266" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K266" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>1221</v>
-      </c>
-    </row>
-    <row r="267" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A267" s="7" t="s">
         <v>768</v>
       </c>
@@ -20177,14 +20141,14 @@
       </c>
       <c r="J267" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K267" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>558</v>
-      </c>
-    </row>
-    <row r="268" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A268" s="15" t="s">
         <v>768</v>
       </c>
@@ -20212,14 +20176,14 @@
       </c>
       <c r="J268" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K268" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>490</v>
-      </c>
-    </row>
-    <row r="269" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A269" s="15" t="s">
         <v>768</v>
       </c>
@@ -20247,14 +20211,14 @@
       </c>
       <c r="J269" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K269" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>490</v>
-      </c>
-    </row>
-    <row r="270" spans="1:11" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" ht="21.75" customHeight="1" thickBot="1">
       <c r="A270" s="15" t="s">
         <v>768</v>
       </c>
@@ -20282,14 +20246,14 @@
       </c>
       <c r="J270" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K270" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>855</v>
-      </c>
-    </row>
-    <row r="271" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A271" s="15" t="s">
         <v>768</v>
       </c>
@@ -20317,14 +20281,14 @@
       </c>
       <c r="J271" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K271" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="272" spans="1:11" ht="20.25" hidden="1" customHeight="1" thickBot="1">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
       <c r="A272" s="15" t="s">
         <v>768</v>
       </c>
@@ -20352,14 +20316,14 @@
       </c>
       <c r="J272" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K272" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>124</v>
-      </c>
-    </row>
-    <row r="273" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A273" s="15" t="s">
         <v>768</v>
       </c>
@@ -20387,14 +20351,14 @@
       </c>
       <c r="J273" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K273" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>854</v>
-      </c>
-    </row>
-    <row r="274" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A274" s="15" t="s">
         <v>768</v>
       </c>
@@ -20422,14 +20386,14 @@
       </c>
       <c r="J274" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K274" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>854</v>
-      </c>
-    </row>
-    <row r="275" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A275" s="15" t="s">
         <v>768</v>
       </c>
@@ -20457,14 +20421,14 @@
       </c>
       <c r="J275" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K275" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>854</v>
-      </c>
-    </row>
-    <row r="276" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A276" s="41" t="s">
         <v>768</v>
       </c>
@@ -20494,14 +20458,14 @@
       </c>
       <c r="J276" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K276" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>642</v>
-      </c>
-    </row>
-    <row r="277" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A277" s="15" t="s">
         <v>768</v>
       </c>
@@ -20529,14 +20493,14 @@
       </c>
       <c r="J277" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K277" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="278" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+    <row r="278" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A278" s="15" t="s">
         <v>768</v>
       </c>
@@ -20564,14 +20528,14 @@
       </c>
       <c r="J278" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K278" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>275</v>
-      </c>
-    </row>
-    <row r="279" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A279" s="15" t="s">
         <v>768</v>
       </c>
@@ -20599,14 +20563,14 @@
       </c>
       <c r="J279" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K279" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>275</v>
-      </c>
-    </row>
-    <row r="280" spans="1:11" ht="21" hidden="1" customHeight="1" thickBot="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" ht="21" customHeight="1" thickBot="1">
       <c r="A280" s="15" t="s">
         <v>768</v>
       </c>
@@ -20634,14 +20598,14 @@
       </c>
       <c r="J280" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K280" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="281" spans="1:11" ht="17.5" hidden="1" thickBot="1">
+    <row r="281" spans="1:11" ht="17.5" thickBot="1">
       <c r="A281" s="15" t="s">
         <v>768</v>
       </c>
@@ -20669,14 +20633,14 @@
       </c>
       <c r="J281" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K281" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="282" spans="1:11" ht="17.5" hidden="1" thickBot="1">
+    <row r="282" spans="1:11" ht="17.5" thickBot="1">
       <c r="A282" s="15" t="s">
         <v>768</v>
       </c>
@@ -20704,14 +20668,14 @@
       </c>
       <c r="J282" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K282" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="283" spans="1:11" ht="17.5" hidden="1" thickBot="1">
+    <row r="283" spans="1:11" ht="17.5" thickBot="1">
       <c r="A283" s="15" t="s">
         <v>768</v>
       </c>
@@ -20739,14 +20703,14 @@
       </c>
       <c r="J283" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K283" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="284" spans="1:11" ht="17.5" hidden="1" thickBot="1">
+    <row r="284" spans="1:11" ht="17.5" thickBot="1">
       <c r="A284" s="15" t="s">
         <v>768</v>
       </c>
@@ -20774,14 +20738,14 @@
       </c>
       <c r="J284" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K284" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="285" spans="1:11" ht="17.5" hidden="1" thickBot="1">
+    <row r="285" spans="1:11" ht="17.5" thickBot="1">
       <c r="A285" s="15" t="s">
         <v>768</v>
       </c>
@@ -20809,14 +20773,14 @@
       </c>
       <c r="J285" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K285" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="286" spans="1:11" ht="17.5" hidden="1" thickBot="1">
+    <row r="286" spans="1:11" ht="17.5" thickBot="1">
       <c r="A286" s="15" t="s">
         <v>768</v>
       </c>
@@ -20844,14 +20808,14 @@
       </c>
       <c r="J286" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K286" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="287" spans="1:11" ht="17.5" hidden="1" thickBot="1">
+    <row r="287" spans="1:11" ht="17.5" thickBot="1">
       <c r="A287" s="15" t="s">
         <v>768</v>
       </c>
@@ -20879,14 +20843,14 @@
       </c>
       <c r="J287" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K287" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="288" spans="1:11" ht="17.5" hidden="1" thickBot="1">
+    <row r="288" spans="1:11" ht="17.5" thickBot="1">
       <c r="A288" s="15" t="s">
         <v>768</v>
       </c>
@@ -20914,14 +20878,14 @@
       </c>
       <c r="J288" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K288" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="289" spans="1:11 16361:16361" ht="17.5" hidden="1" thickBot="1">
+    <row r="289" spans="1:11 16361:16361" ht="17.5" thickBot="1">
       <c r="A289" s="15" t="s">
         <v>768</v>
       </c>
@@ -20949,14 +20913,14 @@
       </c>
       <c r="J289" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="K289" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="290" spans="1:11 16361:16361" ht="21.75" hidden="1" customHeight="1" thickBot="1">
+    <row r="290" spans="1:11 16361:16361" ht="21.75" customHeight="1" thickBot="1">
       <c r="A290" s="15" t="s">
         <v>768</v>
       </c>
@@ -20984,14 +20948,14 @@
       </c>
       <c r="J290" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K290" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="291" spans="1:11 16361:16361" ht="17.5" hidden="1" thickBot="1">
+    <row r="291" spans="1:11 16361:16361" ht="17.5" thickBot="1">
       <c r="A291" s="15" t="s">
         <v>768</v>
       </c>
@@ -21019,7 +20983,7 @@
       </c>
       <c r="J291" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K291" s="56">
         <f t="shared" si="9"/>
@@ -21027,7 +20991,7 @@
       </c>
       <c r="XEG291" s="46"/>
     </row>
-    <row r="292" spans="1:11 16361:16361" ht="17.5" hidden="1" thickBot="1">
+    <row r="292" spans="1:11 16361:16361" ht="17.5" thickBot="1">
       <c r="A292" s="15" t="s">
         <v>768</v>
       </c>
@@ -21055,15 +21019,15 @@
       </c>
       <c r="J292" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K292" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="XEG292" s="46"/>
     </row>
-    <row r="293" spans="1:11 16361:16361" ht="17.5" hidden="1" thickBot="1">
+    <row r="293" spans="1:11 16361:16361" ht="17.5" thickBot="1">
       <c r="A293" s="15" t="s">
         <v>768</v>
       </c>
@@ -21091,7 +21055,7 @@
       </c>
       <c r="J293" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K293" s="56">
         <f t="shared" si="9"/>
@@ -21099,7 +21063,7 @@
       </c>
       <c r="XEG293" s="46"/>
     </row>
-    <row r="294" spans="1:11 16361:16361" ht="17.5" hidden="1" thickBot="1">
+    <row r="294" spans="1:11 16361:16361" ht="17.5" thickBot="1">
       <c r="A294" s="15" t="s">
         <v>768</v>
       </c>
@@ -21127,14 +21091,14 @@
       </c>
       <c r="J294" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="K294" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="295" spans="1:11 16361:16361" ht="17.5" hidden="1" thickBot="1">
+    <row r="295" spans="1:11 16361:16361" ht="17.5" thickBot="1">
       <c r="A295" s="15" t="s">
         <v>768</v>
       </c>
@@ -21160,14 +21124,14 @@
       </c>
       <c r="J295" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>-244589</v>
+        <v>-244594</v>
       </c>
       <c r="K295" s="56">
         <f t="shared" si="9"/>
         <v>999</v>
       </c>
     </row>
-    <row r="296" spans="1:11 16361:16361" ht="17.5" hidden="1" thickBot="1">
+    <row r="296" spans="1:11 16361:16361" ht="17.5" thickBot="1">
       <c r="A296" s="15" t="s">
         <v>768</v>
       </c>
@@ -21191,15 +21155,15 @@
       <c r="I296" s="57"/>
       <c r="J296" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>-244589</v>
+        <v>-244594</v>
       </c>
       <c r="K296" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>-244589</v>
+        <v>-244594</v>
       </c>
       <c r="XEG296" s="46"/>
     </row>
-    <row r="297" spans="1:11 16361:16361" ht="17.5" hidden="1" thickBot="1">
+    <row r="297" spans="1:11 16361:16361" ht="17.5" thickBot="1">
       <c r="A297" s="15" t="s">
         <v>768</v>
       </c>
@@ -21223,126 +21187,115 @@
       <c r="I297" s="57"/>
       <c r="J297" s="56">
         <f t="shared" ca="1" si="8"/>
-        <v>-244589</v>
+        <v>-244594</v>
       </c>
       <c r="K297" s="56">
         <f t="shared" ca="1" si="9"/>
-        <v>-244589</v>
+        <v>-244594</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I297" xr:uid="{2ADD9999-E05E-4DFC-9ACA-F5F92389CAD8}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="NORTHEAST"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="5">
-      <filters>
-        <dateGroupItem year="2569" month="8" dateTimeGrouping="month"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I297" xr:uid="{2ADD9999-E05E-4DFC-9ACA-F5F92389CAD8}"/>
   <sortState ref="A2:G296">
     <sortCondition ref="A2:A296"/>
   </sortState>
-  <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G293 F261:G275 F277:F293 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F214:F231 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204 F4:F5 F51 F27:F28 F56 F65:G100 G203:G204 F102:G202 E295:E297 A295:D296 F295:G296 A3:E204 A206:E293 A205:D205 G206:G211">
-    <cfRule type="expression" dxfId="43" priority="366">
+  <conditionalFormatting sqref="G42 A2:G2 G213:G230 G232:G260 G276:G293 F261:G275 F277:F293 F29:G40 F57:G58 F43:G50 F60:G63 F52:G55 F6:G26 F3:G3 F233:F235 F251:F260 F245:F247 F237:F242 F207:F210 F41:F42 F249 F64 F204 F4:F5 F51 F27:F28 F56 F65:G100 G203:G204 F102:G202 E295:E297 A295:D296 F295:G296 A3:E204 A206:E293 A205:D205 G206:G211 F214:F231">
+    <cfRule type="expression" dxfId="38" priority="366">
       <formula>$F2="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G101">
-    <cfRule type="expression" dxfId="42" priority="277">
+    <cfRule type="expression" dxfId="37" priority="277">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G4">
-    <cfRule type="expression" dxfId="41" priority="252">
+    <cfRule type="expression" dxfId="36" priority="252">
       <formula>$F4="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5">
-    <cfRule type="expression" dxfId="40" priority="251">
+    <cfRule type="expression" dxfId="35" priority="251">
       <formula>$F5="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G27">
-    <cfRule type="expression" dxfId="39" priority="250">
+    <cfRule type="expression" dxfId="34" priority="250">
       <formula>$F27="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G41">
-    <cfRule type="expression" dxfId="38" priority="247">
+    <cfRule type="expression" dxfId="33" priority="247">
       <formula>$F41="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G51">
-    <cfRule type="expression" dxfId="37" priority="245">
+    <cfRule type="expression" dxfId="32" priority="245">
       <formula>$F51="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G64">
-    <cfRule type="expression" dxfId="36" priority="244">
+    <cfRule type="expression" dxfId="31" priority="244">
       <formula>$F64="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G56">
-    <cfRule type="expression" dxfId="35" priority="243">
+    <cfRule type="expression" dxfId="30" priority="243">
       <formula>$F56="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G28">
-    <cfRule type="expression" dxfId="34" priority="229">
+    <cfRule type="expression" dxfId="29" priority="229">
       <formula>$F28="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G59">
-    <cfRule type="expression" dxfId="33" priority="223">
+    <cfRule type="expression" dxfId="28" priority="223">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101">
-    <cfRule type="expression" dxfId="32" priority="205">
+    <cfRule type="expression" dxfId="27" priority="205">
       <formula>$F101="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A297">
-    <cfRule type="expression" dxfId="31" priority="203">
+    <cfRule type="expression" dxfId="26" priority="203">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F203">
-    <cfRule type="expression" dxfId="29" priority="193">
+    <cfRule type="expression" dxfId="25" priority="193">
       <formula>$F203="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F59">
-    <cfRule type="expression" dxfId="28" priority="172">
+    <cfRule type="expression" dxfId="24" priority="172">
       <formula>$F59="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G212">
-    <cfRule type="expression" dxfId="27" priority="171">
+    <cfRule type="expression" dxfId="23" priority="171">
       <formula>$F212="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B297">
-    <cfRule type="expression" dxfId="26" priority="165">
+    <cfRule type="expression" dxfId="22" priority="165">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F297">
-    <cfRule type="expression" dxfId="25" priority="163">
+    <cfRule type="expression" dxfId="21" priority="163">
       <formula>$F297="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F236">
-    <cfRule type="expression" dxfId="23" priority="139">
+    <cfRule type="expression" dxfId="20" priority="139">
       <formula>$F236="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F250">
-    <cfRule type="expression" dxfId="22" priority="135">
+    <cfRule type="expression" dxfId="19" priority="135">
       <formula>$F250="ปิดชั่วคราว"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/SmartLicense.xlsx
+++ b/SmartLicense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E6BF2C-0286-4F65-9DEF-B4618129367E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EA4256-D746-466F-A0EC-95B9C31DF26C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14834,7 +14834,7 @@
         <v>775</v>
       </c>
       <c r="F117" s="32">
-        <v>244592</v>
+        <v>244622</v>
       </c>
       <c r="G117" s="33" t="s">
         <v>3</v>

--- a/SmartLicense.xlsx
+++ b/SmartLicense.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\DASHBOARD สัญญา\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EA4256-D746-466F-A0EC-95B9C31DF26C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6746CAB-90C0-4B93-A9CC-5603385D8227}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="90" yWindow="1670" windowWidth="16260" windowHeight="4220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18760,7 +18760,7 @@
         <v>245626</v>
       </c>
       <c r="I228" s="57">
-        <v>244590</v>
+        <v>244955</v>
       </c>
       <c r="J228" s="56">
         <f t="shared" ca="1" si="6"/>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="K228" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>-4</v>
+        <v>361</v>
       </c>
     </row>
     <row r="229" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
@@ -18795,7 +18795,7 @@
         <v>245260</v>
       </c>
       <c r="I229" s="57">
-        <v>244590</v>
+        <v>244955</v>
       </c>
       <c r="J229" s="56">
         <f t="shared" ca="1" si="6"/>
@@ -18803,7 +18803,7 @@
       </c>
       <c r="K229" s="56">
         <f t="shared" ca="1" si="7"/>
-        <v>-4</v>
+        <v>361</v>
       </c>
     </row>
     <row r="230" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
